--- a/src/attributions/attributions_saliency_traj_469.xlsx
+++ b/src/attributions/attributions_saliency_traj_469.xlsx
@@ -999,571 +999,571 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>0.004858608823269606</v>
+        <v>4.772743658620904e-11</v>
       </c>
       <c r="B2" t="n">
-        <v>0.07132245600223541</v>
+        <v>1.462488116721339e-11</v>
       </c>
       <c r="C2" t="n">
-        <v>0.005224904045462608</v>
+        <v>4.096143910170547e-11</v>
       </c>
       <c r="D2" t="n">
-        <v>0.02196274325251579</v>
+        <v>8.822917396678065e-11</v>
       </c>
       <c r="E2" t="n">
-        <v>0.01575196348130703</v>
+        <v>1.735259436141945e-10</v>
       </c>
       <c r="F2" t="n">
-        <v>0.01883189007639885</v>
+        <v>1.65811531172011e-10</v>
       </c>
       <c r="G2" t="n">
-        <v>0.0009021861478686333</v>
+        <v>8.221143210640491e-11</v>
       </c>
       <c r="H2" t="n">
-        <v>0.03169742971658707</v>
+        <v>1.139534473726389e-11</v>
       </c>
       <c r="I2" t="n">
-        <v>0.06177708506584167</v>
+        <v>1.204646278563093e-11</v>
       </c>
       <c r="J2" t="n">
-        <v>0.01773512735962868</v>
+        <v>3.466612066849173e-11</v>
       </c>
       <c r="K2" t="n">
-        <v>0.05718287080526352</v>
+        <v>7.970055865280656e-11</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0005658455193042755</v>
+        <v>1.275385526355866e-11</v>
       </c>
       <c r="M2" t="n">
-        <v>0.0356341227889061</v>
+        <v>1.066066263044618e-10</v>
       </c>
       <c r="N2" t="n">
-        <v>0.0360933244228363</v>
+        <v>1.88557072733353e-10</v>
       </c>
       <c r="O2" t="n">
-        <v>0.02108196914196014</v>
+        <v>2.308624402758142e-10</v>
       </c>
       <c r="P2" t="n">
-        <v>0.005530941765755415</v>
+        <v>5.83646464491494e-11</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.01452624797821045</v>
+        <v>6.073375830029093e-11</v>
       </c>
       <c r="R2" t="n">
-        <v>0.05824650079011917</v>
+        <v>2.765884223043802e-11</v>
       </c>
       <c r="S2" t="n">
-        <v>0.003777314908802509</v>
+        <v>2.572239643505725e-11</v>
       </c>
       <c r="T2" t="n">
-        <v>0.0108437966555357</v>
+        <v>1.288929987047771e-11</v>
       </c>
       <c r="U2" t="n">
-        <v>0.01041878666728735</v>
+        <v>7.975667001836051e-12</v>
       </c>
       <c r="V2" t="n">
-        <v>0.009096171706914902</v>
+        <v>7.899714216108578e-11</v>
       </c>
       <c r="W2" t="n">
-        <v>0.0008301667403429747</v>
+        <v>3.632980027923338e-11</v>
       </c>
       <c r="X2" t="n">
-        <v>0.01187621988356113</v>
+        <v>8.248459207327308e-12</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.005386232398450375</v>
+        <v>2.880776867053569e-11</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.003828613553196192</v>
+        <v>3.903215944900396e-11</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.003804194740951061</v>
+        <v>1.688644016284435e-11</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.01326406747102737</v>
+        <v>3.774457135730103e-11</v>
       </c>
       <c r="AC2" t="n">
-        <v>0.003716205712407827</v>
+        <v>2.056588059573539e-11</v>
       </c>
       <c r="AD2" t="n">
-        <v>0.02876567095518112</v>
+        <v>5.99906652132276e-11</v>
       </c>
       <c r="AE2" t="n">
-        <v>0.004726060666143894</v>
+        <v>1.243865010991385e-10</v>
       </c>
       <c r="AF2" t="n">
-        <v>0.00660665100440383</v>
+        <v>9.893576236041923e-11</v>
       </c>
       <c r="AG2" t="n">
-        <v>0.01978455856442451</v>
+        <v>3.109396420897248e-11</v>
       </c>
       <c r="AH2" t="n">
-        <v>0.003112748265266418</v>
+        <v>2.21411344120126e-11</v>
       </c>
       <c r="AI2" t="n">
-        <v>0.0108047341927886</v>
+        <v>5.911719030970986e-11</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0.0002149161882698536</v>
+        <v>4.438449260901756e-11</v>
       </c>
       <c r="AK2" t="n">
-        <v>0.005901900585740805</v>
+        <v>3.614340077229272e-11</v>
       </c>
       <c r="AL2" t="n">
-        <v>0.006699255667626858</v>
+        <v>2.426285561352159e-11</v>
       </c>
       <c r="AM2" t="n">
-        <v>0.003408890450373292</v>
+        <v>9.51993258530015e-12</v>
       </c>
       <c r="AN2" t="n">
-        <v>0.0002728128747548908</v>
+        <v>2.117404168666681e-11</v>
       </c>
       <c r="AO2" t="n">
-        <v>0.01602398790419102</v>
+        <v>3.727260861063897e-11</v>
       </c>
       <c r="AP2" t="n">
-        <v>0.01237685047090054</v>
+        <v>3.739982282202625e-11</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0.005200657993555069</v>
+        <v>5.524454851912886e-11</v>
       </c>
       <c r="AR2" t="n">
-        <v>0.008139407262206078</v>
+        <v>2.659583143993505e-11</v>
       </c>
       <c r="AS2" t="n">
-        <v>0.00423846859484911</v>
+        <v>1.716798925244234e-11</v>
       </c>
       <c r="AT2" t="n">
-        <v>0.004153801128268242</v>
+        <v>2.64988708059688e-11</v>
       </c>
       <c r="AU2" t="n">
-        <v>0.05602898076176643</v>
+        <v>2.501259477316609e-10</v>
       </c>
       <c r="AV2" t="n">
-        <v>0.007624452468007803</v>
+        <v>1.797756713460552e-12</v>
       </c>
       <c r="AW2" t="n">
-        <v>0.01212265994399786</v>
+        <v>1.847220987283293e-11</v>
       </c>
       <c r="AX2" t="n">
-        <v>0.02139810472726822</v>
+        <v>4.056971425470124e-11</v>
       </c>
       <c r="AY2" t="n">
-        <v>0.005989032797515392</v>
+        <v>1.64969340271659e-11</v>
       </c>
       <c r="AZ2" t="n">
-        <v>0.02226714789867401</v>
+        <v>4.296230732281359e-11</v>
       </c>
       <c r="BA2" t="n">
-        <v>0.001697429572232068</v>
+        <v>4.946158066454487e-11</v>
       </c>
       <c r="BB2" t="n">
-        <v>0.01615142822265625</v>
+        <v>5.227662920603837e-12</v>
       </c>
       <c r="BC2" t="n">
-        <v>0.006472441833466291</v>
+        <v>3.602201176233777e-11</v>
       </c>
       <c r="BD2" t="n">
-        <v>0.008356781676411629</v>
+        <v>9.328858519008776e-11</v>
       </c>
       <c r="BE2" t="n">
-        <v>0.01134651899337769</v>
+        <v>2.923445513447476e-11</v>
       </c>
       <c r="BF2" t="n">
-        <v>0.0002972509246319532</v>
+        <v>7.011215913399482e-11</v>
       </c>
       <c r="BG2" t="n">
-        <v>0.01329950895160437</v>
+        <v>1.468477561772374e-10</v>
       </c>
       <c r="BH2" t="n">
-        <v>0.02425804734230042</v>
+        <v>1.078030720247369e-10</v>
       </c>
       <c r="BI2" t="n">
-        <v>0.00360042555257678</v>
+        <v>2.436163250296719e-11</v>
       </c>
       <c r="BJ2" t="n">
-        <v>0.0104032289236784</v>
+        <v>3.126140318832071e-11</v>
       </c>
       <c r="BK2" t="n">
-        <v>0.04728471487760544</v>
+        <v>2.061187158453048e-11</v>
       </c>
       <c r="BL2" t="n">
-        <v>0.00626553175970912</v>
+        <v>2.915975447215224e-11</v>
       </c>
       <c r="BM2" t="n">
-        <v>0.01034356933087111</v>
+        <v>9.636148129432698e-11</v>
       </c>
       <c r="BN2" t="n">
-        <v>0.0005136530380696058</v>
+        <v>1.077220777856436e-11</v>
       </c>
       <c r="BO2" t="n">
-        <v>0.007745637558400631</v>
+        <v>3.82801429443802e-14</v>
       </c>
       <c r="BP2" t="n">
-        <v>0.05082781612873077</v>
+        <v>9.853339671961336e-11</v>
       </c>
       <c r="BQ2" t="n">
-        <v>0.0143874017521739</v>
+        <v>4.419858576354407e-11</v>
       </c>
       <c r="BR2" t="n">
-        <v>0.008963948115706444</v>
+        <v>1.10146579357373e-10</v>
       </c>
       <c r="BS2" t="n">
-        <v>0.003796042408794165</v>
+        <v>2.381603247947339e-11</v>
       </c>
       <c r="BT2" t="n">
-        <v>0.0130225345492363</v>
+        <v>3.76949790825698e-11</v>
       </c>
       <c r="BU2" t="n">
-        <v>0.001242356724105775</v>
+        <v>2.626366485403153e-11</v>
       </c>
       <c r="BV2" t="n">
-        <v>0.03569778800010681</v>
+        <v>1.130730925558154e-10</v>
       </c>
       <c r="BW2" t="n">
-        <v>0.01558982022106647</v>
+        <v>1.917533840045671e-12</v>
       </c>
       <c r="BX2" t="n">
-        <v>0.01402324251830578</v>
+        <v>7.085443343157749e-12</v>
       </c>
       <c r="BY2" t="n">
-        <v>0.0004364836495369673</v>
+        <v>9.848741960860607e-11</v>
       </c>
       <c r="BZ2" t="n">
-        <v>0.006403504870831966</v>
+        <v>9.34253195639112e-12</v>
       </c>
       <c r="CA2" t="n">
-        <v>0.001756946323439479</v>
+        <v>2.339802830653159e-11</v>
       </c>
       <c r="CB2" t="n">
-        <v>0.002138874726369977</v>
+        <v>5.001041941676831e-11</v>
       </c>
       <c r="CC2" t="n">
-        <v>0.004783318378031254</v>
+        <v>1.951728015314735e-11</v>
       </c>
       <c r="CD2" t="n">
-        <v>0.0004683654988184571</v>
+        <v>5.75790196771786e-12</v>
       </c>
       <c r="CE2" t="n">
-        <v>0.01162859052419662</v>
+        <v>1.425510837843591e-11</v>
       </c>
       <c r="CF2" t="n">
-        <v>0.005593833513557911</v>
+        <v>9.457485142250199e-12</v>
       </c>
       <c r="CG2" t="n">
-        <v>0.0007763924659229815</v>
+        <v>4.111092369307734e-11</v>
       </c>
       <c r="CH2" t="n">
-        <v>0.002395227318629622</v>
+        <v>4.007861750809916e-11</v>
       </c>
       <c r="CI2" t="n">
-        <v>0.00307756382972002</v>
+        <v>3.437568632524979e-11</v>
       </c>
       <c r="CJ2" t="n">
-        <v>0.0001577825751155615</v>
+        <v>4.09286458891156e-11</v>
       </c>
       <c r="CK2" t="n">
-        <v>0.003788806032389402</v>
+        <v>6.127707716241382e-12</v>
       </c>
       <c r="CL2" t="n">
-        <v>0.01335454918444157</v>
+        <v>3.34568896025178e-12</v>
       </c>
       <c r="CM2" t="n">
-        <v>0.02156591601669788</v>
+        <v>8.584736393979497e-11</v>
       </c>
       <c r="CN2" t="n">
-        <v>0.01426036190241575</v>
+        <v>1.841739538654963e-10</v>
       </c>
       <c r="CO2" t="n">
-        <v>0.0001594468485563993</v>
+        <v>7.470205010129405e-13</v>
       </c>
       <c r="CP2" t="n">
-        <v>0.01077665109187365</v>
+        <v>1.257962345402319e-10</v>
       </c>
       <c r="CQ2" t="n">
-        <v>0.01149892061948776</v>
+        <v>9.29805468730116e-11</v>
       </c>
       <c r="CR2" t="n">
-        <v>0.01194297801703215</v>
+        <v>1.619527255358744e-11</v>
       </c>
       <c r="CS2" t="n">
-        <v>0.01524183992296457</v>
+        <v>2.036241487923807e-11</v>
       </c>
       <c r="CT2" t="n">
-        <v>0.03255921602249146</v>
+        <v>4.602761921601584e-11</v>
       </c>
       <c r="CU2" t="n">
-        <v>0.01188178453594446</v>
+        <v>2.751875290141204e-11</v>
       </c>
       <c r="CV2" t="n">
-        <v>0.0002568796335253865</v>
+        <v>1.880668537568297e-11</v>
       </c>
       <c r="CW2" t="n">
-        <v>0.01215789094567299</v>
+        <v>1.996196437314968e-11</v>
       </c>
       <c r="CX2" t="n">
-        <v>0.006156176794320345</v>
+        <v>7.285294763292871e-12</v>
       </c>
       <c r="CY2" t="n">
-        <v>0.002033152617514133</v>
+        <v>3.106868581848055e-11</v>
       </c>
       <c r="CZ2" t="n">
-        <v>0.00626109354197979</v>
+        <v>2.740154804448114e-11</v>
       </c>
       <c r="DA2" t="n">
-        <v>0.001264799619093537</v>
+        <v>3.883728061371272e-11</v>
       </c>
       <c r="DB2" t="n">
-        <v>0.002040026010945439</v>
+        <v>2.341428786967192e-11</v>
       </c>
       <c r="DC2" t="n">
-        <v>0.003617795649915934</v>
+        <v>1.25209556264827e-11</v>
       </c>
       <c r="DD2" t="n">
-        <v>0.008345424197614193</v>
+        <v>1.367613487734953e-11</v>
       </c>
       <c r="DE2" t="n">
-        <v>0.008307947777211666</v>
+        <v>5.542934167213076e-11</v>
       </c>
       <c r="DF2" t="n">
-        <v>0.02228358946740627</v>
+        <v>2.659473682942171e-11</v>
       </c>
       <c r="DG2" t="n">
-        <v>0.006252055056393147</v>
+        <v>2.014925726268046e-11</v>
       </c>
       <c r="DH2" t="n">
-        <v>0.01917950063943863</v>
+        <v>4.51291157221867e-11</v>
       </c>
       <c r="DI2" t="n">
-        <v>0.002001740504056215</v>
+        <v>3.699822392899677e-11</v>
       </c>
       <c r="DJ2" t="n">
-        <v>0.0006104774656705558</v>
+        <v>1.873869982793597e-11</v>
       </c>
       <c r="DK2" t="n">
-        <v>0.008411390706896782</v>
+        <v>7.446200600558228e-11</v>
       </c>
       <c r="DL2" t="n">
-        <v>0.02604223415255547</v>
+        <v>2.571946995655328e-11</v>
       </c>
       <c r="DM2" t="n">
-        <v>0.006287992000579834</v>
+        <v>6.840874654939766e-12</v>
       </c>
       <c r="DN2" t="n">
-        <v>0.002186226192861795</v>
+        <v>8.603119952543814e-12</v>
       </c>
       <c r="DO2" t="n">
-        <v>0.01227278914302588</v>
+        <v>1.14517726898522e-11</v>
       </c>
       <c r="DP2" t="n">
-        <v>0.004030261188745499</v>
+        <v>1.979891944836609e-11</v>
       </c>
       <c r="DQ2" t="n">
-        <v>0.002459663897752762</v>
+        <v>8.149120961364886e-11</v>
       </c>
       <c r="DR2" t="n">
-        <v>0.001092456746846437</v>
+        <v>9.209655954522944e-11</v>
       </c>
       <c r="DS2" t="n">
-        <v>0.0001593278429936618</v>
+        <v>5.603031927314817e-11</v>
       </c>
       <c r="DT2" t="n">
-        <v>0.01404660567641258</v>
+        <v>8.739755447129127e-11</v>
       </c>
       <c r="DU2" t="n">
-        <v>0.009906308725476265</v>
+        <v>5.777481271174167e-11</v>
       </c>
       <c r="DV2" t="n">
-        <v>0.007629372179508209</v>
+        <v>2.53883043060954e-11</v>
       </c>
       <c r="DW2" t="n">
-        <v>0.0005124129820615053</v>
+        <v>2.420565484162474e-11</v>
       </c>
       <c r="DX2" t="n">
-        <v>0.02732754871249199</v>
+        <v>6.444905720215388e-11</v>
       </c>
       <c r="DY2" t="n">
-        <v>0.003487769514322281</v>
+        <v>3.829833672419625e-11</v>
       </c>
       <c r="DZ2" t="n">
-        <v>0.002895111683756113</v>
+        <v>4.842840017893479e-11</v>
       </c>
       <c r="EA2" t="n">
-        <v>0.006391825154423714</v>
+        <v>6.205162772499051e-11</v>
       </c>
       <c r="EB2" t="n">
-        <v>0.008932624012231827</v>
+        <v>2.451603330066998e-11</v>
       </c>
       <c r="EC2" t="n">
-        <v>0.005889417603611946</v>
+        <v>2.957793732161207e-12</v>
       </c>
       <c r="ED2" t="n">
-        <v>0.01383450627326965</v>
+        <v>8.263472545122497e-11</v>
       </c>
       <c r="EE2" t="n">
-        <v>0.002699139527976513</v>
+        <v>1.348710726434277e-11</v>
       </c>
       <c r="EF2" t="n">
-        <v>0.0009922732133418322</v>
+        <v>4.480995782762953e-11</v>
       </c>
       <c r="EG2" t="n">
-        <v>0.0001370413228869438</v>
+        <v>3.12057012175071e-11</v>
       </c>
       <c r="EH2" t="n">
-        <v>0.01016294024884701</v>
+        <v>5.781721455766498e-12</v>
       </c>
       <c r="EI2" t="n">
-        <v>0.001720157451927662</v>
+        <v>2.357410620879019e-11</v>
       </c>
       <c r="EJ2" t="n">
-        <v>0.01346644945442677</v>
+        <v>1.176839875549618e-11</v>
       </c>
       <c r="EK2" t="n">
-        <v>0.0003210257855243981</v>
+        <v>1.760540498108032e-11</v>
       </c>
       <c r="EL2" t="n">
-        <v>0.006044507492333651</v>
+        <v>2.270160448514247e-11</v>
       </c>
       <c r="EM2" t="n">
-        <v>0.002529148943722248</v>
+        <v>2.701475675104259e-11</v>
       </c>
       <c r="EN2" t="n">
-        <v>0.01617663353681564</v>
+        <v>1.53668848479338e-11</v>
       </c>
       <c r="EO2" t="n">
-        <v>0.003167493036016822</v>
+        <v>2.896432919896608e-11</v>
       </c>
       <c r="EP2" t="n">
-        <v>0.008010666817426682</v>
+        <v>3.712655877174953e-11</v>
       </c>
       <c r="EQ2" t="n">
-        <v>0.008254979737102985</v>
+        <v>1.748563620285193e-11</v>
       </c>
       <c r="ER2" t="n">
-        <v>0.001985382288694382</v>
+        <v>5.120927293322808e-11</v>
       </c>
       <c r="ES2" t="n">
-        <v>0.01007205620408058</v>
+        <v>3.760945374575719e-11</v>
       </c>
       <c r="ET2" t="n">
-        <v>0.002719052135944366</v>
+        <v>2.99204975032219e-12</v>
       </c>
       <c r="EU2" t="n">
-        <v>0.01121371611952782</v>
+        <v>1.558031481607713e-11</v>
       </c>
       <c r="EV2" t="n">
-        <v>0.003275059629231691</v>
+        <v>5.304997413579926e-11</v>
       </c>
       <c r="EW2" t="n">
-        <v>0.003333104774355888</v>
+        <v>6.360263010707357e-11</v>
       </c>
       <c r="EX2" t="n">
-        <v>0.002745053730905056</v>
+        <v>1.683709421884672e-11</v>
       </c>
       <c r="EY2" t="n">
-        <v>0.01343523524701595</v>
+        <v>2.550423587599493e-11</v>
       </c>
       <c r="EZ2" t="n">
-        <v>0.004922083579003811</v>
+        <v>7.91844107644879e-12</v>
       </c>
       <c r="FA2" t="n">
-        <v>0.0005573234520852566</v>
+        <v>3.121856245735799e-11</v>
       </c>
       <c r="FB2" t="n">
-        <v>0.006436802912503481</v>
+        <v>3.946783178054858e-11</v>
       </c>
       <c r="FC2" t="n">
-        <v>0.003089801175519824</v>
+        <v>2.365126323955469e-11</v>
       </c>
       <c r="FD2" t="n">
-        <v>0.003554158611223102</v>
+        <v>2.494221496007754e-11</v>
       </c>
       <c r="FE2" t="n">
-        <v>0.001661231741309166</v>
+        <v>1.381888180274071e-11</v>
       </c>
       <c r="FF2" t="n">
-        <v>0.008339639753103256</v>
+        <v>8.072609421205801e-13</v>
       </c>
       <c r="FG2" t="n">
-        <v>0.003799998899921775</v>
+        <v>3.032235226796409e-11</v>
       </c>
       <c r="FH2" t="n">
-        <v>0.009707498364150524</v>
+        <v>3.779225196676173e-11</v>
       </c>
       <c r="FI2" t="n">
-        <v>0.002941656159237027</v>
+        <v>8.149909566657065e-12</v>
       </c>
       <c r="FJ2" t="n">
-        <v>0.002374387811869383</v>
+        <v>4.25860180452986e-11</v>
       </c>
       <c r="FK2" t="n">
-        <v>0.01304224506020546</v>
+        <v>5.954969590354908e-14</v>
       </c>
       <c r="FL2" t="n">
-        <v>0.003887325059622526</v>
+        <v>2.908222274111694e-12</v>
       </c>
       <c r="FM2" t="n">
-        <v>0.005505742505192757</v>
+        <v>1.087817076000919e-11</v>
       </c>
       <c r="FN2" t="n">
-        <v>0.0008181568700820208</v>
+        <v>6.170350341783148e-11</v>
       </c>
       <c r="FO2" t="n">
-        <v>0.002067324472591281</v>
+        <v>1.602389401722526e-11</v>
       </c>
       <c r="FP2" t="n">
-        <v>0.00595211423933506</v>
+        <v>9.403178236055965e-11</v>
       </c>
       <c r="FQ2" t="n">
-        <v>0.007984117604792118</v>
+        <v>9.058351985169466e-11</v>
       </c>
       <c r="FR2" t="n">
-        <v>0.004393045790493488</v>
+        <v>3.489118022281801e-11</v>
       </c>
       <c r="FS2" t="n">
-        <v>0.003512433264404535</v>
+        <v>5.39594965931478e-11</v>
       </c>
       <c r="FT2" t="n">
-        <v>0.001626811921596527</v>
+        <v>5.247129120089511e-12</v>
       </c>
       <c r="FU2" t="n">
-        <v>0.01786042749881744</v>
+        <v>2.106770140286596e-11</v>
       </c>
       <c r="FV2" t="n">
-        <v>0.0215088278055191</v>
+        <v>4.194417035918718e-11</v>
       </c>
       <c r="FW2" t="n">
-        <v>0.01311074011027813</v>
+        <v>5.585885920478262e-11</v>
       </c>
       <c r="FX2" t="n">
-        <v>0.002057082019746304</v>
+        <v>2.406661848974867e-11</v>
       </c>
       <c r="FY2" t="n">
-        <v>0.01132978871464729</v>
+        <v>1.372127151483271e-11</v>
       </c>
       <c r="FZ2" t="n">
-        <v>0.006100901402533054</v>
+        <v>4.854695204864479e-12</v>
       </c>
       <c r="GA2" t="n">
-        <v>0.004438214935362339</v>
+        <v>1.924040267387017e-11</v>
       </c>
       <c r="GB2" t="n">
-        <v>0.007801971398293972</v>
+        <v>8.005657768650476e-12</v>
       </c>
       <c r="GC2" t="n">
-        <v>0.003149870317429304</v>
+        <v>5.207471606705205e-12</v>
       </c>
       <c r="GD2" t="n">
-        <v>0.01722233928740025</v>
+        <v>5.424003607368277e-11</v>
       </c>
       <c r="GE2" t="n">
-        <v>0.01123045850545168</v>
+        <v>5.111691625536707e-11</v>
       </c>
       <c r="GF2" t="n">
-        <v>0.005884808488190174</v>
+        <v>3.674413204257654e-12</v>
       </c>
       <c r="GG2" t="n">
-        <v>0.0001517495838925242</v>
+        <v>3.503003226032475e-12</v>
       </c>
     </row>
     <row r="3">
@@ -2706,571 +2706,571 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>0.001694912789389491</v>
+        <v>1.141453331854336e-08</v>
       </c>
       <c r="B5" t="n">
-        <v>0.01261883322149515</v>
+        <v>4.133492659263993e-09</v>
       </c>
       <c r="C5" t="n">
-        <v>0.003025155048817396</v>
+        <v>3.848139584761157e-09</v>
       </c>
       <c r="D5" t="n">
-        <v>0.003374514635652304</v>
+        <v>1.572765029322909e-09</v>
       </c>
       <c r="E5" t="n">
-        <v>0.00659368047490716</v>
+        <v>1.593962517532077e-09</v>
       </c>
       <c r="F5" t="n">
-        <v>0.002571494551375508</v>
+        <v>1.930575344033514e-08</v>
       </c>
       <c r="G5" t="n">
-        <v>0.006670400034636259</v>
+        <v>1.327662868533253e-08</v>
       </c>
       <c r="H5" t="n">
-        <v>0.0009169141412712634</v>
+        <v>1.802134264039523e-08</v>
       </c>
       <c r="I5" t="n">
-        <v>0.007949796505272388</v>
+        <v>1.065893151519504e-09</v>
       </c>
       <c r="J5" t="n">
-        <v>0.003646224969998002</v>
+        <v>1.025387597053395e-08</v>
       </c>
       <c r="K5" t="n">
-        <v>0.01359925139695406</v>
+        <v>4.770350336968932e-09</v>
       </c>
       <c r="L5" t="n">
-        <v>0.001891112769953907</v>
+        <v>3.910281431984686e-09</v>
       </c>
       <c r="M5" t="n">
-        <v>0.00238098157569766</v>
+        <v>9.600384487384872e-09</v>
       </c>
       <c r="N5" t="n">
-        <v>0.006899044383317232</v>
+        <v>4.903326189520385e-09</v>
       </c>
       <c r="O5" t="n">
-        <v>0.0006431667134165764</v>
+        <v>2.33427179807677e-08</v>
       </c>
       <c r="P5" t="n">
-        <v>0.004806333687156439</v>
+        <v>1.91810602956366e-08</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.0002774281310848892</v>
+        <v>1.643647884463917e-08</v>
       </c>
       <c r="R5" t="n">
-        <v>0.006929701194167137</v>
+        <v>7.523639489193101e-09</v>
       </c>
       <c r="S5" t="n">
-        <v>0.001327550155110657</v>
+        <v>2.768516971229928e-09</v>
       </c>
       <c r="T5" t="n">
-        <v>0.00334344245493412</v>
+        <v>1.357551737690699e-09</v>
       </c>
       <c r="U5" t="n">
-        <v>0.0002887620939873159</v>
+        <v>2.396704612550593e-09</v>
       </c>
       <c r="V5" t="n">
-        <v>0.003212990937754512</v>
+        <v>4.584419066588907e-09</v>
       </c>
       <c r="W5" t="n">
-        <v>0.006972507573664188</v>
+        <v>2.644912955318546e-09</v>
       </c>
       <c r="X5" t="n">
-        <v>0.003473160322755575</v>
+        <v>8.867567791170927e-10</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.000950513465795666</v>
+        <v>4.307198153696845e-09</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.0006928303046151996</v>
+        <v>1.898917023623881e-09</v>
       </c>
       <c r="AA5" t="n">
-        <v>7.088291749823838e-05</v>
+        <v>4.492966443336854e-09</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.002635533921420574</v>
+        <v>1.362053225761883e-08</v>
       </c>
       <c r="AC5" t="n">
-        <v>0.001454646699130535</v>
+        <v>1.661803672448059e-08</v>
       </c>
       <c r="AD5" t="n">
-        <v>0.005330790765583515</v>
+        <v>5.069950681502178e-09</v>
       </c>
       <c r="AE5" t="n">
-        <v>0.001715211081318557</v>
+        <v>1.409186989320688e-09</v>
       </c>
       <c r="AF5" t="n">
-        <v>0.001445159665308893</v>
+        <v>6.998477797282021e-09</v>
       </c>
       <c r="AG5" t="n">
-        <v>0.000713920802809298</v>
+        <v>9.060382666348232e-09</v>
       </c>
       <c r="AH5" t="n">
-        <v>4.311831435188651e-05</v>
+        <v>1.469590560354561e-09</v>
       </c>
       <c r="AI5" t="n">
-        <v>0.003128852462396026</v>
+        <v>1.083017675540532e-08</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0.0005295263254083693</v>
+        <v>5.252043688841468e-09</v>
       </c>
       <c r="AK5" t="n">
-        <v>0.002629691734910011</v>
+        <v>1.237753233240824e-09</v>
       </c>
       <c r="AL5" t="n">
-        <v>8.822273230180144e-05</v>
+        <v>2.116290698239709e-09</v>
       </c>
       <c r="AM5" t="n">
-        <v>0.0001550859888084233</v>
+        <v>8.69469207742668e-09</v>
       </c>
       <c r="AN5" t="n">
-        <v>0.001320198527537286</v>
+        <v>6.057188084440668e-09</v>
       </c>
       <c r="AO5" t="n">
-        <v>0.0006418279372155666</v>
+        <v>2.016736222465454e-10</v>
       </c>
       <c r="AP5" t="n">
-        <v>0.0007304074242711067</v>
+        <v>3.220760547151258e-09</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0.0002503273426555097</v>
+        <v>5.018501170184209e-09</v>
       </c>
       <c r="AR5" t="n">
-        <v>0.001228309236466885</v>
+        <v>6.768633653564393e-09</v>
       </c>
       <c r="AS5" t="n">
-        <v>0.001150815631262958</v>
+        <v>1.151316375569422e-09</v>
       </c>
       <c r="AT5" t="n">
-        <v>0.001891535241156816</v>
+        <v>9.623479790832334e-11</v>
       </c>
       <c r="AU5" t="n">
-        <v>0.006866172887384892</v>
+        <v>9.154489610807559e-09</v>
       </c>
       <c r="AV5" t="n">
-        <v>0.003186912974342704</v>
+        <v>1.208270816732693e-08</v>
       </c>
       <c r="AW5" t="n">
-        <v>0.005003273952752352</v>
+        <v>6.121239071177342e-10</v>
       </c>
       <c r="AX5" t="n">
-        <v>0.0003538683522492647</v>
+        <v>8.734880374561271e-09</v>
       </c>
       <c r="AY5" t="n">
-        <v>0.001662085065618157</v>
+        <v>1.768720103711985e-08</v>
       </c>
       <c r="AZ5" t="n">
-        <v>0.006441116333007812</v>
+        <v>3.419123650871825e-09</v>
       </c>
       <c r="BA5" t="n">
-        <v>0.0001646510791033506</v>
+        <v>1.120902304307947e-08</v>
       </c>
       <c r="BB5" t="n">
-        <v>0.003917173482477665</v>
+        <v>6.021378506915198e-09</v>
       </c>
       <c r="BC5" t="n">
-        <v>0.0005507002351805568</v>
+        <v>1.431312401933837e-09</v>
       </c>
       <c r="BD5" t="n">
-        <v>0.008063919842243195</v>
+        <v>6.113443085098424e-11</v>
       </c>
       <c r="BE5" t="n">
-        <v>0.004340499639511108</v>
+        <v>1.354987233526117e-10</v>
       </c>
       <c r="BF5" t="n">
-        <v>0.000820333487354219</v>
+        <v>2.128802467638025e-09</v>
       </c>
       <c r="BG5" t="n">
-        <v>0.0005980376154184341</v>
+        <v>1.16510641134937e-08</v>
       </c>
       <c r="BH5" t="n">
-        <v>0.002061293693259358</v>
+        <v>3.830578965136056e-09</v>
       </c>
       <c r="BI5" t="n">
-        <v>0.0009514042176306248</v>
+        <v>1.308295471957877e-09</v>
       </c>
       <c r="BJ5" t="n">
-        <v>0.001466838293708861</v>
+        <v>5.955889115227819e-10</v>
       </c>
       <c r="BK5" t="n">
-        <v>0.0002216914726886898</v>
+        <v>1.56500643555546e-08</v>
       </c>
       <c r="BL5" t="n">
-        <v>0.0002521201386116445</v>
+        <v>4.231497818807384e-09</v>
       </c>
       <c r="BM5" t="n">
-        <v>0.0003687015851028264</v>
+        <v>8.72351080261069e-09</v>
       </c>
       <c r="BN5" t="n">
-        <v>0.002246157731860876</v>
+        <v>5.03357355796652e-09</v>
       </c>
       <c r="BO5" t="n">
-        <v>0.00176589039620012</v>
+        <v>2.561742595830196e-09</v>
       </c>
       <c r="BP5" t="n">
-        <v>0.008316517807543278</v>
+        <v>6.983123856940665e-09</v>
       </c>
       <c r="BQ5" t="n">
-        <v>0.00142063049133867</v>
+        <v>1.778640346117299e-09</v>
       </c>
       <c r="BR5" t="n">
-        <v>0.0006994657451286912</v>
+        <v>8.249212868349787e-09</v>
       </c>
       <c r="BS5" t="n">
-        <v>0.006047696806490421</v>
+        <v>4.430452116288564e-10</v>
       </c>
       <c r="BT5" t="n">
-        <v>0.0003538237942848355</v>
+        <v>1.137262506389902e-09</v>
       </c>
       <c r="BU5" t="n">
-        <v>0.001113238278776407</v>
+        <v>4.125833008572499e-09</v>
       </c>
       <c r="BV5" t="n">
-        <v>0.001692339079454541</v>
+        <v>6.76114897402158e-09</v>
       </c>
       <c r="BW5" t="n">
-        <v>0.001832596259191632</v>
+        <v>1.77817960356208e-09</v>
       </c>
       <c r="BX5" t="n">
-        <v>0.003592291846871376</v>
+        <v>1.525089055043338e-09</v>
       </c>
       <c r="BY5" t="n">
-        <v>0.002371362876147032</v>
+        <v>2.129360909819411e-09</v>
       </c>
       <c r="BZ5" t="n">
-        <v>0.0003896724083460867</v>
+        <v>4.03925559666618e-10</v>
       </c>
       <c r="CA5" t="n">
-        <v>0.003649113699793816</v>
+        <v>8.522185623860423e-09</v>
       </c>
       <c r="CB5" t="n">
-        <v>0.003947858698666096</v>
+        <v>1.312647879281315e-09</v>
       </c>
       <c r="CC5" t="n">
-        <v>0.002878003055229783</v>
+        <v>3.996549757800949e-09</v>
       </c>
       <c r="CD5" t="n">
-        <v>0.0004549866425804794</v>
+        <v>1.721502052021151e-09</v>
       </c>
       <c r="CE5" t="n">
-        <v>0.00256182299926877</v>
+        <v>5.529036783968877e-09</v>
       </c>
       <c r="CF5" t="n">
-        <v>0.0004264689923729748</v>
+        <v>2.883112415474898e-09</v>
       </c>
       <c r="CG5" t="n">
-        <v>0.0009981925832107663</v>
+        <v>5.03433683629595e-10</v>
       </c>
       <c r="CH5" t="n">
-        <v>0.001200038474053144</v>
+        <v>8.431590980961801e-10</v>
       </c>
       <c r="CI5" t="n">
-        <v>0.0005997598636895418</v>
+        <v>3.532011794149525e-09</v>
       </c>
       <c r="CJ5" t="n">
-        <v>0.0007767986971884966</v>
+        <v>2.983398195155473e-09</v>
       </c>
       <c r="CK5" t="n">
-        <v>0.0006200618809089065</v>
+        <v>2.335927451468933e-09</v>
       </c>
       <c r="CL5" t="n">
-        <v>8.615307160653174e-05</v>
+        <v>5.097572364221037e-10</v>
       </c>
       <c r="CM5" t="n">
-        <v>0.003594452049583197</v>
+        <v>7.447858330067447e-09</v>
       </c>
       <c r="CN5" t="n">
-        <v>0.004679652862250805</v>
+        <v>9.632789677027631e-09</v>
       </c>
       <c r="CO5" t="n">
-        <v>0.001000977121293545</v>
+        <v>1.020623763281492e-08</v>
       </c>
       <c r="CP5" t="n">
-        <v>0.005425681360065937</v>
+        <v>7.72256125713966e-09</v>
       </c>
       <c r="CQ5" t="n">
-        <v>0.007661502342671156</v>
+        <v>5.809281056201598e-09</v>
       </c>
       <c r="CR5" t="n">
-        <v>9.33879055082798e-05</v>
+        <v>7.362070952865452e-09</v>
       </c>
       <c r="CS5" t="n">
-        <v>0.001995183527469635</v>
+        <v>2.130640108788384e-09</v>
       </c>
       <c r="CT5" t="n">
-        <v>0.001298263086937368</v>
+        <v>7.132999968462173e-09</v>
       </c>
       <c r="CU5" t="n">
-        <v>0.00360071798786521</v>
+        <v>8.488808767026512e-09</v>
       </c>
       <c r="CV5" t="n">
-        <v>0.0007014383445493877</v>
+        <v>1.101600810571313e-09</v>
       </c>
       <c r="CW5" t="n">
-        <v>0.001940806745551527</v>
+        <v>3.143668436678126e-09</v>
       </c>
       <c r="CX5" t="n">
-        <v>0.0006727827712893486</v>
+        <v>3.232241807538117e-09</v>
       </c>
       <c r="CY5" t="n">
-        <v>4.464449739316478e-05</v>
+        <v>7.743860552800186e-10</v>
       </c>
       <c r="CZ5" t="n">
-        <v>0.0002970341884065419</v>
+        <v>2.987739500248665e-10</v>
       </c>
       <c r="DA5" t="n">
-        <v>0.001222116989083588</v>
+        <v>5.038210737495774e-09</v>
       </c>
       <c r="DB5" t="n">
-        <v>0.001012075575999916</v>
+        <v>1.781305547510215e-09</v>
       </c>
       <c r="DC5" t="n">
-        <v>0.001525683794170618</v>
+        <v>2.770565554754967e-09</v>
       </c>
       <c r="DD5" t="n">
-        <v>0.0008876745705492795</v>
+        <v>1.130795679316066e-09</v>
       </c>
       <c r="DE5" t="n">
-        <v>0.003943359944969416</v>
+        <v>2.376584262719916e-09</v>
       </c>
       <c r="DF5" t="n">
-        <v>0.001457970240153372</v>
+        <v>4.194577574168079e-09</v>
       </c>
       <c r="DG5" t="n">
-        <v>0.001419120002537966</v>
+        <v>1.552047557140668e-08</v>
       </c>
       <c r="DH5" t="n">
-        <v>0.004465436097234488</v>
+        <v>1.473940081098135e-08</v>
       </c>
       <c r="DI5" t="n">
-        <v>0.003931304905563593</v>
+        <v>7.306399485429438e-09</v>
       </c>
       <c r="DJ5" t="n">
-        <v>0.0001055102329701185</v>
+        <v>1.192991572196433e-08</v>
       </c>
       <c r="DK5" t="n">
-        <v>0.001025485573336482</v>
+        <v>8.771331216905764e-09</v>
       </c>
       <c r="DL5" t="n">
-        <v>0.001618881360627711</v>
+        <v>2.62856625354857e-10</v>
       </c>
       <c r="DM5" t="n">
-        <v>0.004805845208466053</v>
+        <v>5.477620579341647e-10</v>
       </c>
       <c r="DN5" t="n">
-        <v>0.003037011716514826</v>
+        <v>2.72230182840616e-10</v>
       </c>
       <c r="DO5" t="n">
-        <v>0.001992406789213419</v>
+        <v>7.476397279049252e-09</v>
       </c>
       <c r="DP5" t="n">
-        <v>0.001881466945633292</v>
+        <v>9.131723155419991e-10</v>
       </c>
       <c r="DQ5" t="n">
-        <v>0.001253043883480132</v>
+        <v>2.71441424892771e-09</v>
       </c>
       <c r="DR5" t="n">
-        <v>0.000792226055637002</v>
+        <v>7.591546058449694e-09</v>
       </c>
       <c r="DS5" t="n">
-        <v>5.627554492093623e-05</v>
+        <v>3.128045156230996e-09</v>
       </c>
       <c r="DT5" t="n">
-        <v>0.0006517480360344052</v>
+        <v>7.897572373849471e-09</v>
       </c>
       <c r="DU5" t="n">
-        <v>0.001333140768110752</v>
+        <v>5.359568788776414e-09</v>
       </c>
       <c r="DV5" t="n">
-        <v>0.00275228382088244</v>
+        <v>5.29456789521987e-09</v>
       </c>
       <c r="DW5" t="n">
-        <v>0.0005179023137316108</v>
+        <v>5.731840002631827e-10</v>
       </c>
       <c r="DX5" t="n">
-        <v>0.005369256716221571</v>
+        <v>1.187473763764046e-08</v>
       </c>
       <c r="DY5" t="n">
-        <v>0.0007303829188458622</v>
+        <v>7.532576340452124e-09</v>
       </c>
       <c r="DZ5" t="n">
-        <v>0.002697786316275597</v>
+        <v>6.339268665556119e-09</v>
       </c>
       <c r="EA5" t="n">
-        <v>0.001069304416887462</v>
+        <v>7.302812576881479e-09</v>
       </c>
       <c r="EB5" t="n">
-        <v>0.0001444801455363631</v>
+        <v>4.134208531070271e-09</v>
       </c>
       <c r="EC5" t="n">
-        <v>0.001103837275877595</v>
+        <v>5.818070913932161e-09</v>
       </c>
       <c r="ED5" t="n">
-        <v>0.001288886996917427</v>
+        <v>4.355754867901851e-09</v>
       </c>
       <c r="EE5" t="n">
-        <v>0.001281970413401723</v>
+        <v>1.490566425843554e-08</v>
       </c>
       <c r="EF5" t="n">
-        <v>5.153400707058609e-06</v>
+        <v>2.327304571281275e-09</v>
       </c>
       <c r="EG5" t="n">
-        <v>0.001156279467977583</v>
+        <v>5.182266171743777e-09</v>
       </c>
       <c r="EH5" t="n">
-        <v>0.0001502173690823838</v>
+        <v>1.52753365512126e-11</v>
       </c>
       <c r="EI5" t="n">
-        <v>0.001320329261943698</v>
+        <v>1.822910489224228e-09</v>
       </c>
       <c r="EJ5" t="n">
-        <v>0.000909418158698827</v>
+        <v>1.567763252552368e-09</v>
       </c>
       <c r="EK5" t="n">
-        <v>0.0003137079766020179</v>
+        <v>7.015655167919022e-09</v>
       </c>
       <c r="EL5" t="n">
-        <v>0.002583665773272514</v>
+        <v>1.180118558430365e-09</v>
       </c>
       <c r="EM5" t="n">
-        <v>0.0003266082203481346</v>
+        <v>9.034233916516143e-10</v>
       </c>
       <c r="EN5" t="n">
-        <v>0.0001333719992544502</v>
+        <v>6.920873318883025e-10</v>
       </c>
       <c r="EO5" t="n">
-        <v>0.002445830265060067</v>
+        <v>2.528613318730777e-09</v>
       </c>
       <c r="EP5" t="n">
-        <v>0.0004555586783681065</v>
+        <v>2.37401098779344e-10</v>
       </c>
       <c r="EQ5" t="n">
-        <v>0.001001121592707932</v>
+        <v>1.950940520245581e-10</v>
       </c>
       <c r="ER5" t="n">
-        <v>0.0001773727999534458</v>
+        <v>3.55739748769679e-09</v>
       </c>
       <c r="ES5" t="n">
-        <v>0.0009680456132628024</v>
+        <v>6.025265619769016e-09</v>
       </c>
       <c r="ET5" t="n">
-        <v>0.004844390321522951</v>
+        <v>2.591313386091088e-09</v>
       </c>
       <c r="EU5" t="n">
-        <v>0.0007141767418943346</v>
+        <v>5.849998707674331e-09</v>
       </c>
       <c r="EV5" t="n">
-        <v>0.0008640633895993233</v>
+        <v>1.607510791146183e-09</v>
       </c>
       <c r="EW5" t="n">
-        <v>0.0002131056971848011</v>
+        <v>8.783296312486755e-11</v>
       </c>
       <c r="EX5" t="n">
-        <v>0.001073425635695457</v>
+        <v>2.953691069507158e-09</v>
       </c>
       <c r="EY5" t="n">
-        <v>0.002417052630335093</v>
+        <v>5.028899963122058e-09</v>
       </c>
       <c r="EZ5" t="n">
-        <v>0.0002007691218750551</v>
+        <v>3.638042089804117e-09</v>
       </c>
       <c r="FA5" t="n">
-        <v>0.001056938199326396</v>
+        <v>1.688543749267524e-09</v>
       </c>
       <c r="FB5" t="n">
-        <v>0.0002711289853323251</v>
+        <v>8.464097200899801e-10</v>
       </c>
       <c r="FC5" t="n">
-        <v>0.0005252495757304132</v>
+        <v>4.022795430103088e-09</v>
       </c>
       <c r="FD5" t="n">
-        <v>0.0005966223543509841</v>
+        <v>2.074975302690518e-09</v>
       </c>
       <c r="FE5" t="n">
-        <v>0.001625892124138772</v>
+        <v>2.742846172409941e-09</v>
       </c>
       <c r="FF5" t="n">
-        <v>0.0007904054946266115</v>
+        <v>2.295480472369604e-09</v>
       </c>
       <c r="FG5" t="n">
-        <v>0.001695792539976537</v>
+        <v>6.234672333960134e-09</v>
       </c>
       <c r="FH5" t="n">
-        <v>0.001686768839135766</v>
+        <v>6.249668782487561e-09</v>
       </c>
       <c r="FI5" t="n">
-        <v>0.001092141028493643</v>
+        <v>2.417278821553737e-09</v>
       </c>
       <c r="FJ5" t="n">
-        <v>0.0006136386655271053</v>
+        <v>7.642582677824805e-10</v>
       </c>
       <c r="FK5" t="n">
-        <v>0.0004842461785301566</v>
+        <v>2.252655395551528e-09</v>
       </c>
       <c r="FL5" t="n">
-        <v>0.004260447341948748</v>
+        <v>7.760518450083964e-09</v>
       </c>
       <c r="FM5" t="n">
-        <v>0.0007525283144786954</v>
+        <v>2.92931057188639e-09</v>
       </c>
       <c r="FN5" t="n">
-        <v>0.002133035799488425</v>
+        <v>1.135572968991028e-08</v>
       </c>
       <c r="FO5" t="n">
-        <v>0.00479792058467865</v>
+        <v>1.722507647627936e-08</v>
       </c>
       <c r="FP5" t="n">
-        <v>0.001076521584764123</v>
+        <v>3.332288223134583e-09</v>
       </c>
       <c r="FQ5" t="n">
-        <v>0.003147169249132276</v>
+        <v>1.254193637834078e-08</v>
       </c>
       <c r="FR5" t="n">
-        <v>0.002031306736171246</v>
+        <v>5.86729775875483e-09</v>
       </c>
       <c r="FS5" t="n">
-        <v>0.00219107954762876</v>
+        <v>6.725109358285408e-09</v>
       </c>
       <c r="FT5" t="n">
-        <v>0.00161265954375267</v>
+        <v>3.672378401375909e-09</v>
       </c>
       <c r="FU5" t="n">
-        <v>0.002837951527908444</v>
+        <v>8.693398001469177e-09</v>
       </c>
       <c r="FV5" t="n">
-        <v>0.0004417742020450532</v>
+        <v>1.143731065411657e-08</v>
       </c>
       <c r="FW5" t="n">
-        <v>0.002120611257851124</v>
+        <v>2.546692634552983e-08</v>
       </c>
       <c r="FX5" t="n">
-        <v>0.003094705985859036</v>
+        <v>5.786273238328477e-09</v>
       </c>
       <c r="FY5" t="n">
-        <v>0.002799336332827806</v>
+        <v>4.140543463648783e-10</v>
       </c>
       <c r="FZ5" t="n">
-        <v>0.0003724632260855287</v>
+        <v>1.834763896368941e-09</v>
       </c>
       <c r="GA5" t="n">
-        <v>0.002776868175715208</v>
+        <v>9.964791658489958e-09</v>
       </c>
       <c r="GB5" t="n">
-        <v>0.001529067405499518</v>
+        <v>6.954343323428702e-09</v>
       </c>
       <c r="GC5" t="n">
-        <v>0.002881943713873625</v>
+        <v>1.403252802845145e-08</v>
       </c>
       <c r="GD5" t="n">
-        <v>0.001420363900251687</v>
+        <v>1.036833197076703e-08</v>
       </c>
       <c r="GE5" t="n">
-        <v>0.002803615760058165</v>
+        <v>1.293119389345065e-09</v>
       </c>
       <c r="GF5" t="n">
-        <v>0.006817639339715242</v>
+        <v>8.853955790755208e-09</v>
       </c>
       <c r="GG5" t="n">
-        <v>0.0008040187531150877</v>
+        <v>6.154474263553311e-09</v>
       </c>
     </row>
     <row r="6">
@@ -3844,1140 +3844,1140 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>0.002361772349104285</v>
+        <v>0.06302029639482498</v>
       </c>
       <c r="B7" t="n">
-        <v>0.0786978155374527</v>
+        <v>0.1378700137138367</v>
       </c>
       <c r="C7" t="n">
-        <v>0.004136876203119755</v>
+        <v>0.1034454703330994</v>
       </c>
       <c r="D7" t="n">
-        <v>0.05560679733753204</v>
+        <v>0.1735483705997467</v>
       </c>
       <c r="E7" t="n">
-        <v>0.01559466775506735</v>
+        <v>0.02046261727809906</v>
       </c>
       <c r="F7" t="n">
-        <v>0.002543284557759762</v>
+        <v>0.02502268925309181</v>
       </c>
       <c r="G7" t="n">
-        <v>0.008243342861533165</v>
+        <v>0.1252109855413437</v>
       </c>
       <c r="H7" t="n">
-        <v>0.01557026989758015</v>
+        <v>0.1921635568141937</v>
       </c>
       <c r="I7" t="n">
-        <v>0.01939420960843563</v>
+        <v>0.1121188253164291</v>
       </c>
       <c r="J7" t="n">
-        <v>0.005010260734707117</v>
+        <v>0.0588163435459137</v>
       </c>
       <c r="K7" t="n">
-        <v>0.06493858247995377</v>
+        <v>0.1688868701457977</v>
       </c>
       <c r="L7" t="n">
-        <v>0.001996905310079455</v>
+        <v>0.06787970662117004</v>
       </c>
       <c r="M7" t="n">
-        <v>0.05064778029918671</v>
+        <v>0.2372468411922455</v>
       </c>
       <c r="N7" t="n">
-        <v>0.02910900115966797</v>
+        <v>0.02826888114213943</v>
       </c>
       <c r="O7" t="n">
-        <v>0.01857699826359749</v>
+        <v>0.06249255686998367</v>
       </c>
       <c r="P7" t="n">
-        <v>0.003507414367049932</v>
+        <v>0.03881124779582024</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.006791154853999615</v>
+        <v>0.3479314744472504</v>
       </c>
       <c r="R7" t="n">
-        <v>0.01270224340260029</v>
+        <v>0.08903676271438599</v>
       </c>
       <c r="S7" t="n">
-        <v>0.002161146141588688</v>
+        <v>0.03302937373518944</v>
       </c>
       <c r="T7" t="n">
-        <v>0.01345623098313808</v>
+        <v>0.1145421341061592</v>
       </c>
       <c r="U7" t="n">
-        <v>0.002146537648513913</v>
+        <v>0.10707638412714</v>
       </c>
       <c r="V7" t="n">
-        <v>0.002658142242580652</v>
+        <v>0.002080065663903952</v>
       </c>
       <c r="W7" t="n">
-        <v>0.01171176787465811</v>
+        <v>0.02183039858937263</v>
       </c>
       <c r="X7" t="n">
-        <v>0.009364028461277485</v>
+        <v>0.04988347738981247</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.01035092119127512</v>
+        <v>0.0103418380022049</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.0078524025157094</v>
+        <v>0.03317666053771973</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.01043177396059036</v>
+        <v>0.05156037211418152</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.0102284736931324</v>
+        <v>0.04394668340682983</v>
       </c>
       <c r="AC7" t="n">
-        <v>0.01184620894491673</v>
+        <v>0.09322378039360046</v>
       </c>
       <c r="AD7" t="n">
-        <v>0.001614955952391028</v>
+        <v>0.03498660027980804</v>
       </c>
       <c r="AE7" t="n">
-        <v>0.0004417011514306068</v>
+        <v>0.1865370273590088</v>
       </c>
       <c r="AF7" t="n">
-        <v>0.00791114941239357</v>
+        <v>0.04521795734763145</v>
       </c>
       <c r="AG7" t="n">
-        <v>0.01110590063035488</v>
+        <v>0.1942038983106613</v>
       </c>
       <c r="AH7" t="n">
-        <v>0.006033179350197315</v>
+        <v>0.03768955171108246</v>
       </c>
       <c r="AI7" t="n">
-        <v>0.007142866030335426</v>
+        <v>0.05922917276620865</v>
       </c>
       <c r="AJ7" t="n">
-        <v>0.00243111071176827</v>
+        <v>0.01487500220537186</v>
       </c>
       <c r="AK7" t="n">
-        <v>0.004787830635905266</v>
+        <v>0.005924449302256107</v>
       </c>
       <c r="AL7" t="n">
-        <v>0.002969601424410939</v>
+        <v>0.1843394339084625</v>
       </c>
       <c r="AM7" t="n">
-        <v>0.002045202301815152</v>
+        <v>0.1530525684356689</v>
       </c>
       <c r="AN7" t="n">
-        <v>0.004545870237052441</v>
+        <v>0.03214819729328156</v>
       </c>
       <c r="AO7" t="n">
-        <v>0.009263090789318085</v>
+        <v>0.1306157559156418</v>
       </c>
       <c r="AP7" t="n">
-        <v>0.004469956271350384</v>
+        <v>0.02445781975984573</v>
       </c>
       <c r="AQ7" t="n">
-        <v>0.007174662314355373</v>
+        <v>0.004153510555624962</v>
       </c>
       <c r="AR7" t="n">
-        <v>0.0001713810488581657</v>
+        <v>0.01629940792918205</v>
       </c>
       <c r="AS7" t="n">
-        <v>0.000265357899479568</v>
+        <v>0.04810115694999695</v>
       </c>
       <c r="AT7" t="n">
-        <v>0.01111029367893934</v>
+        <v>0.009150195866823196</v>
       </c>
       <c r="AU7" t="n">
-        <v>0.05332135409116745</v>
+        <v>0.1869138479232788</v>
       </c>
       <c r="AV7" t="n">
-        <v>0.0116922901943326</v>
+        <v>0.03580716997385025</v>
       </c>
       <c r="AW7" t="n">
-        <v>0.0112376194447279</v>
+        <v>0.08278459310531616</v>
       </c>
       <c r="AX7" t="n">
-        <v>0.002096113748848438</v>
+        <v>0.0001633171923458576</v>
       </c>
       <c r="AY7" t="n">
-        <v>0.004308057948946953</v>
+        <v>0.04667216911911964</v>
       </c>
       <c r="AZ7" t="n">
-        <v>0.003384667448699474</v>
+        <v>0.005748092196881771</v>
       </c>
       <c r="BA7" t="n">
-        <v>0.01457804441452026</v>
+        <v>0.1218090951442719</v>
       </c>
       <c r="BB7" t="n">
-        <v>0.002153226174414158</v>
+        <v>0.05914076790213585</v>
       </c>
       <c r="BC7" t="n">
-        <v>0.008823158219456673</v>
+        <v>0.05864168331027031</v>
       </c>
       <c r="BD7" t="n">
-        <v>0.01359327137470245</v>
+        <v>0.2122538983821869</v>
       </c>
       <c r="BE7" t="n">
-        <v>0.02237892895936966</v>
+        <v>0.1037331968545914</v>
       </c>
       <c r="BF7" t="n">
-        <v>0.01581601426005363</v>
+        <v>0.1253552138805389</v>
       </c>
       <c r="BG7" t="n">
-        <v>0.02719457633793354</v>
+        <v>0.1920102089643478</v>
       </c>
       <c r="BH7" t="n">
-        <v>0.0009155147708952427</v>
+        <v>0.05757854878902435</v>
       </c>
       <c r="BI7" t="n">
-        <v>0.001730818417854607</v>
+        <v>0.01895037293434143</v>
       </c>
       <c r="BJ7" t="n">
-        <v>0.0136819202452898</v>
+        <v>0.1469078660011292</v>
       </c>
       <c r="BK7" t="n">
-        <v>0.006961189210414886</v>
+        <v>0.1306503117084503</v>
       </c>
       <c r="BL7" t="n">
-        <v>0.0162266381084919</v>
+        <v>0.008036484941840172</v>
       </c>
       <c r="BM7" t="n">
-        <v>0.007845576852560043</v>
+        <v>0.08390452712774277</v>
       </c>
       <c r="BN7" t="n">
-        <v>0.002818798180669546</v>
+        <v>0.03763837367296219</v>
       </c>
       <c r="BO7" t="n">
-        <v>0.0004193212371319532</v>
+        <v>0.06284966319799423</v>
       </c>
       <c r="BP7" t="n">
-        <v>0.01592737436294556</v>
+        <v>0.07802689075469971</v>
       </c>
       <c r="BQ7" t="n">
-        <v>0.01075575686991215</v>
+        <v>0.08281730860471725</v>
       </c>
       <c r="BR7" t="n">
-        <v>0.00257783243432641</v>
+        <v>0.01208417303860188</v>
       </c>
       <c r="BS7" t="n">
-        <v>0.01295379083603621</v>
+        <v>0.08621063828468323</v>
       </c>
       <c r="BT7" t="n">
-        <v>0.004821024369448423</v>
+        <v>0.02374245598912239</v>
       </c>
       <c r="BU7" t="n">
-        <v>0.004855489358305931</v>
+        <v>0.04149169847369194</v>
       </c>
       <c r="BV7" t="n">
-        <v>0.02298696897923946</v>
+        <v>0.2637621760368347</v>
       </c>
       <c r="BW7" t="n">
-        <v>0.0007799459854140878</v>
+        <v>0.07013110816478729</v>
       </c>
       <c r="BX7" t="n">
-        <v>0.002359438687562943</v>
+        <v>0.05459891259670258</v>
       </c>
       <c r="BY7" t="n">
-        <v>0.00888310931622982</v>
+        <v>0.00840932410210371</v>
       </c>
       <c r="BZ7" t="n">
-        <v>0.001826961524784565</v>
+        <v>0.09143303334712982</v>
       </c>
       <c r="CA7" t="n">
-        <v>0.006987580098211765</v>
+        <v>0.008881676010787487</v>
       </c>
       <c r="CB7" t="n">
-        <v>0.005176810547709465</v>
+        <v>0.1753550469875336</v>
       </c>
       <c r="CC7" t="n">
-        <v>0.003457405604422092</v>
+        <v>0.06927764415740967</v>
       </c>
       <c r="CD7" t="n">
-        <v>0.003001181175932288</v>
+        <v>0.004167346283793449</v>
       </c>
       <c r="CE7" t="n">
-        <v>0.01362071186304092</v>
+        <v>0.04974302649497986</v>
       </c>
       <c r="CF7" t="n">
-        <v>0.004217575769871473</v>
+        <v>0.02450810559093952</v>
       </c>
       <c r="CG7" t="n">
-        <v>0.005745534785091877</v>
+        <v>0.06065311655402184</v>
       </c>
       <c r="CH7" t="n">
-        <v>0.002670907881110907</v>
+        <v>0.04614182561635971</v>
       </c>
       <c r="CI7" t="n">
-        <v>0.0005807081470265985</v>
+        <v>0.01246079616248608</v>
       </c>
       <c r="CJ7" t="n">
-        <v>0.00243968446739018</v>
+        <v>0.01299283653497696</v>
       </c>
       <c r="CK7" t="n">
-        <v>0.0002255266299471259</v>
+        <v>0.03069951757788658</v>
       </c>
       <c r="CL7" t="n">
-        <v>0.004263810347765684</v>
+        <v>0.01649583503603935</v>
       </c>
       <c r="CM7" t="n">
-        <v>0.01705698668956757</v>
+        <v>0.04934075474739075</v>
       </c>
       <c r="CN7" t="n">
-        <v>0.004972490482032299</v>
+        <v>0.02033359743654728</v>
       </c>
       <c r="CO7" t="n">
-        <v>0.0008306448580697179</v>
+        <v>0.05095387250185013</v>
       </c>
       <c r="CP7" t="n">
-        <v>0.01876819506287575</v>
+        <v>0.1763354539871216</v>
       </c>
       <c r="CQ7" t="n">
-        <v>0.0108618475496769</v>
+        <v>0.1896467506885529</v>
       </c>
       <c r="CR7" t="n">
-        <v>0.007300222292542458</v>
+        <v>0.03913799673318863</v>
       </c>
       <c r="CS7" t="n">
-        <v>0.01451478432863951</v>
+        <v>0.0539730116724968</v>
       </c>
       <c r="CT7" t="n">
-        <v>0.01295130513608456</v>
+        <v>0.09782323241233826</v>
       </c>
       <c r="CU7" t="n">
-        <v>0.001575297676026821</v>
+        <v>0.09693420678377151</v>
       </c>
       <c r="CV7" t="n">
-        <v>0.002360391430556774</v>
+        <v>0.004690358880907297</v>
       </c>
       <c r="CW7" t="n">
-        <v>0.01136164274066687</v>
+        <v>0.05022621899843216</v>
       </c>
       <c r="CX7" t="n">
-        <v>0.007280953694134951</v>
+        <v>0.03020132333040237</v>
       </c>
       <c r="CY7" t="n">
-        <v>0.009231779724359512</v>
+        <v>0.0692993700504303</v>
       </c>
       <c r="CZ7" t="n">
-        <v>0.003671016078442335</v>
+        <v>0.01274105161428452</v>
       </c>
       <c r="DA7" t="n">
-        <v>0.002017584396526217</v>
+        <v>0.006929556839168072</v>
       </c>
       <c r="DB7" t="n">
-        <v>0.004113529808819294</v>
+        <v>0.01033749803900719</v>
       </c>
       <c r="DC7" t="n">
-        <v>0.001712583471089602</v>
+        <v>0.03409532457590103</v>
       </c>
       <c r="DD7" t="n">
-        <v>0.003435833845287561</v>
+        <v>0.008796427398920059</v>
       </c>
       <c r="DE7" t="n">
-        <v>0.004717419855296612</v>
+        <v>0.004361801780760288</v>
       </c>
       <c r="DF7" t="n">
-        <v>0.00340259145013988</v>
+        <v>0.124395988881588</v>
       </c>
       <c r="DG7" t="n">
-        <v>0.009298047982156277</v>
+        <v>0.1591207385063171</v>
       </c>
       <c r="DH7" t="n">
-        <v>0.009454097598791122</v>
+        <v>0.04044096171855927</v>
       </c>
       <c r="DI7" t="n">
-        <v>0.01813492923974991</v>
+        <v>0.002519413828849792</v>
       </c>
       <c r="DJ7" t="n">
-        <v>0.0003123870119452477</v>
+        <v>0.1054451614618301</v>
       </c>
       <c r="DK7" t="n">
-        <v>0.005635639652609825</v>
+        <v>0.02853358536958694</v>
       </c>
       <c r="DL7" t="n">
-        <v>0.009612396359443665</v>
+        <v>0.1263525784015656</v>
       </c>
       <c r="DM7" t="n">
-        <v>0.01237011142075062</v>
+        <v>0.06781482696533203</v>
       </c>
       <c r="DN7" t="n">
-        <v>0.000363773200660944</v>
+        <v>0.03422288224101067</v>
       </c>
       <c r="DO7" t="n">
-        <v>0.001855631824582815</v>
+        <v>0.007090655621141195</v>
       </c>
       <c r="DP7" t="n">
-        <v>0.00322366738691926</v>
+        <v>0.009935007430613041</v>
       </c>
       <c r="DQ7" t="n">
-        <v>0.004464928060770035</v>
+        <v>0.03060735762119293</v>
       </c>
       <c r="DR7" t="n">
-        <v>0.00699948612600565</v>
+        <v>0.04389224201440811</v>
       </c>
       <c r="DS7" t="n">
-        <v>0.007445344235748053</v>
+        <v>0.003773478791117668</v>
       </c>
       <c r="DT7" t="n">
-        <v>0.0006058535072952509</v>
+        <v>0.01676472648978233</v>
       </c>
       <c r="DU7" t="n">
-        <v>0.008837655186653137</v>
+        <v>0.02271029725670815</v>
       </c>
       <c r="DV7" t="n">
-        <v>0.007076510228216648</v>
+        <v>0.09558676928281784</v>
       </c>
       <c r="DW7" t="n">
-        <v>0.002096256241202354</v>
+        <v>0.01160780712962151</v>
       </c>
       <c r="DX7" t="n">
-        <v>0.0008168870699591935</v>
+        <v>0.0410197339951992</v>
       </c>
       <c r="DY7" t="n">
-        <v>0.0139522161334753</v>
+        <v>0.07956790924072266</v>
       </c>
       <c r="DZ7" t="n">
-        <v>0.005664042197167873</v>
+        <v>0.02668179199099541</v>
       </c>
       <c r="EA7" t="n">
-        <v>0.004247532226145267</v>
+        <v>0.06669902801513672</v>
       </c>
       <c r="EB7" t="n">
-        <v>0.003090759506449103</v>
+        <v>0.04499827697873116</v>
       </c>
       <c r="EC7" t="n">
-        <v>0.003965743817389011</v>
+        <v>0.03899741172790527</v>
       </c>
       <c r="ED7" t="n">
-        <v>0.001962698996067047</v>
+        <v>0.009467109106481075</v>
       </c>
       <c r="EE7" t="n">
-        <v>8.311192505061626e-05</v>
+        <v>0.06220867112278938</v>
       </c>
       <c r="EF7" t="n">
-        <v>0.001622207462787628</v>
+        <v>0.02454034611582756</v>
       </c>
       <c r="EG7" t="n">
-        <v>0.01161682140082121</v>
+        <v>0.01178339309990406</v>
       </c>
       <c r="EH7" t="n">
-        <v>0.00826143566519022</v>
+        <v>0.02855618670582771</v>
       </c>
       <c r="EI7" t="n">
-        <v>0.005402150098234415</v>
+        <v>0.04774270951747894</v>
       </c>
       <c r="EJ7" t="n">
-        <v>0.007371880114078522</v>
+        <v>0.0452876128256321</v>
       </c>
       <c r="EK7" t="n">
-        <v>0.00348268635571003</v>
+        <v>0.0774492472410202</v>
       </c>
       <c r="EL7" t="n">
-        <v>0.004352064803242683</v>
+        <v>0.0008824463002383709</v>
       </c>
       <c r="EM7" t="n">
-        <v>0.001702571520581841</v>
+        <v>0.02190928906202316</v>
       </c>
       <c r="EN7" t="n">
-        <v>0.003599550109356642</v>
+        <v>0.02218171954154968</v>
       </c>
       <c r="EO7" t="n">
-        <v>0.001722821965813637</v>
+        <v>0.02077474072575569</v>
       </c>
       <c r="EP7" t="n">
-        <v>0.007612128742039204</v>
+        <v>0.07769870758056641</v>
       </c>
       <c r="EQ7" t="n">
-        <v>0.008413617499172688</v>
+        <v>0.04348857328295708</v>
       </c>
       <c r="ER7" t="n">
-        <v>0.0002416166244074702</v>
+        <v>0.02044934593141079</v>
       </c>
       <c r="ES7" t="n">
-        <v>0.00497409887611866</v>
+        <v>0.0162856075912714</v>
       </c>
       <c r="ET7" t="n">
-        <v>0.0005741510540246964</v>
+        <v>0.01588829979300499</v>
       </c>
       <c r="EU7" t="n">
-        <v>0.009432164952158928</v>
+        <v>0.04194421693682671</v>
       </c>
       <c r="EV7" t="n">
-        <v>0.01185330934822559</v>
+        <v>0.05531993508338928</v>
       </c>
       <c r="EW7" t="n">
-        <v>0.00539892166852951</v>
+        <v>0.05092206224799156</v>
       </c>
       <c r="EX7" t="n">
-        <v>0.0004898594925180078</v>
+        <v>0.001030812738463283</v>
       </c>
       <c r="EY7" t="n">
-        <v>0.01195278950035572</v>
+        <v>0.05800477415323257</v>
       </c>
       <c r="EZ7" t="n">
-        <v>0.00317831989377737</v>
+        <v>0.005302857607603073</v>
       </c>
       <c r="FA7" t="n">
-        <v>0.006737601477652788</v>
+        <v>0.06869254261255264</v>
       </c>
       <c r="FB7" t="n">
-        <v>0.003141284920275211</v>
+        <v>0.02952542714774609</v>
       </c>
       <c r="FC7" t="n">
-        <v>0.003027603263035417</v>
+        <v>0.002125856466591358</v>
       </c>
       <c r="FD7" t="n">
-        <v>0.003356299130246043</v>
+        <v>0.009105462580919266</v>
       </c>
       <c r="FE7" t="n">
-        <v>0.0009248381247743964</v>
+        <v>0.01651883497834206</v>
       </c>
       <c r="FF7" t="n">
-        <v>0.005321344826370478</v>
+        <v>0.01258818805217743</v>
       </c>
       <c r="FG7" t="n">
-        <v>0.001208721776492894</v>
+        <v>0.01411850936710835</v>
       </c>
       <c r="FH7" t="n">
-        <v>0.00590679282322526</v>
+        <v>0.03225580975413322</v>
       </c>
       <c r="FI7" t="n">
-        <v>0.01068236399441957</v>
+        <v>0.02842952683568001</v>
       </c>
       <c r="FJ7" t="n">
-        <v>0.01028515957295895</v>
+        <v>0.07515997439622879</v>
       </c>
       <c r="FK7" t="n">
-        <v>0.003400306915864348</v>
+        <v>0.06729141622781754</v>
       </c>
       <c r="FL7" t="n">
-        <v>0.007069469429552555</v>
+        <v>0.05053047090768814</v>
       </c>
       <c r="FM7" t="n">
-        <v>0.00191901158541441</v>
+        <v>0.004574401769787073</v>
       </c>
       <c r="FN7" t="n">
-        <v>0.00159275543410331</v>
+        <v>0.007369227707386017</v>
       </c>
       <c r="FO7" t="n">
-        <v>0.005914398469030857</v>
+        <v>0.09734406322240829</v>
       </c>
       <c r="FP7" t="n">
-        <v>0.0002566603943705559</v>
+        <v>0.05587085708975792</v>
       </c>
       <c r="FQ7" t="n">
-        <v>0.008292078971862793</v>
+        <v>0.04515264183282852</v>
       </c>
       <c r="FR7" t="n">
-        <v>0.006794223561882973</v>
+        <v>0.01864566281437874</v>
       </c>
       <c r="FS7" t="n">
-        <v>0.001928437734022737</v>
+        <v>0.05105508863925934</v>
       </c>
       <c r="FT7" t="n">
-        <v>0.0008015413768589497</v>
+        <v>0.2387467920780182</v>
       </c>
       <c r="FU7" t="n">
-        <v>0.0008388618007302284</v>
+        <v>0.05725318938493729</v>
       </c>
       <c r="FV7" t="n">
-        <v>0.006161231081932783</v>
+        <v>0.05856350436806679</v>
       </c>
       <c r="FW7" t="n">
-        <v>0.00211715791374445</v>
+        <v>0.05306314677000046</v>
       </c>
       <c r="FX7" t="n">
-        <v>0.01004256960004568</v>
+        <v>0.02536182850599289</v>
       </c>
       <c r="FY7" t="n">
-        <v>0.01418653316795826</v>
+        <v>0.002957598306238651</v>
       </c>
       <c r="FZ7" t="n">
-        <v>0.007053710985928774</v>
+        <v>0.1443073749542236</v>
       </c>
       <c r="GA7" t="n">
-        <v>0.003961518406867981</v>
+        <v>0.04893714189529419</v>
       </c>
       <c r="GB7" t="n">
-        <v>0.00405857851728797</v>
+        <v>0.00800728052854538</v>
       </c>
       <c r="GC7" t="n">
-        <v>0.007744939997792244</v>
+        <v>0.07876059412956238</v>
       </c>
       <c r="GD7" t="n">
-        <v>0.01620415970683098</v>
+        <v>0.05231019482016563</v>
       </c>
       <c r="GE7" t="n">
-        <v>0.02483719401061535</v>
+        <v>0.07523930817842484</v>
       </c>
       <c r="GF7" t="n">
-        <v>0.00423933332785964</v>
+        <v>0.03120152465999126</v>
       </c>
       <c r="GG7" t="n">
-        <v>0.009501399472355843</v>
+        <v>0.0008309539407491684</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>0.001183612854219973</v>
+        <v>0.3331156969070435</v>
       </c>
       <c r="B8" t="n">
-        <v>0.009030566550791264</v>
+        <v>0.7004615068435669</v>
       </c>
       <c r="C8" t="n">
-        <v>0.0006644478417001665</v>
+        <v>0.03365316241979599</v>
       </c>
       <c r="D8" t="n">
-        <v>0.005296670831739902</v>
+        <v>0.01931624859571457</v>
       </c>
       <c r="E8" t="n">
-        <v>0.001710657496005297</v>
+        <v>0.02672050893306732</v>
       </c>
       <c r="F8" t="n">
-        <v>0.006016894709318876</v>
+        <v>0.5036761164665222</v>
       </c>
       <c r="G8" t="n">
-        <v>0.0007689015474170446</v>
+        <v>0.02375559508800507</v>
       </c>
       <c r="H8" t="n">
-        <v>0.001914486521854997</v>
+        <v>0.1352242231369019</v>
       </c>
       <c r="I8" t="n">
-        <v>0.0004243147850502282</v>
+        <v>0.164822980761528</v>
       </c>
       <c r="J8" t="n">
-        <v>0.002623932203277946</v>
+        <v>0.2063747644424438</v>
       </c>
       <c r="K8" t="n">
-        <v>0.006957152858376503</v>
+        <v>0.9748733639717102</v>
       </c>
       <c r="L8" t="n">
-        <v>8.242539479397237e-05</v>
+        <v>0.07208618521690369</v>
       </c>
       <c r="M8" t="n">
-        <v>0.004741862881928682</v>
+        <v>0.210763543844223</v>
       </c>
       <c r="N8" t="n">
-        <v>0.001794175826944411</v>
+        <v>0.1914084851741791</v>
       </c>
       <c r="O8" t="n">
-        <v>0.006538770627230406</v>
+        <v>0.5804300308227539</v>
       </c>
       <c r="P8" t="n">
-        <v>0.000140571326483041</v>
+        <v>0.09819020330905914</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.000430060550570488</v>
+        <v>0.1424765139818192</v>
       </c>
       <c r="R8" t="n">
-        <v>0.0003487257054075599</v>
+        <v>0.1509985029697418</v>
       </c>
       <c r="S8" t="n">
-        <v>0.0006482256576418877</v>
+        <v>0.06466230750083923</v>
       </c>
       <c r="T8" t="n">
-        <v>0.001292341388761997</v>
+        <v>0.2862302660942078</v>
       </c>
       <c r="U8" t="n">
-        <v>0.0005236914148554206</v>
+        <v>0.04283161833882332</v>
       </c>
       <c r="V8" t="n">
-        <v>0.001062436029314995</v>
+        <v>0.2833859324455261</v>
       </c>
       <c r="W8" t="n">
-        <v>0.0005067113088443875</v>
+        <v>0.158642053604126</v>
       </c>
       <c r="X8" t="n">
-        <v>0.0005763855879195035</v>
+        <v>0.08817987889051437</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.001096672145649791</v>
+        <v>0.05547718703746796</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.0006279092049226165</v>
+        <v>0.2252895087003708</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.001009565778076649</v>
+        <v>0.06745219230651855</v>
       </c>
       <c r="AB8" t="n">
-        <v>7.073371671140194e-05</v>
+        <v>0.02039212360978127</v>
       </c>
       <c r="AC8" t="n">
-        <v>0.000947076827287674</v>
+        <v>0.1439182609319687</v>
       </c>
       <c r="AD8" t="n">
-        <v>0.0002521107671782374</v>
+        <v>0.05902458727359772</v>
       </c>
       <c r="AE8" t="n">
-        <v>3.543967613950372e-05</v>
+        <v>0.2846933603286743</v>
       </c>
       <c r="AF8" t="n">
-        <v>0.0004655607044696808</v>
+        <v>0.5645184516906738</v>
       </c>
       <c r="AG8" t="n">
-        <v>0.0002069129113806412</v>
+        <v>0.1936437636613846</v>
       </c>
       <c r="AH8" t="n">
-        <v>0.0008677722653374076</v>
+        <v>0.04668241739273071</v>
       </c>
       <c r="AI8" t="n">
-        <v>0.0004781704919878393</v>
+        <v>0.2932357490062714</v>
       </c>
       <c r="AJ8" t="n">
-        <v>0.000337753037456423</v>
+        <v>0.03834342956542969</v>
       </c>
       <c r="AK8" t="n">
-        <v>0.0007919815252535045</v>
+        <v>0.003534700721502304</v>
       </c>
       <c r="AL8" t="n">
-        <v>0.001375863794237375</v>
+        <v>0.3089063763618469</v>
       </c>
       <c r="AM8" t="n">
-        <v>0.0004652994684875011</v>
+        <v>0.0633874237537384</v>
       </c>
       <c r="AN8" t="n">
-        <v>0.0003145324299111962</v>
+        <v>0.131075993180275</v>
       </c>
       <c r="AO8" t="n">
-        <v>0.000428431638283655</v>
+        <v>0.1054434925317764</v>
       </c>
       <c r="AP8" t="n">
-        <v>0.001188328256830573</v>
+        <v>0.160856157541275</v>
       </c>
       <c r="AQ8" t="n">
-        <v>0.0002052040072157979</v>
+        <v>0.1342364549636841</v>
       </c>
       <c r="AR8" t="n">
-        <v>0.0005065644509159029</v>
+        <v>0.3017286360263824</v>
       </c>
       <c r="AS8" t="n">
-        <v>0.001282300800085068</v>
+        <v>0.1101114973425865</v>
       </c>
       <c r="AT8" t="n">
-        <v>0.0007941760704852641</v>
+        <v>0.1255246549844742</v>
       </c>
       <c r="AU8" t="n">
-        <v>0.005835086572915316</v>
+        <v>1.060760021209717</v>
       </c>
       <c r="AV8" t="n">
-        <v>0.0004718105192296207</v>
+        <v>0.03934839740395546</v>
       </c>
       <c r="AW8" t="n">
-        <v>0.000129997351905331</v>
+        <v>0.02159450203180313</v>
       </c>
       <c r="AX8" t="n">
-        <v>6.413127994164824e-05</v>
+        <v>0.1402307599782944</v>
       </c>
       <c r="AY8" t="n">
-        <v>0.003321431111544371</v>
+        <v>0.6420058012008667</v>
       </c>
       <c r="AZ8" t="n">
-        <v>0.0004727235063910484</v>
+        <v>0.02977703884243965</v>
       </c>
       <c r="BA8" t="n">
-        <v>0.001994577934965491</v>
+        <v>0.0277927853167057</v>
       </c>
       <c r="BB8" t="n">
-        <v>0.001927939476445317</v>
+        <v>0.07086991518735886</v>
       </c>
       <c r="BC8" t="n">
-        <v>0.001484662527218461</v>
+        <v>0.1298250705003738</v>
       </c>
       <c r="BD8" t="n">
-        <v>0.001668471843004227</v>
+        <v>0.265599399805069</v>
       </c>
       <c r="BE8" t="n">
-        <v>0.002425901824608445</v>
+        <v>0.01506395637989044</v>
       </c>
       <c r="BF8" t="n">
-        <v>0.001711077988147736</v>
+        <v>0.1470826417207718</v>
       </c>
       <c r="BG8" t="n">
-        <v>0.003033322747796774</v>
+        <v>0.3502009212970734</v>
       </c>
       <c r="BH8" t="n">
-        <v>0.001744386507198215</v>
+        <v>0.001128727570176125</v>
       </c>
       <c r="BI8" t="n">
-        <v>0.0005613346002064645</v>
+        <v>0.1707954704761505</v>
       </c>
       <c r="BJ8" t="n">
-        <v>0.002213435946032405</v>
+        <v>0.0756683424115181</v>
       </c>
       <c r="BK8" t="n">
-        <v>0.0001408814860042185</v>
+        <v>0.09533090889453888</v>
       </c>
       <c r="BL8" t="n">
-        <v>0.0001749158691382036</v>
+        <v>0.1353156268596649</v>
       </c>
       <c r="BM8" t="n">
-        <v>0.001354206469841301</v>
+        <v>0.09688498824834824</v>
       </c>
       <c r="BN8" t="n">
-        <v>0.001118878717534244</v>
+        <v>0.01634856127202511</v>
       </c>
       <c r="BO8" t="n">
-        <v>0.001356750261038542</v>
+        <v>0.1154493987560272</v>
       </c>
       <c r="BP8" t="n">
-        <v>0.0002112819347530603</v>
+        <v>0.09475803375244141</v>
       </c>
       <c r="BQ8" t="n">
-        <v>2.460987616359489e-06</v>
+        <v>0.1087513417005539</v>
       </c>
       <c r="BR8" t="n">
-        <v>0.001270821550861001</v>
+        <v>0.1188121438026428</v>
       </c>
       <c r="BS8" t="n">
-        <v>0.0003451304219197482</v>
+        <v>0.01480084098875523</v>
       </c>
       <c r="BT8" t="n">
-        <v>8.16075480543077e-05</v>
+        <v>0.1146403253078461</v>
       </c>
       <c r="BU8" t="n">
-        <v>0.0005296766757965088</v>
+        <v>0.1475502401590347</v>
       </c>
       <c r="BV8" t="n">
-        <v>0.002948238048702478</v>
+        <v>0.735812246799469</v>
       </c>
       <c r="BW8" t="n">
-        <v>0.001351975370198488</v>
+        <v>0.009503185749053955</v>
       </c>
       <c r="BX8" t="n">
-        <v>0.0009931614622473717</v>
+        <v>0.1262430250644684</v>
       </c>
       <c r="BY8" t="n">
-        <v>0.0009247419657185674</v>
+        <v>0.06321500241756439</v>
       </c>
       <c r="BZ8" t="n">
-        <v>0.001061547663994133</v>
+        <v>0.3476530015468597</v>
       </c>
       <c r="CA8" t="n">
-        <v>0.00106929789762944</v>
+        <v>0.1108224838972092</v>
       </c>
       <c r="CB8" t="n">
-        <v>0.001039638766087592</v>
+        <v>0.1253302395343781</v>
       </c>
       <c r="CC8" t="n">
-        <v>0.001420876244083047</v>
+        <v>0.02440914511680603</v>
       </c>
       <c r="CD8" t="n">
-        <v>5.417517968453467e-05</v>
+        <v>0.02229440212249756</v>
       </c>
       <c r="CE8" t="n">
-        <v>0.001484757172875106</v>
+        <v>0.2666559815406799</v>
       </c>
       <c r="CF8" t="n">
-        <v>0.001196930534206331</v>
+        <v>0.01262469869107008</v>
       </c>
       <c r="CG8" t="n">
-        <v>0.001034465152770281</v>
+        <v>0.0543711930513382</v>
       </c>
       <c r="CH8" t="n">
-        <v>0.0005683451890945435</v>
+        <v>0.06606949120759964</v>
       </c>
       <c r="CI8" t="n">
-        <v>0.001085333991795778</v>
+        <v>0.1684402376413345</v>
       </c>
       <c r="CJ8" t="n">
-        <v>0.0004863609792664647</v>
+        <v>0.08680243045091629</v>
       </c>
       <c r="CK8" t="n">
-        <v>0.000307781680021435</v>
+        <v>0.03475155681371689</v>
       </c>
       <c r="CL8" t="n">
-        <v>0.000806154333986342</v>
+        <v>0.0130206635221839</v>
       </c>
       <c r="CM8" t="n">
-        <v>0.001182898413389921</v>
+        <v>0.2929575443267822</v>
       </c>
       <c r="CN8" t="n">
-        <v>0.0002362184168305248</v>
+        <v>0.5468201041221619</v>
       </c>
       <c r="CO8" t="n">
-        <v>0.0005335420137271285</v>
+        <v>0.008814457803964615</v>
       </c>
       <c r="CP8" t="n">
-        <v>0.001063372590579093</v>
+        <v>0.3786193430423737</v>
       </c>
       <c r="CQ8" t="n">
-        <v>0.0001607542508281767</v>
+        <v>0.4434267580509186</v>
       </c>
       <c r="CR8" t="n">
-        <v>4.450956475920975e-05</v>
+        <v>0.3578807413578033</v>
       </c>
       <c r="CS8" t="n">
-        <v>0.001053513609804213</v>
+        <v>0.07709898799657822</v>
       </c>
       <c r="CT8" t="n">
-        <v>0.0008436100906692445</v>
+        <v>0.007153873331844807</v>
       </c>
       <c r="CU8" t="n">
-        <v>0.0001196258308482356</v>
+        <v>0.09067858010530472</v>
       </c>
       <c r="CV8" t="n">
-        <v>8.376588812097907e-05</v>
+        <v>0.02322095632553101</v>
       </c>
       <c r="CW8" t="n">
-        <v>0.00133028719574213</v>
+        <v>0.2347142100334167</v>
       </c>
       <c r="CX8" t="n">
-        <v>0.001154587371274829</v>
+        <v>0.01774701289832592</v>
       </c>
       <c r="CY8" t="n">
-        <v>0.001407565549015999</v>
+        <v>0.06316456198692322</v>
       </c>
       <c r="CZ8" t="n">
-        <v>0.0004834797000512481</v>
+        <v>0.05910290032625198</v>
       </c>
       <c r="DA8" t="n">
-        <v>0.001205941080115736</v>
+        <v>0.17188860476017</v>
       </c>
       <c r="DB8" t="n">
-        <v>0.0005126980831846595</v>
+        <v>0.03002971410751343</v>
       </c>
       <c r="DC8" t="n">
-        <v>0.0008534106891602278</v>
+        <v>0.0650586262345314</v>
       </c>
       <c r="DD8" t="n">
-        <v>0.0005502025596797466</v>
+        <v>0.01490830443799496</v>
       </c>
       <c r="DE8" t="n">
-        <v>0.0002651555696502328</v>
+        <v>0.0850503146648407</v>
       </c>
       <c r="DF8" t="n">
-        <v>0.001702738110907376</v>
+        <v>0.06768795102834702</v>
       </c>
       <c r="DG8" t="n">
-        <v>0.0003206850087735802</v>
+        <v>0.05021714419126511</v>
       </c>
       <c r="DH8" t="n">
-        <v>0.003400480840355158</v>
+        <v>0.01366961747407913</v>
       </c>
       <c r="DI8" t="n">
-        <v>0.0005878570955246687</v>
+        <v>0.3600948750972748</v>
       </c>
       <c r="DJ8" t="n">
-        <v>0.0003695205668918788</v>
+        <v>0.02077168971300125</v>
       </c>
       <c r="DK8" t="n">
-        <v>0.001380050438456237</v>
+        <v>0.1922165751457214</v>
       </c>
       <c r="DL8" t="n">
-        <v>0.00136731646489352</v>
+        <v>0.1702413558959961</v>
       </c>
       <c r="DM8" t="n">
-        <v>0.0004622193810064346</v>
+        <v>0.005429644137620926</v>
       </c>
       <c r="DN8" t="n">
-        <v>4.757315036840737e-05</v>
+        <v>0.001371832564473152</v>
       </c>
       <c r="DO8" t="n">
-        <v>0.0002973260707221925</v>
+        <v>0.150163322687149</v>
       </c>
       <c r="DP8" t="n">
-        <v>0.0007468027761206031</v>
+        <v>0.02205777354538441</v>
       </c>
       <c r="DQ8" t="n">
-        <v>0.0009911564411595464</v>
+        <v>0.1897891163825989</v>
       </c>
       <c r="DR8" t="n">
-        <v>0.0003645549004431814</v>
+        <v>0.1418638974428177</v>
       </c>
       <c r="DS8" t="n">
-        <v>9.02258325368166e-05</v>
+        <v>0.02920319326221943</v>
       </c>
       <c r="DT8" t="n">
-        <v>0.0003611148276831955</v>
+        <v>0.0481756292283535</v>
       </c>
       <c r="DU8" t="n">
-        <v>7.112095772754401e-05</v>
+        <v>0.2507509291172028</v>
       </c>
       <c r="DV8" t="n">
-        <v>0.001313210930675268</v>
+        <v>0.0712738037109375</v>
       </c>
       <c r="DW8" t="n">
-        <v>0.0002821136731654406</v>
+        <v>0.1197425723075867</v>
       </c>
       <c r="DX8" t="n">
-        <v>0.0006642062216997147</v>
+        <v>0.05345339700579643</v>
       </c>
       <c r="DY8" t="n">
-        <v>0.001463126856833696</v>
+        <v>0.06024587154388428</v>
       </c>
       <c r="DZ8" t="n">
-        <v>1.158792292699218e-05</v>
+        <v>0.08831828087568283</v>
       </c>
       <c r="EA8" t="n">
-        <v>0.0004239778500050306</v>
+        <v>0.07603015005588531</v>
       </c>
       <c r="EB8" t="n">
-        <v>0.0006408412009477615</v>
+        <v>0.1326557844877243</v>
       </c>
       <c r="EC8" t="n">
-        <v>9.867787593975663e-05</v>
+        <v>0.05982012301683426</v>
       </c>
       <c r="ED8" t="n">
-        <v>0.0005821405211463571</v>
+        <v>0.01286726444959641</v>
       </c>
       <c r="EE8" t="n">
-        <v>2.423617115709931e-05</v>
+        <v>0.03571227565407753</v>
       </c>
       <c r="EF8" t="n">
-        <v>0.0006291650934144855</v>
+        <v>0.02842629514634609</v>
       </c>
       <c r="EG8" t="n">
-        <v>0.0008893332560546696</v>
+        <v>0.004654264077544212</v>
       </c>
       <c r="EH8" t="n">
-        <v>0.0008634116966277361</v>
+        <v>0.02410919778048992</v>
       </c>
       <c r="EI8" t="n">
-        <v>0.0001949444995261729</v>
+        <v>0.04987402260303497</v>
       </c>
       <c r="EJ8" t="n">
-        <v>0.0001740383449941874</v>
+        <v>0.041156105697155</v>
       </c>
       <c r="EK8" t="n">
-        <v>0.0009178371401503682</v>
+        <v>0.02155662141740322</v>
       </c>
       <c r="EL8" t="n">
-        <v>0.001001082826405764</v>
+        <v>0.04020172730088234</v>
       </c>
       <c r="EM8" t="n">
-        <v>2.851047429430764e-05</v>
+        <v>0.03272084146738052</v>
       </c>
       <c r="EN8" t="n">
-        <v>0.0002067209861706942</v>
+        <v>0.001818584278225899</v>
       </c>
       <c r="EO8" t="n">
-        <v>0.000249291566433385</v>
+        <v>0.02691712230443954</v>
       </c>
       <c r="EP8" t="n">
-        <v>0.0005447711446322501</v>
+        <v>0.04613770544528961</v>
       </c>
       <c r="EQ8" t="n">
-        <v>0.001282288925722241</v>
+        <v>0.02787705697119236</v>
       </c>
       <c r="ER8" t="n">
-        <v>0.000841283006593585</v>
+        <v>0.1019570529460907</v>
       </c>
       <c r="ES8" t="n">
-        <v>0.0008684010826982558</v>
+        <v>0.1301054805517197</v>
       </c>
       <c r="ET8" t="n">
-        <v>0.001123258261941373</v>
+        <v>0.03397795930504799</v>
       </c>
       <c r="EU8" t="n">
-        <v>0.0009973994456231594</v>
+        <v>0.009226543828845024</v>
       </c>
       <c r="EV8" t="n">
-        <v>0.001270915963687003</v>
+        <v>0.03654102608561516</v>
       </c>
       <c r="EW8" t="n">
-        <v>3.023110912181437e-05</v>
+        <v>0.05107543617486954</v>
       </c>
       <c r="EX8" t="n">
-        <v>0.0001355163258267567</v>
+        <v>0.03114629536867142</v>
       </c>
       <c r="EY8" t="n">
-        <v>0.001252553891390562</v>
+        <v>0.2643618285655975</v>
       </c>
       <c r="EZ8" t="n">
-        <v>0.0009199795313179493</v>
+        <v>0.01511060446500778</v>
       </c>
       <c r="FA8" t="n">
-        <v>0.001188001362606883</v>
+        <v>0.06634575873613358</v>
       </c>
       <c r="FB8" t="n">
-        <v>0.000616159406490624</v>
+        <v>0.02016055956482887</v>
       </c>
       <c r="FC8" t="n">
-        <v>0.0009683109819889069</v>
+        <v>0.1676941215991974</v>
       </c>
       <c r="FD8" t="n">
-        <v>0.0008529496844857931</v>
+        <v>0.1147411838173866</v>
       </c>
       <c r="FE8" t="n">
-        <v>0.0004371277755126357</v>
+        <v>0.06025460734963417</v>
       </c>
       <c r="FF8" t="n">
-        <v>0.0009043082827702165</v>
+        <v>0.02299471572041512</v>
       </c>
       <c r="FG8" t="n">
-        <v>0.0001072801533155143</v>
+        <v>0.05933238938450813</v>
       </c>
       <c r="FH8" t="n">
-        <v>0.0007055046153254807</v>
+        <v>0.3100296854972839</v>
       </c>
       <c r="FI8" t="n">
-        <v>0.001175178098492324</v>
+        <v>0.04633504897356033</v>
       </c>
       <c r="FJ8" t="n">
-        <v>0.001373256789520383</v>
+        <v>0.3141735792160034</v>
       </c>
       <c r="FK8" t="n">
-        <v>0.0004487349942792207</v>
+        <v>0.1420612186193466</v>
       </c>
       <c r="FL8" t="n">
-        <v>0.0008127663750201464</v>
+        <v>0.1974340975284576</v>
       </c>
       <c r="FM8" t="n">
-        <v>0.0006275863852351904</v>
+        <v>0.1567089110612869</v>
       </c>
       <c r="FN8" t="n">
-        <v>0.0002970568893942982</v>
+        <v>0.3475358486175537</v>
       </c>
       <c r="FO8" t="n">
-        <v>0.0006494678091257811</v>
+        <v>0.002451131120324135</v>
       </c>
       <c r="FP8" t="n">
-        <v>0.0004037085745949298</v>
+        <v>0.1185628995299339</v>
       </c>
       <c r="FQ8" t="n">
-        <v>0.001467059017159045</v>
+        <v>0.4987656772136688</v>
       </c>
       <c r="FR8" t="n">
-        <v>0.0007900165510363877</v>
+        <v>0.01268074288964272</v>
       </c>
       <c r="FS8" t="n">
-        <v>0.001788132591173053</v>
+        <v>0.3346046805381775</v>
       </c>
       <c r="FT8" t="n">
-        <v>0.001916108070872724</v>
+        <v>0.1079187318682671</v>
       </c>
       <c r="FU8" t="n">
-        <v>0.0006005850154906511</v>
+        <v>0.1162674576044083</v>
       </c>
       <c r="FV8" t="n">
-        <v>0.001083732815459371</v>
+        <v>0.1458241939544678</v>
       </c>
       <c r="FW8" t="n">
-        <v>0.0006567080854438245</v>
+        <v>0.05636311694979668</v>
       </c>
       <c r="FX8" t="n">
-        <v>0.0001551886380184442</v>
+        <v>0.02542896196246147</v>
       </c>
       <c r="FY8" t="n">
-        <v>0.001748178037814796</v>
+        <v>0.08603473007678986</v>
       </c>
       <c r="FZ8" t="n">
-        <v>6.476050475612283e-05</v>
+        <v>0.0864221528172493</v>
       </c>
       <c r="GA8" t="n">
-        <v>0.000233703147387132</v>
+        <v>0.001694511622190475</v>
       </c>
       <c r="GB8" t="n">
-        <v>0.0001052865554811433</v>
+        <v>0.1541159749031067</v>
       </c>
       <c r="GC8" t="n">
-        <v>0.0003431887016631663</v>
+        <v>0.01205072738230228</v>
       </c>
       <c r="GD8" t="n">
-        <v>0.0008515632362104952</v>
+        <v>0.01751985587179661</v>
       </c>
       <c r="GE8" t="n">
-        <v>0.004463485907763243</v>
+        <v>0.1257138550281525</v>
       </c>
       <c r="GF8" t="n">
-        <v>0.0005328379338607192</v>
+        <v>0.1675367802381516</v>
       </c>
       <c r="GG8" t="n">
-        <v>0.0006941123865544796</v>
+        <v>0.1602092832326889</v>
       </c>
     </row>
     <row r="9">
@@ -5551,2278 +5551,2278 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>0.4998252987861633</v>
+        <v>0.0003528970119077712</v>
       </c>
       <c r="B10" t="n">
-        <v>1.923424959182739</v>
+        <v>4.757966598845087e-05</v>
       </c>
       <c r="C10" t="n">
-        <v>0.2176386266946793</v>
+        <v>5.696554580936208e-05</v>
       </c>
       <c r="D10" t="n">
-        <v>0.1777415126562119</v>
+        <v>0.0001632828498259187</v>
       </c>
       <c r="E10" t="n">
-        <v>0.2243903577327728</v>
+        <v>0.0006642492371611297</v>
       </c>
       <c r="F10" t="n">
-        <v>0.2587854564189911</v>
+        <v>1.067154153133743e-05</v>
       </c>
       <c r="G10" t="n">
-        <v>0.06262095272541046</v>
+        <v>0.0004588281735777855</v>
       </c>
       <c r="H10" t="n">
-        <v>0.9849560856819153</v>
+        <v>0.0003813665243797004</v>
       </c>
       <c r="I10" t="n">
-        <v>0.1440526694059372</v>
+        <v>0.0003943376359529793</v>
       </c>
       <c r="J10" t="n">
-        <v>0.4420915246009827</v>
+        <v>0.0007915617898106575</v>
       </c>
       <c r="K10" t="n">
-        <v>1.5854651927948</v>
+        <v>0.0001124202244682238</v>
       </c>
       <c r="L10" t="n">
-        <v>0.08290630578994751</v>
+        <v>7.698200352024287e-05</v>
       </c>
       <c r="M10" t="n">
-        <v>0.001257568597793579</v>
+        <v>0.0005361153744161129</v>
       </c>
       <c r="N10" t="n">
-        <v>0.2801760733127594</v>
+        <v>0.001237226650118828</v>
       </c>
       <c r="O10" t="n">
-        <v>0.1984639018774033</v>
+        <v>7.062272197799757e-05</v>
       </c>
       <c r="P10" t="n">
-        <v>0.03982508182525635</v>
+        <v>0.001100149122066796</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.169104099273682</v>
+        <v>0.001021846779622138</v>
       </c>
       <c r="R10" t="n">
-        <v>0.44675013422966</v>
+        <v>0.0005204193294048309</v>
       </c>
       <c r="S10" t="n">
-        <v>0.1368479132652283</v>
+        <v>0.0005161953158676624</v>
       </c>
       <c r="T10" t="n">
-        <v>0.2766191959381104</v>
+        <v>0.0005303686484694481</v>
       </c>
       <c r="U10" t="n">
-        <v>0.03254881501197815</v>
+        <v>0.0001951857120729983</v>
       </c>
       <c r="V10" t="n">
-        <v>0.2555984556674957</v>
+        <v>0.0002096193347824737</v>
       </c>
       <c r="W10" t="n">
-        <v>0.0448792465031147</v>
+        <v>0.0002216847060481086</v>
       </c>
       <c r="X10" t="n">
-        <v>0.3226050436496735</v>
+        <v>0.000309766037389636</v>
       </c>
       <c r="Y10" t="n">
-        <v>0.1233664900064468</v>
+        <v>0.0001596242655068636</v>
       </c>
       <c r="Z10" t="n">
-        <v>0.2981707453727722</v>
+        <v>0.0005280941259115934</v>
       </c>
       <c r="AA10" t="n">
-        <v>0.07318118959665298</v>
+        <v>0.0001972702302737162</v>
       </c>
       <c r="AB10" t="n">
-        <v>0.05593742430210114</v>
+        <v>0.0001661914284341037</v>
       </c>
       <c r="AC10" t="n">
-        <v>0.290365070104599</v>
+        <v>0.0001291815133299679</v>
       </c>
       <c r="AD10" t="n">
-        <v>0.1115806400775909</v>
+        <v>0.0004969068104401231</v>
       </c>
       <c r="AE10" t="n">
-        <v>0.005700097419321537</v>
+        <v>0.0003408316697459668</v>
       </c>
       <c r="AF10" t="n">
-        <v>0.2658684551715851</v>
+        <v>0.000464629614725709</v>
       </c>
       <c r="AG10" t="n">
-        <v>0.009065579622983932</v>
+        <v>0.000463497475720942</v>
       </c>
       <c r="AH10" t="n">
-        <v>0.1118654310703278</v>
+        <v>0.0001212584611494094</v>
       </c>
       <c r="AI10" t="n">
-        <v>0.3345914483070374</v>
+        <v>0.0001691725046839565</v>
       </c>
       <c r="AJ10" t="n">
-        <v>0.07421949505805969</v>
+        <v>0.0001420850458089262</v>
       </c>
       <c r="AK10" t="n">
-        <v>0.4673464298248291</v>
+        <v>0.0005789856077171862</v>
       </c>
       <c r="AL10" t="n">
-        <v>0.05444292724132538</v>
+        <v>0.0003941688046324998</v>
       </c>
       <c r="AM10" t="n">
-        <v>0.0653146356344223</v>
+        <v>9.383061842527241e-05</v>
       </c>
       <c r="AN10" t="n">
-        <v>0.02971053496003151</v>
+        <v>0.0002731779823079705</v>
       </c>
       <c r="AO10" t="n">
-        <v>0.1494429111480713</v>
+        <v>0.0003035058616660535</v>
       </c>
       <c r="AP10" t="n">
-        <v>0.03432333096861839</v>
+        <v>4.998162330593914e-05</v>
       </c>
       <c r="AQ10" t="n">
-        <v>0.0614880695939064</v>
+        <v>9.383945871377364e-05</v>
       </c>
       <c r="AR10" t="n">
-        <v>0.02303703129291534</v>
+        <v>0.000133101872052066</v>
       </c>
       <c r="AS10" t="n">
-        <v>0.1676953285932541</v>
+        <v>0.0001964595576282591</v>
       </c>
       <c r="AT10" t="n">
-        <v>0.07201382517814636</v>
+        <v>0.001166898873634636</v>
       </c>
       <c r="AU10" t="n">
-        <v>1.588694453239441</v>
+        <v>0.001299273804761469</v>
       </c>
       <c r="AV10" t="n">
-        <v>0.1092673912644386</v>
+        <v>0.000321252562571317</v>
       </c>
       <c r="AW10" t="n">
-        <v>0.1490118801593781</v>
+        <v>0.000131692286231555</v>
       </c>
       <c r="AX10" t="n">
-        <v>0.2650790810585022</v>
+        <v>0.0001111516176024452</v>
       </c>
       <c r="AY10" t="n">
-        <v>0.05524876341223717</v>
+        <v>8.091883501037955e-07</v>
       </c>
       <c r="AZ10" t="n">
-        <v>0.06916917115449905</v>
+        <v>0.0002084978332277387</v>
       </c>
       <c r="BA10" t="n">
-        <v>0.1357570886611938</v>
+        <v>0.0001020463678287342</v>
       </c>
       <c r="BB10" t="n">
-        <v>0.1082384586334229</v>
+        <v>0.0002977692929562181</v>
       </c>
       <c r="BC10" t="n">
-        <v>0.1894969195127487</v>
+        <v>0.0001405397633789107</v>
       </c>
       <c r="BD10" t="n">
-        <v>0.6751415729522705</v>
+        <v>0.000957354495767504</v>
       </c>
       <c r="BE10" t="n">
-        <v>0.4548468291759491</v>
+        <v>0.0001221574930241331</v>
       </c>
       <c r="BF10" t="n">
-        <v>0.4182444214820862</v>
+        <v>0.0004034034791402519</v>
       </c>
       <c r="BG10" t="n">
-        <v>0.3094128370285034</v>
+        <v>0.001375286607071757</v>
       </c>
       <c r="BH10" t="n">
-        <v>0.04550963640213013</v>
+        <v>0.000247094314545393</v>
       </c>
       <c r="BI10" t="n">
-        <v>0.2287632524967194</v>
+        <v>0.0006685905973426998</v>
       </c>
       <c r="BJ10" t="n">
-        <v>0.5636746287345886</v>
+        <v>2.598211722215638e-06</v>
       </c>
       <c r="BK10" t="n">
-        <v>0.05789702013134956</v>
+        <v>0.0001913324813358486</v>
       </c>
       <c r="BL10" t="n">
-        <v>0.155774861574173</v>
+        <v>0.000192343577509746</v>
       </c>
       <c r="BM10" t="n">
-        <v>0.948845386505127</v>
+        <v>0.0008394208271056414</v>
       </c>
       <c r="BN10" t="n">
-        <v>0.1343147456645966</v>
+        <v>0.0002957804535981268</v>
       </c>
       <c r="BO10" t="n">
-        <v>0.5223429799079895</v>
+        <v>0.0002712456625886261</v>
       </c>
       <c r="BP10" t="n">
-        <v>0.8064308166503906</v>
+        <v>0.0008274720748886466</v>
       </c>
       <c r="BQ10" t="n">
-        <v>0.1424164772033691</v>
+        <v>0.0008540772832930088</v>
       </c>
       <c r="BR10" t="n">
-        <v>0.2632484138011932</v>
+        <v>5.596518167294562e-05</v>
       </c>
       <c r="BS10" t="n">
-        <v>0.3822627067565918</v>
+        <v>0.0002280901971971616</v>
       </c>
       <c r="BT10" t="n">
-        <v>0.09925055503845215</v>
+        <v>1.086976135411533e-05</v>
       </c>
       <c r="BU10" t="n">
-        <v>0.04764256253838539</v>
+        <v>0.001007319311611354</v>
       </c>
       <c r="BV10" t="n">
-        <v>0.8304651379585266</v>
+        <v>0.001060390495695174</v>
       </c>
       <c r="BW10" t="n">
-        <v>0.2381940484046936</v>
+        <v>0.0002257785818073899</v>
       </c>
       <c r="BX10" t="n">
-        <v>0.09477041661739349</v>
+        <v>0.000254348327871412</v>
       </c>
       <c r="BY10" t="n">
-        <v>0.2670705318450928</v>
+        <v>0.0001259848213521764</v>
       </c>
       <c r="BZ10" t="n">
-        <v>0.1494571417570114</v>
+        <v>2.394481271039695e-06</v>
       </c>
       <c r="CA10" t="n">
-        <v>0.3681254088878632</v>
+        <v>0.0003626929246820509</v>
       </c>
       <c r="CB10" t="n">
-        <v>0.09300278127193451</v>
+        <v>0.0002677814627531916</v>
       </c>
       <c r="CC10" t="n">
-        <v>0.09693095833063126</v>
+        <v>5.105627133161761e-05</v>
       </c>
       <c r="CD10" t="n">
-        <v>0.01396066136658192</v>
+        <v>0.000334292883053422</v>
       </c>
       <c r="CE10" t="n">
-        <v>0.3394770324230194</v>
+        <v>2.824306648108177e-06</v>
       </c>
       <c r="CF10" t="n">
-        <v>0.1071708425879478</v>
+        <v>7.395797001663595e-05</v>
       </c>
       <c r="CG10" t="n">
-        <v>0.03834891319274902</v>
+        <v>0.0001852699497248977</v>
       </c>
       <c r="CH10" t="n">
-        <v>0.1101890429854393</v>
+        <v>0.0002598354476504028</v>
       </c>
       <c r="CI10" t="n">
-        <v>0.154060423374176</v>
+        <v>0.0001171612821053714</v>
       </c>
       <c r="CJ10" t="n">
-        <v>0.02889610268175602</v>
+        <v>0.0001777674333425239</v>
       </c>
       <c r="CK10" t="n">
-        <v>0.2002800405025482</v>
+        <v>0.0001187087182188407</v>
       </c>
       <c r="CL10" t="n">
-        <v>0.1089737042784691</v>
+        <v>0.0001209288166137412</v>
       </c>
       <c r="CM10" t="n">
-        <v>0.664746880531311</v>
+        <v>0.0002875592617783695</v>
       </c>
       <c r="CN10" t="n">
-        <v>0.9224744439125061</v>
+        <v>0.000636230455711484</v>
       </c>
       <c r="CO10" t="n">
-        <v>0.005555062554776669</v>
+        <v>4.685971362050623e-07</v>
       </c>
       <c r="CP10" t="n">
-        <v>0.467170923948288</v>
+        <v>8.661963511258364e-05</v>
       </c>
       <c r="CQ10" t="n">
-        <v>0.7487056255340576</v>
+        <v>0.0007645254954695702</v>
       </c>
       <c r="CR10" t="n">
-        <v>0.1672195047140121</v>
+        <v>0.0001978450163733214</v>
       </c>
       <c r="CS10" t="n">
-        <v>0.1766794621944427</v>
+        <v>0.0006509532686322927</v>
       </c>
       <c r="CT10" t="n">
-        <v>0.1031116172671318</v>
+        <v>7.991248276084661e-05</v>
       </c>
       <c r="CU10" t="n">
-        <v>0.08433020114898682</v>
+        <v>0.0004359513113740832</v>
       </c>
       <c r="CV10" t="n">
-        <v>0.0135835213586688</v>
+        <v>0.0002380492660449818</v>
       </c>
       <c r="CW10" t="n">
-        <v>0.2948133647441864</v>
+        <v>6.73778195050545e-05</v>
       </c>
       <c r="CX10" t="n">
-        <v>0.1561225801706314</v>
+        <v>0.0001229816261911765</v>
       </c>
       <c r="CY10" t="n">
-        <v>0.1446697413921356</v>
+        <v>0.0001486612454755232</v>
       </c>
       <c r="CZ10" t="n">
-        <v>0.06121625751256943</v>
+        <v>0.0001950214063981548</v>
       </c>
       <c r="DA10" t="n">
-        <v>0.1829411089420319</v>
+        <v>8.564475865568966e-05</v>
       </c>
       <c r="DB10" t="n">
-        <v>0.04179009050130844</v>
+        <v>0.0001644107687752694</v>
       </c>
       <c r="DC10" t="n">
-        <v>0.09231346845626831</v>
+        <v>0.0002813388709910214</v>
       </c>
       <c r="DD10" t="n">
-        <v>0.06597789376974106</v>
+        <v>0.0001391152036376297</v>
       </c>
       <c r="DE10" t="n">
-        <v>0.5504904985427856</v>
+        <v>0.0002479851536918432</v>
       </c>
       <c r="DF10" t="n">
-        <v>0.6700021624565125</v>
+        <v>0.000152474400238134</v>
       </c>
       <c r="DG10" t="n">
-        <v>0.003816880285739899</v>
+        <v>7.098596688592806e-05</v>
       </c>
       <c r="DH10" t="n">
-        <v>0.9861368536949158</v>
+        <v>0.0004444059450179338</v>
       </c>
       <c r="DI10" t="n">
-        <v>0.1277234256267548</v>
+        <v>0.0005743412766605616</v>
       </c>
       <c r="DJ10" t="n">
-        <v>0.09246804565191269</v>
+        <v>0.0004704591119661927</v>
       </c>
       <c r="DK10" t="n">
-        <v>0.6121181845664978</v>
+        <v>2.715116715990007e-05</v>
       </c>
       <c r="DL10" t="n">
-        <v>0.1776622086763382</v>
+        <v>0.0006663751555606723</v>
       </c>
       <c r="DM10" t="n">
-        <v>0.02754290401935577</v>
+        <v>0.001402548048645258</v>
       </c>
       <c r="DN10" t="n">
-        <v>0.2413041293621063</v>
+        <v>0.0007389821112155914</v>
       </c>
       <c r="DO10" t="n">
-        <v>0.4498136341571808</v>
+        <v>0.0001774517440935597</v>
       </c>
       <c r="DP10" t="n">
-        <v>0.1120468974113464</v>
+        <v>4.601319233188406e-05</v>
       </c>
       <c r="DQ10" t="n">
-        <v>0.2440106868743896</v>
+        <v>0.0002960825804620981</v>
       </c>
       <c r="DR10" t="n">
-        <v>0.07193506509065628</v>
+        <v>0.0002646411012392491</v>
       </c>
       <c r="DS10" t="n">
-        <v>0.0524044930934906</v>
+        <v>0.0009457161650061607</v>
       </c>
       <c r="DT10" t="n">
-        <v>0.04889919236302376</v>
+        <v>0.0001128871008404531</v>
       </c>
       <c r="DU10" t="n">
-        <v>0.2664954662322998</v>
+        <v>0.000439259922131896</v>
       </c>
       <c r="DV10" t="n">
-        <v>0.01786016672849655</v>
+        <v>7.353878754656762e-05</v>
       </c>
       <c r="DW10" t="n">
-        <v>0.1163226664066315</v>
+        <v>0.0001653027138672769</v>
       </c>
       <c r="DX10" t="n">
-        <v>0.1134885773062706</v>
+        <v>3.5273715184303e-05</v>
       </c>
       <c r="DY10" t="n">
-        <v>0.142281174659729</v>
+        <v>0.0002628526126500219</v>
       </c>
       <c r="DZ10" t="n">
-        <v>0.2672837376594543</v>
+        <v>0.0003209714486729354</v>
       </c>
       <c r="EA10" t="n">
-        <v>0.1444855928421021</v>
+        <v>0.0008891924517229199</v>
       </c>
       <c r="EB10" t="n">
-        <v>0.2932483553886414</v>
+        <v>0.0003613425651565194</v>
       </c>
       <c r="EC10" t="n">
-        <v>0.2435330450534821</v>
+        <v>0.0002958400873467326</v>
       </c>
       <c r="ED10" t="n">
-        <v>0.1588887274265289</v>
+        <v>0.0001346835488220677</v>
       </c>
       <c r="EE10" t="n">
-        <v>0.1165195405483246</v>
+        <v>4.055803583469242e-05</v>
       </c>
       <c r="EF10" t="n">
-        <v>0.08709943294525146</v>
+        <v>0.0001756760757416487</v>
       </c>
       <c r="EG10" t="n">
-        <v>0.1024798005819321</v>
+        <v>0.0002738097682595253</v>
       </c>
       <c r="EH10" t="n">
-        <v>0.05763985961675644</v>
+        <v>0.0003242628299631178</v>
       </c>
       <c r="EI10" t="n">
-        <v>0.3129061162471771</v>
+        <v>7.3269970016554e-05</v>
       </c>
       <c r="EJ10" t="n">
-        <v>0.01819682493805885</v>
+        <v>0.0001006163802230731</v>
       </c>
       <c r="EK10" t="n">
-        <v>0.08663307875394821</v>
+        <v>9.486504131928086e-05</v>
       </c>
       <c r="EL10" t="n">
-        <v>0.007387807592749596</v>
+        <v>0.0003857341653201729</v>
       </c>
       <c r="EM10" t="n">
-        <v>0.1886072605848312</v>
+        <v>0.000177848050952889</v>
       </c>
       <c r="EN10" t="n">
-        <v>0.08950497955083847</v>
+        <v>0.00011555923265405</v>
       </c>
       <c r="EO10" t="n">
-        <v>0.2197783291339874</v>
+        <v>0.0001308898936258629</v>
       </c>
       <c r="EP10" t="n">
-        <v>0.124640665948391</v>
+        <v>0.000281540909782052</v>
       </c>
       <c r="EQ10" t="n">
-        <v>0.1294800788164139</v>
+        <v>0.000290682801278308</v>
       </c>
       <c r="ER10" t="n">
-        <v>0.04001341760158539</v>
+        <v>0.0002674689167179167</v>
       </c>
       <c r="ES10" t="n">
-        <v>0.02099731750786304</v>
+        <v>0.0002505031879991293</v>
       </c>
       <c r="ET10" t="n">
-        <v>0.1149158179759979</v>
+        <v>0.0003573851136025041</v>
       </c>
       <c r="EU10" t="n">
-        <v>0.2418533861637115</v>
+        <v>0.0001168298695120029</v>
       </c>
       <c r="EV10" t="n">
-        <v>0.2912701666355133</v>
+        <v>0.0003345052828080952</v>
       </c>
       <c r="EW10" t="n">
-        <v>0.04533061385154724</v>
+        <v>0.0002985179307870567</v>
       </c>
       <c r="EX10" t="n">
-        <v>0.02053403481841087</v>
+        <v>0.0003427392803132534</v>
       </c>
       <c r="EY10" t="n">
-        <v>0.2744033634662628</v>
+        <v>6.885011680424213e-05</v>
       </c>
       <c r="EZ10" t="n">
-        <v>0.07955475896596909</v>
+        <v>8.317665196955204e-05</v>
       </c>
       <c r="FA10" t="n">
-        <v>0.07396455854177475</v>
+        <v>0.0002146608458133414</v>
       </c>
       <c r="FB10" t="n">
-        <v>0.05302577093243599</v>
+        <v>0.000157704358571209</v>
       </c>
       <c r="FC10" t="n">
-        <v>0.1750225424766541</v>
+        <v>6.641559593845159e-05</v>
       </c>
       <c r="FD10" t="n">
-        <v>0.1159718334674835</v>
+        <v>0.0001955746265593916</v>
       </c>
       <c r="FE10" t="n">
-        <v>0.2297014892101288</v>
+        <v>0.0003112703270744532</v>
       </c>
       <c r="FF10" t="n">
-        <v>0.0989677757024765</v>
+        <v>0.000248147000093013</v>
       </c>
       <c r="FG10" t="n">
-        <v>0.09121943265199661</v>
+        <v>0.0001149271702161059</v>
       </c>
       <c r="FH10" t="n">
-        <v>0.0601232722401619</v>
+        <v>0.0001742065069265664</v>
       </c>
       <c r="FI10" t="n">
-        <v>0.1130028814077377</v>
+        <v>0.0005674627609550953</v>
       </c>
       <c r="FJ10" t="n">
-        <v>0.04426955431699753</v>
+        <v>0.000616132456343621</v>
       </c>
       <c r="FK10" t="n">
-        <v>0.2257789671421051</v>
+        <v>0.0003419925342313945</v>
       </c>
       <c r="FL10" t="n">
-        <v>0.09034328907728195</v>
+        <v>3.355308581376448e-05</v>
       </c>
       <c r="FM10" t="n">
-        <v>0.1236865818500519</v>
+        <v>8.448489097645506e-05</v>
       </c>
       <c r="FN10" t="n">
-        <v>0.1879333406686783</v>
+        <v>0.0001766719797160476</v>
       </c>
       <c r="FO10" t="n">
-        <v>0.07093587517738342</v>
+        <v>0.0002788577112369239</v>
       </c>
       <c r="FP10" t="n">
-        <v>0.2537055015563965</v>
+        <v>0.0009647613624110818</v>
       </c>
       <c r="FQ10" t="n">
-        <v>0.02736565843224525</v>
+        <v>0.0006400898564606905</v>
       </c>
       <c r="FR10" t="n">
-        <v>0.2400118410587311</v>
+        <v>0.001411174773238599</v>
       </c>
       <c r="FS10" t="n">
-        <v>0.3938583731651306</v>
+        <v>0.0009015662944875658</v>
       </c>
       <c r="FT10" t="n">
-        <v>0.08444947749376297</v>
+        <v>0.0009401061106473207</v>
       </c>
       <c r="FU10" t="n">
-        <v>0.05648843199014664</v>
+        <v>2.899867831729352e-05</v>
       </c>
       <c r="FV10" t="n">
-        <v>0.1152653470635414</v>
+        <v>9.753709309734404e-05</v>
       </c>
       <c r="FW10" t="n">
-        <v>0.05855530500411987</v>
+        <v>1.535822229925543e-05</v>
       </c>
       <c r="FX10" t="n">
-        <v>0.121086522936821</v>
+        <v>0.0004162584082223475</v>
       </c>
       <c r="FY10" t="n">
-        <v>0.3005736470222473</v>
+        <v>0.0004710472421720624</v>
       </c>
       <c r="FZ10" t="n">
-        <v>0.3904782235622406</v>
+        <v>0.0005115319509059191</v>
       </c>
       <c r="GA10" t="n">
-        <v>0.1263233870267868</v>
+        <v>0.0001594572677277029</v>
       </c>
       <c r="GB10" t="n">
-        <v>0.0449942946434021</v>
+        <v>0.0007412609411403537</v>
       </c>
       <c r="GC10" t="n">
-        <v>0.08069375902414322</v>
+        <v>0.0007752327946946025</v>
       </c>
       <c r="GD10" t="n">
-        <v>0.09286487847566605</v>
+        <v>7.905433449195698e-05</v>
       </c>
       <c r="GE10" t="n">
-        <v>0.4772658944129944</v>
+        <v>0.0001345165073871613</v>
       </c>
       <c r="GF10" t="n">
-        <v>0.1438503861427307</v>
+        <v>0.0002847152063623071</v>
       </c>
       <c r="GG10" t="n">
-        <v>0.03161982819437981</v>
+        <v>6.699086225125939e-05</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>0.08718274533748627</v>
+        <v>0.3076356649398804</v>
       </c>
       <c r="B11" t="n">
-        <v>0.4229502975940704</v>
+        <v>0.2478847950696945</v>
       </c>
       <c r="C11" t="n">
-        <v>0.008007068186998367</v>
+        <v>0.004398494958877563</v>
       </c>
       <c r="D11" t="n">
-        <v>0.1576797068119049</v>
+        <v>0.07478587329387665</v>
       </c>
       <c r="E11" t="n">
-        <v>0.2364848107099533</v>
+        <v>0.1300386339426041</v>
       </c>
       <c r="F11" t="n">
-        <v>0.1140234023332596</v>
+        <v>0.04139029234647751</v>
       </c>
       <c r="G11" t="n">
-        <v>0.08345705270767212</v>
+        <v>0.1395008414983749</v>
       </c>
       <c r="H11" t="n">
-        <v>0.08369220048189163</v>
+        <v>0.1131452620029449</v>
       </c>
       <c r="I11" t="n">
-        <v>0.05331514775753021</v>
+        <v>0.1542719453573227</v>
       </c>
       <c r="J11" t="n">
-        <v>0.0501410998404026</v>
+        <v>0.1503058820962906</v>
       </c>
       <c r="K11" t="n">
-        <v>0.3330986797809601</v>
+        <v>0.484029233455658</v>
       </c>
       <c r="L11" t="n">
-        <v>0.02426040358841419</v>
+        <v>0.09500858932733536</v>
       </c>
       <c r="M11" t="n">
-        <v>0.04173325002193451</v>
+        <v>0.2477491647005081</v>
       </c>
       <c r="N11" t="n">
-        <v>0.4542860686779022</v>
+        <v>0.170293003320694</v>
       </c>
       <c r="O11" t="n">
-        <v>0.1546508073806763</v>
+        <v>0.2051087319850922</v>
       </c>
       <c r="P11" t="n">
-        <v>0.02573533356189728</v>
+        <v>0.06512220203876495</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.3814702033996582</v>
+        <v>0.3287241458892822</v>
       </c>
       <c r="R11" t="n">
-        <v>0.06420295685529709</v>
+        <v>0.2433328479528427</v>
       </c>
       <c r="S11" t="n">
-        <v>0.007064684294164181</v>
+        <v>0.09200151264667511</v>
       </c>
       <c r="T11" t="n">
-        <v>0.232913613319397</v>
+        <v>0.1018688827753067</v>
       </c>
       <c r="U11" t="n">
-        <v>0.06855268776416779</v>
+        <v>0.1866618394851685</v>
       </c>
       <c r="V11" t="n">
-        <v>0.04796876758337021</v>
+        <v>0.04072612896561623</v>
       </c>
       <c r="W11" t="n">
-        <v>0.2239392399787903</v>
+        <v>0.0551152229309082</v>
       </c>
       <c r="X11" t="n">
-        <v>0.0933506190776825</v>
+        <v>0.1388028413057327</v>
       </c>
       <c r="Y11" t="n">
-        <v>0.03148725628852844</v>
+        <v>0.02713438123464584</v>
       </c>
       <c r="Z11" t="n">
-        <v>0.05404902994632721</v>
+        <v>0.02990386635065079</v>
       </c>
       <c r="AA11" t="n">
-        <v>0.04884711280465126</v>
+        <v>0.01817349344491959</v>
       </c>
       <c r="AB11" t="n">
-        <v>0.00122014619410038</v>
+        <v>0.1760283261537552</v>
       </c>
       <c r="AC11" t="n">
-        <v>0.1495012640953064</v>
+        <v>0.2770029902458191</v>
       </c>
       <c r="AD11" t="n">
-        <v>0.02493386901915073</v>
+        <v>0.03892627358436584</v>
       </c>
       <c r="AE11" t="n">
-        <v>0.177610382437706</v>
+        <v>0.006358688697218895</v>
       </c>
       <c r="AF11" t="n">
-        <v>0.06699670106172562</v>
+        <v>0.3157313466072083</v>
       </c>
       <c r="AG11" t="n">
-        <v>0.1416183412075043</v>
+        <v>0.03926332667469978</v>
       </c>
       <c r="AH11" t="n">
-        <v>0.1524500846862793</v>
+        <v>0.04771765321493149</v>
       </c>
       <c r="AI11" t="n">
-        <v>0.1098671108484268</v>
+        <v>0.1000670194625854</v>
       </c>
       <c r="AJ11" t="n">
-        <v>0.02534983307123184</v>
+        <v>0.01093960646539927</v>
       </c>
       <c r="AK11" t="n">
-        <v>0.1393211334943771</v>
+        <v>0.004216279834508896</v>
       </c>
       <c r="AL11" t="n">
-        <v>0.1409315764904022</v>
+        <v>0.09290316700935364</v>
       </c>
       <c r="AM11" t="n">
-        <v>0.03505124151706696</v>
+        <v>0.07500298321247101</v>
       </c>
       <c r="AN11" t="n">
-        <v>0.08972083032131195</v>
+        <v>0.0842699408531189</v>
       </c>
       <c r="AO11" t="n">
-        <v>0.02270181477069855</v>
+        <v>0.2764661610126495</v>
       </c>
       <c r="AP11" t="n">
-        <v>0.1531084179878235</v>
+        <v>0.09926325082778931</v>
       </c>
       <c r="AQ11" t="n">
-        <v>0.132347971200943</v>
+        <v>0.01817317306995392</v>
       </c>
       <c r="AR11" t="n">
-        <v>0.1305807679891586</v>
+        <v>0.07773195207118988</v>
       </c>
       <c r="AS11" t="n">
-        <v>0.04508676007390022</v>
+        <v>0.008209869265556335</v>
       </c>
       <c r="AT11" t="n">
-        <v>0.2919116616249084</v>
+        <v>0.0946664959192276</v>
       </c>
       <c r="AU11" t="n">
-        <v>0.5043414235115051</v>
+        <v>0.3663521111011505</v>
       </c>
       <c r="AV11" t="n">
-        <v>0.01210800651460886</v>
+        <v>0.1682250052690506</v>
       </c>
       <c r="AW11" t="n">
-        <v>0.2519349455833435</v>
+        <v>0.06771606951951981</v>
       </c>
       <c r="AX11" t="n">
-        <v>0.3884045779705048</v>
+        <v>0.08379291743040085</v>
       </c>
       <c r="AY11" t="n">
-        <v>0.04743872582912445</v>
+        <v>0.1242166608572006</v>
       </c>
       <c r="AZ11" t="n">
-        <v>0.08081428706645966</v>
+        <v>0.08845353126525879</v>
       </c>
       <c r="BA11" t="n">
-        <v>0.197432741522789</v>
+        <v>0.009652517735958099</v>
       </c>
       <c r="BB11" t="n">
-        <v>0.08291184902191162</v>
+        <v>0.003430208191275597</v>
       </c>
       <c r="BC11" t="n">
-        <v>0.1054543629288673</v>
+        <v>0.3317697644233704</v>
       </c>
       <c r="BD11" t="n">
-        <v>0.1138232052326202</v>
+        <v>0.06242502480745316</v>
       </c>
       <c r="BE11" t="n">
-        <v>0.03597582876682281</v>
+        <v>0.01983515545725822</v>
       </c>
       <c r="BF11" t="n">
-        <v>0.02373291552066803</v>
+        <v>0.02938628755509853</v>
       </c>
       <c r="BG11" t="n">
-        <v>0.426533043384552</v>
+        <v>0.1659194380044937</v>
       </c>
       <c r="BH11" t="n">
-        <v>0.04477380961179733</v>
+        <v>0.01341839320957661</v>
       </c>
       <c r="BI11" t="n">
-        <v>0.008679389953613281</v>
+        <v>0.06524243950843811</v>
       </c>
       <c r="BJ11" t="n">
-        <v>0.2942180931568146</v>
+        <v>0.03040244616568089</v>
       </c>
       <c r="BK11" t="n">
-        <v>0.05406005308032036</v>
+        <v>0.09869977086782455</v>
       </c>
       <c r="BL11" t="n">
-        <v>0.01161909569054842</v>
+        <v>0.1335102021694183</v>
       </c>
       <c r="BM11" t="n">
-        <v>0.1687144339084625</v>
+        <v>0.4387487471103668</v>
       </c>
       <c r="BN11" t="n">
-        <v>0.03716488555073738</v>
+        <v>0.1956851631402969</v>
       </c>
       <c r="BO11" t="n">
-        <v>0.3122652769088745</v>
+        <v>0.1169569790363312</v>
       </c>
       <c r="BP11" t="n">
-        <v>0.4610851407051086</v>
+        <v>0.3001567721366882</v>
       </c>
       <c r="BQ11" t="n">
-        <v>0.09183383733034134</v>
+        <v>0.2421707808971405</v>
       </c>
       <c r="BR11" t="n">
-        <v>0.01750965043902397</v>
+        <v>0.0924542099237442</v>
       </c>
       <c r="BS11" t="n">
-        <v>0.2485316842794418</v>
+        <v>0.07167631387710571</v>
       </c>
       <c r="BT11" t="n">
-        <v>0.1141746416687965</v>
+        <v>0.02121914923191071</v>
       </c>
       <c r="BU11" t="n">
-        <v>0.1473492980003357</v>
+        <v>0.1653304994106293</v>
       </c>
       <c r="BV11" t="n">
-        <v>0.2551120817661285</v>
+        <v>0.3839480876922607</v>
       </c>
       <c r="BW11" t="n">
-        <v>0.0426517054438591</v>
+        <v>0.2492154985666275</v>
       </c>
       <c r="BX11" t="n">
-        <v>0.02864522859454155</v>
+        <v>0.05426237359642982</v>
       </c>
       <c r="BY11" t="n">
-        <v>0.1641825884580612</v>
+        <v>0.03510191291570663</v>
       </c>
       <c r="BZ11" t="n">
-        <v>0.03439672291278839</v>
+        <v>0.06033627316355705</v>
       </c>
       <c r="CA11" t="n">
-        <v>0.175944596529007</v>
+        <v>0.1407849192619324</v>
       </c>
       <c r="CB11" t="n">
-        <v>0.1315598785877228</v>
+        <v>0.04403473436832428</v>
       </c>
       <c r="CC11" t="n">
-        <v>0.01511267852038145</v>
+        <v>0.04547147825360298</v>
       </c>
       <c r="CD11" t="n">
-        <v>0.01343859173357487</v>
+        <v>0.06806144118309021</v>
       </c>
       <c r="CE11" t="n">
-        <v>0.09777440875768661</v>
+        <v>0.07341745495796204</v>
       </c>
       <c r="CF11" t="n">
-        <v>0.01428625825792551</v>
+        <v>0.07215707749128342</v>
       </c>
       <c r="CG11" t="n">
-        <v>0.02035474590957165</v>
+        <v>0.03283685445785522</v>
       </c>
       <c r="CH11" t="n">
-        <v>0.002919909544289112</v>
+        <v>0.03839639201760292</v>
       </c>
       <c r="CI11" t="n">
-        <v>0.02670093439519405</v>
+        <v>0.05641200765967369</v>
       </c>
       <c r="CJ11" t="n">
-        <v>0.00130836246535182</v>
+        <v>0.005673179402947426</v>
       </c>
       <c r="CK11" t="n">
-        <v>0.01929747313261032</v>
+        <v>0.05938369408249855</v>
       </c>
       <c r="CL11" t="n">
-        <v>0.01257049944251776</v>
+        <v>0.03760639205574989</v>
       </c>
       <c r="CM11" t="n">
-        <v>0.2362186312675476</v>
+        <v>0.1651471853256226</v>
       </c>
       <c r="CN11" t="n">
-        <v>0.1280432343482971</v>
+        <v>0.3414634168148041</v>
       </c>
       <c r="CO11" t="n">
-        <v>0.01096479874104261</v>
+        <v>0.1407126635313034</v>
       </c>
       <c r="CP11" t="n">
-        <v>0.04978946596384048</v>
+        <v>0.09377089142799377</v>
       </c>
       <c r="CQ11" t="n">
-        <v>0.4612294733524323</v>
+        <v>0.006618384271860123</v>
       </c>
       <c r="CR11" t="n">
-        <v>0.02499409765005112</v>
+        <v>0.04482018947601318</v>
       </c>
       <c r="CS11" t="n">
-        <v>0.06974133104085922</v>
+        <v>0.04957475513219833</v>
       </c>
       <c r="CT11" t="n">
-        <v>0.02705636620521545</v>
+        <v>0.003622420132160187</v>
       </c>
       <c r="CU11" t="n">
-        <v>0.08876857906579971</v>
+        <v>0.01052744872868061</v>
       </c>
       <c r="CV11" t="n">
-        <v>0.01133069675415754</v>
+        <v>0.04253977909684181</v>
       </c>
       <c r="CW11" t="n">
-        <v>0.100461371243</v>
+        <v>0.0823189988732338</v>
       </c>
       <c r="CX11" t="n">
-        <v>0.01573817804455757</v>
+        <v>0.06059576198458672</v>
       </c>
       <c r="CY11" t="n">
-        <v>0.05535317957401276</v>
+        <v>0.06970612704753876</v>
       </c>
       <c r="CZ11" t="n">
-        <v>0.01451177801936865</v>
+        <v>0.009310315363109112</v>
       </c>
       <c r="DA11" t="n">
-        <v>0.0204915776848793</v>
+        <v>0.02646583691239357</v>
       </c>
       <c r="DB11" t="n">
-        <v>0.01708207279443741</v>
+        <v>0.006306531839072704</v>
       </c>
       <c r="DC11" t="n">
-        <v>0.01804523542523384</v>
+        <v>0.02885669842362404</v>
       </c>
       <c r="DD11" t="n">
-        <v>0.01372724957764149</v>
+        <v>0.02803998813033104</v>
       </c>
       <c r="DE11" t="n">
-        <v>0.2636444568634033</v>
+        <v>0.08211816102266312</v>
       </c>
       <c r="DF11" t="n">
-        <v>0.5548843741416931</v>
+        <v>0.5175085663795471</v>
       </c>
       <c r="DG11" t="n">
-        <v>0.05796391144394875</v>
+        <v>0.09864558279514313</v>
       </c>
       <c r="DH11" t="n">
-        <v>0.04009392485022545</v>
+        <v>0.3782583177089691</v>
       </c>
       <c r="DI11" t="n">
-        <v>0.02783726714551449</v>
+        <v>0.02534114941954613</v>
       </c>
       <c r="DJ11" t="n">
-        <v>0.1294164508581161</v>
+        <v>0.2505988776683807</v>
       </c>
       <c r="DK11" t="n">
-        <v>0.2090977728366852</v>
+        <v>0.05020764470100403</v>
       </c>
       <c r="DL11" t="n">
-        <v>0.1363726109266281</v>
+        <v>0.06316529214382172</v>
       </c>
       <c r="DM11" t="n">
-        <v>0.1251311451196671</v>
+        <v>0.05414852499961853</v>
       </c>
       <c r="DN11" t="n">
-        <v>0.1736485958099365</v>
+        <v>0.03323927521705627</v>
       </c>
       <c r="DO11" t="n">
-        <v>0.1842095106840134</v>
+        <v>0.02466857992112637</v>
       </c>
       <c r="DP11" t="n">
-        <v>0.06131472066044807</v>
+        <v>0.1766144931316376</v>
       </c>
       <c r="DQ11" t="n">
-        <v>0.07975310087203979</v>
+        <v>0.04475546628236771</v>
       </c>
       <c r="DR11" t="n">
-        <v>0.05869985371828079</v>
+        <v>0.06678995490074158</v>
       </c>
       <c r="DS11" t="n">
-        <v>0.05560792237520218</v>
+        <v>0.02985242009162903</v>
       </c>
       <c r="DT11" t="n">
-        <v>0.1125156432390213</v>
+        <v>0.09955010563135147</v>
       </c>
       <c r="DU11" t="n">
-        <v>0.0927681103348732</v>
+        <v>0.1166307777166367</v>
       </c>
       <c r="DV11" t="n">
-        <v>0.0502605214715004</v>
+        <v>0.05757733061909676</v>
       </c>
       <c r="DW11" t="n">
-        <v>0.0749785453081131</v>
+        <v>0.155674085021019</v>
       </c>
       <c r="DX11" t="n">
-        <v>0.06266747415065765</v>
+        <v>0.07469525188207626</v>
       </c>
       <c r="DY11" t="n">
-        <v>0.1172436475753784</v>
+        <v>0.03731492534279823</v>
       </c>
       <c r="DZ11" t="n">
-        <v>0.1773560792207718</v>
+        <v>0.01859315112233162</v>
       </c>
       <c r="EA11" t="n">
-        <v>0.06028204411268234</v>
+        <v>0.07858544588088989</v>
       </c>
       <c r="EB11" t="n">
-        <v>0.05811221525073051</v>
+        <v>0.08818003535270691</v>
       </c>
       <c r="EC11" t="n">
-        <v>0.05341057106852531</v>
+        <v>0.03587109223008156</v>
       </c>
       <c r="ED11" t="n">
-        <v>0.048536516726017</v>
+        <v>0.1163788884878159</v>
       </c>
       <c r="EE11" t="n">
-        <v>0.05859313905239105</v>
+        <v>0.07626604288816452</v>
       </c>
       <c r="EF11" t="n">
-        <v>0.1014342978596687</v>
+        <v>0.01164590567350388</v>
       </c>
       <c r="EG11" t="n">
-        <v>0.1400466859340668</v>
+        <v>0.05004347860813141</v>
       </c>
       <c r="EH11" t="n">
-        <v>0.02232034876942635</v>
+        <v>0.08316578716039658</v>
       </c>
       <c r="EI11" t="n">
-        <v>0.05620431154966354</v>
+        <v>0.06797579675912857</v>
       </c>
       <c r="EJ11" t="n">
-        <v>0.01035319548100233</v>
+        <v>0.04046002402901649</v>
       </c>
       <c r="EK11" t="n">
-        <v>0.01065284851938486</v>
+        <v>0.04906844720244408</v>
       </c>
       <c r="EL11" t="n">
-        <v>0.05864731967449188</v>
+        <v>0.0223962776362896</v>
       </c>
       <c r="EM11" t="n">
-        <v>0.01741366274654865</v>
+        <v>0.09030351787805557</v>
       </c>
       <c r="EN11" t="n">
-        <v>0.02571416273713112</v>
+        <v>0.02206235378980637</v>
       </c>
       <c r="EO11" t="n">
-        <v>0.07098886370658875</v>
+        <v>0.02172520384192467</v>
       </c>
       <c r="EP11" t="n">
-        <v>0.0165523886680603</v>
+        <v>0.09694353491067886</v>
       </c>
       <c r="EQ11" t="n">
-        <v>0.0150339100509882</v>
+        <v>0.04473806917667389</v>
       </c>
       <c r="ER11" t="n">
-        <v>0.03835704177618027</v>
+        <v>0.036667350679636</v>
       </c>
       <c r="ES11" t="n">
-        <v>0.00883090402930975</v>
+        <v>0.1783284842967987</v>
       </c>
       <c r="ET11" t="n">
-        <v>0.06167353689670563</v>
+        <v>0.06309501826763153</v>
       </c>
       <c r="EU11" t="n">
-        <v>0.02393713220953941</v>
+        <v>0.1394422501325607</v>
       </c>
       <c r="EV11" t="n">
-        <v>0.02577219530940056</v>
+        <v>0.04697772115468979</v>
       </c>
       <c r="EW11" t="n">
-        <v>0.04345311969518661</v>
+        <v>0.0145510695874691</v>
       </c>
       <c r="EX11" t="n">
-        <v>0.02139867097139359</v>
+        <v>0.04158222675323486</v>
       </c>
       <c r="EY11" t="n">
-        <v>0.07024235278367996</v>
+        <v>0.1247200965881348</v>
       </c>
       <c r="EZ11" t="n">
-        <v>0.007152218837291002</v>
+        <v>0.06074518710374832</v>
       </c>
       <c r="FA11" t="n">
-        <v>0.03350904583930969</v>
+        <v>0.03176163509488106</v>
       </c>
       <c r="FB11" t="n">
-        <v>0.01484758872538805</v>
+        <v>0.01875145547091961</v>
       </c>
       <c r="FC11" t="n">
-        <v>0.0009946614736691117</v>
+        <v>0.04621098563075066</v>
       </c>
       <c r="FD11" t="n">
-        <v>0.008685516193509102</v>
+        <v>0.009635938331484795</v>
       </c>
       <c r="FE11" t="n">
-        <v>0.04396221414208412</v>
+        <v>0.04450877755880356</v>
       </c>
       <c r="FF11" t="n">
-        <v>0.006565921939909458</v>
+        <v>0.04308446124196053</v>
       </c>
       <c r="FG11" t="n">
-        <v>0.1784050166606903</v>
+        <v>0.03493211790919304</v>
       </c>
       <c r="FH11" t="n">
-        <v>0.1003618016839027</v>
+        <v>0.002817302942276001</v>
       </c>
       <c r="FI11" t="n">
-        <v>0.05413350462913513</v>
+        <v>0.005433820188045502</v>
       </c>
       <c r="FJ11" t="n">
-        <v>0.05827060341835022</v>
+        <v>0.06096872314810753</v>
       </c>
       <c r="FK11" t="n">
-        <v>0.04530729725956917</v>
+        <v>0.04665156081318855</v>
       </c>
       <c r="FL11" t="n">
-        <v>0.03833622485399246</v>
+        <v>0.1861255019903183</v>
       </c>
       <c r="FM11" t="n">
-        <v>0.01560258120298386</v>
+        <v>0.03927069529891014</v>
       </c>
       <c r="FN11" t="n">
-        <v>0.0905970111489296</v>
+        <v>0.02244530990719795</v>
       </c>
       <c r="FO11" t="n">
-        <v>0.0156182711943984</v>
+        <v>0.05825607106089592</v>
       </c>
       <c r="FP11" t="n">
-        <v>0.1156041100621223</v>
+        <v>0.1939982026815414</v>
       </c>
       <c r="FQ11" t="n">
-        <v>0.05608278885483742</v>
+        <v>0.2219327241182327</v>
       </c>
       <c r="FR11" t="n">
-        <v>0.07839351147413254</v>
+        <v>0.09771294146776199</v>
       </c>
       <c r="FS11" t="n">
-        <v>0.3836862742900848</v>
+        <v>0.2336768954992294</v>
       </c>
       <c r="FT11" t="n">
-        <v>0.1479007005691528</v>
+        <v>0.4966000914573669</v>
       </c>
       <c r="FU11" t="n">
-        <v>0.001280385535210371</v>
+        <v>0.2066365033388138</v>
       </c>
       <c r="FV11" t="n">
-        <v>0.01171471551060677</v>
+        <v>0.02887715771794319</v>
       </c>
       <c r="FW11" t="n">
-        <v>0.04082655161619186</v>
+        <v>0.04643314331769943</v>
       </c>
       <c r="FX11" t="n">
-        <v>0.04367509484291077</v>
+        <v>0.08094987273216248</v>
       </c>
       <c r="FY11" t="n">
-        <v>0.0231044739484787</v>
+        <v>0.03079877980053425</v>
       </c>
       <c r="FZ11" t="n">
-        <v>0.1842164099216461</v>
+        <v>0.1260204613208771</v>
       </c>
       <c r="GA11" t="n">
-        <v>0.09419061243534088</v>
+        <v>0.02969538792967796</v>
       </c>
       <c r="GB11" t="n">
-        <v>0.3293049931526184</v>
+        <v>0.04186810553073883</v>
       </c>
       <c r="GC11" t="n">
-        <v>0.2919847071170807</v>
+        <v>0.01186426170170307</v>
       </c>
       <c r="GD11" t="n">
-        <v>0.09554892778396606</v>
+        <v>0.05613202974200249</v>
       </c>
       <c r="GE11" t="n">
-        <v>0.1639106422662735</v>
+        <v>0.1143720224499702</v>
       </c>
       <c r="GF11" t="n">
-        <v>0.2901057600975037</v>
+        <v>0.05629958957433701</v>
       </c>
       <c r="GG11" t="n">
-        <v>0.003542311023920774</v>
+        <v>0.08563957363367081</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>0.01151251699775457</v>
+        <v>0.116446852684021</v>
       </c>
       <c r="B12" t="n">
-        <v>0.182843878865242</v>
+        <v>0.1115045249462128</v>
       </c>
       <c r="C12" t="n">
-        <v>0.01300285570323467</v>
+        <v>0.04162075370550156</v>
       </c>
       <c r="D12" t="n">
-        <v>0.04982105642557144</v>
+        <v>0.163736954331398</v>
       </c>
       <c r="E12" t="n">
-        <v>0.04891587793827057</v>
+        <v>0.1298920512199402</v>
       </c>
       <c r="F12" t="n">
-        <v>0.04205528274178505</v>
+        <v>0.2819554209709167</v>
       </c>
       <c r="G12" t="n">
-        <v>0.07500438392162323</v>
+        <v>0.2378935217857361</v>
       </c>
       <c r="H12" t="n">
-        <v>0.01027992740273476</v>
+        <v>0.1822610050439835</v>
       </c>
       <c r="I12" t="n">
-        <v>0.008865335024893284</v>
+        <v>0.1904947310686111</v>
       </c>
       <c r="J12" t="n">
-        <v>0.01842367462813854</v>
+        <v>0.1142728626728058</v>
       </c>
       <c r="K12" t="n">
-        <v>0.1262450516223907</v>
+        <v>0.1955713182687759</v>
       </c>
       <c r="L12" t="n">
-        <v>0.009061811491847038</v>
+        <v>0.09435609728097916</v>
       </c>
       <c r="M12" t="n">
-        <v>0.09248070418834686</v>
+        <v>0.1837194859981537</v>
       </c>
       <c r="N12" t="n">
-        <v>0.06327646225690842</v>
+        <v>0.1733860671520233</v>
       </c>
       <c r="O12" t="n">
-        <v>0.05140372738242149</v>
+        <v>0.1664083003997803</v>
       </c>
       <c r="P12" t="n">
-        <v>0.0667421892285347</v>
+        <v>0.2919058501720428</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.02694720402359962</v>
+        <v>0.1085413321852684</v>
       </c>
       <c r="R12" t="n">
-        <v>0.007602690253406763</v>
+        <v>0.08974073827266693</v>
       </c>
       <c r="S12" t="n">
-        <v>0.02729225158691406</v>
+        <v>0.009796109981834888</v>
       </c>
       <c r="T12" t="n">
-        <v>0.04990958049893379</v>
+        <v>0.03779506683349609</v>
       </c>
       <c r="U12" t="n">
-        <v>0.0007059570634737611</v>
+        <v>0.03056674264371395</v>
       </c>
       <c r="V12" t="n">
-        <v>0.001395133323967457</v>
+        <v>0.01709647476673126</v>
       </c>
       <c r="W12" t="n">
-        <v>0.04326211288571358</v>
+        <v>0.03904119879007339</v>
       </c>
       <c r="X12" t="n">
-        <v>0.03496615216135979</v>
+        <v>0.01738516613841057</v>
       </c>
       <c r="Y12" t="n">
-        <v>0.0002066536108031869</v>
+        <v>0.08500052988529205</v>
       </c>
       <c r="Z12" t="n">
-        <v>0.006405945867300034</v>
+        <v>0.03938914090394974</v>
       </c>
       <c r="AA12" t="n">
-        <v>0.01389175560325384</v>
+        <v>0.07160112261772156</v>
       </c>
       <c r="AB12" t="n">
-        <v>0.01801081746816635</v>
+        <v>0.02426445484161377</v>
       </c>
       <c r="AC12" t="n">
-        <v>0.04240187630057335</v>
+        <v>0.1245471388101578</v>
       </c>
       <c r="AD12" t="n">
-        <v>0.0001467897091060877</v>
+        <v>0.1721761375665665</v>
       </c>
       <c r="AE12" t="n">
-        <v>0.003247216809540987</v>
+        <v>0.03992463275790215</v>
       </c>
       <c r="AF12" t="n">
-        <v>0.00245667016133666</v>
+        <v>0.2021651417016983</v>
       </c>
       <c r="AG12" t="n">
-        <v>0.01167356967926025</v>
+        <v>0.05851263180375099</v>
       </c>
       <c r="AH12" t="n">
-        <v>0.0007841926999390125</v>
+        <v>0.04855562001466751</v>
       </c>
       <c r="AI12" t="n">
-        <v>0.006092903204262257</v>
+        <v>0.08170740306377411</v>
       </c>
       <c r="AJ12" t="n">
-        <v>0.01326570939272642</v>
+        <v>0.01074908673763275</v>
       </c>
       <c r="AK12" t="n">
-        <v>0.01914049498736858</v>
+        <v>0.04721982777118683</v>
       </c>
       <c r="AL12" t="n">
-        <v>0.02182694338262081</v>
+        <v>0.1942110061645508</v>
       </c>
       <c r="AM12" t="n">
-        <v>0.001671913778409362</v>
+        <v>0.001879371702671051</v>
       </c>
       <c r="AN12" t="n">
-        <v>0.01900767721235752</v>
+        <v>0.04604214802384377</v>
       </c>
       <c r="AO12" t="n">
-        <v>0.01251301076263189</v>
+        <v>0.04977799579501152</v>
       </c>
       <c r="AP12" t="n">
-        <v>0.008456332609057426</v>
+        <v>0.05672755837440491</v>
       </c>
       <c r="AQ12" t="n">
-        <v>0.01308383792638779</v>
+        <v>0.08412443101406097</v>
       </c>
       <c r="AR12" t="n">
-        <v>0.002919259946793318</v>
+        <v>0.04315507784485817</v>
       </c>
       <c r="AS12" t="n">
-        <v>0.00839031208306551</v>
+        <v>0.1045171394944191</v>
       </c>
       <c r="AT12" t="n">
-        <v>0.0532643049955368</v>
+        <v>0.1671876609325409</v>
       </c>
       <c r="AU12" t="n">
-        <v>0.164337232708931</v>
+        <v>0.3156302273273468</v>
       </c>
       <c r="AV12" t="n">
-        <v>0.00225400528870523</v>
+        <v>0.005410350859165192</v>
       </c>
       <c r="AW12" t="n">
-        <v>0.04455635696649551</v>
+        <v>0.1639752984046936</v>
       </c>
       <c r="AX12" t="n">
-        <v>0.006204023957252502</v>
+        <v>0.005809618160128593</v>
       </c>
       <c r="AY12" t="n">
-        <v>0.02245635539293289</v>
+        <v>0.02541014924645424</v>
       </c>
       <c r="AZ12" t="n">
-        <v>0.01970934495329857</v>
+        <v>0.006964883767068386</v>
       </c>
       <c r="BA12" t="n">
-        <v>0.02118249610066414</v>
+        <v>0.1034438535571098</v>
       </c>
       <c r="BB12" t="n">
-        <v>0.01111755333840847</v>
+        <v>0.0003353887004777789</v>
       </c>
       <c r="BC12" t="n">
-        <v>0.01218937896192074</v>
+        <v>0.05090180784463882</v>
       </c>
       <c r="BD12" t="n">
-        <v>0.03364145383238792</v>
+        <v>0.2252850234508514</v>
       </c>
       <c r="BE12" t="n">
-        <v>0.05160082876682281</v>
+        <v>0.02483387291431427</v>
       </c>
       <c r="BF12" t="n">
-        <v>0.04987596720457077</v>
+        <v>0.0001404136419296265</v>
       </c>
       <c r="BG12" t="n">
-        <v>0.04837446659803391</v>
+        <v>0.2490005344152451</v>
       </c>
       <c r="BH12" t="n">
-        <v>0.0242401547729969</v>
+        <v>0.0764341726899147</v>
       </c>
       <c r="BI12" t="n">
-        <v>0.03591326251626015</v>
+        <v>0.07374769449234009</v>
       </c>
       <c r="BJ12" t="n">
-        <v>0.03820523619651794</v>
+        <v>0.1610632687807083</v>
       </c>
       <c r="BK12" t="n">
-        <v>0.008311700075864792</v>
+        <v>0.1153317391872406</v>
       </c>
       <c r="BL12" t="n">
-        <v>0.007115978747606277</v>
+        <v>0.03027480840682983</v>
       </c>
       <c r="BM12" t="n">
-        <v>0.05350257456302643</v>
+        <v>0.002397118136286736</v>
       </c>
       <c r="BN12" t="n">
-        <v>0.030536949634552</v>
+        <v>0.05201342329382896</v>
       </c>
       <c r="BO12" t="n">
-        <v>0.01631874404847622</v>
+        <v>0.02538718469440937</v>
       </c>
       <c r="BP12" t="n">
-        <v>0.07481617480516434</v>
+        <v>0.07190743833780289</v>
       </c>
       <c r="BQ12" t="n">
-        <v>0.02146260440349579</v>
+        <v>0.1820655018091202</v>
       </c>
       <c r="BR12" t="n">
-        <v>0.01375014614313841</v>
+        <v>0.05472761765122414</v>
       </c>
       <c r="BS12" t="n">
-        <v>0.01683715544641018</v>
+        <v>0.05805905908346176</v>
       </c>
       <c r="BT12" t="n">
-        <v>0.007780516520142555</v>
+        <v>0.03892071917653084</v>
       </c>
       <c r="BU12" t="n">
-        <v>0.02374518476426601</v>
+        <v>0.1307632774114609</v>
       </c>
       <c r="BV12" t="n">
-        <v>0.07433941215276718</v>
+        <v>0.2064920961856842</v>
       </c>
       <c r="BW12" t="n">
-        <v>0.02721691131591797</v>
+        <v>0.05213841795921326</v>
       </c>
       <c r="BX12" t="n">
-        <v>0.02148628234863281</v>
+        <v>0.005479611456394196</v>
       </c>
       <c r="BY12" t="n">
-        <v>0.000616749282926321</v>
+        <v>0.04203407466411591</v>
       </c>
       <c r="BZ12" t="n">
-        <v>0.0224734079092741</v>
+        <v>0.0768100693821907</v>
       </c>
       <c r="CA12" t="n">
-        <v>0.008797557093203068</v>
+        <v>0.005291684065014124</v>
       </c>
       <c r="CB12" t="n">
-        <v>0.0236943457275629</v>
+        <v>0.1102924272418022</v>
       </c>
       <c r="CC12" t="n">
-        <v>0.01240174099802971</v>
+        <v>0.02784476988017559</v>
       </c>
       <c r="CD12" t="n">
-        <v>0.006138302385807037</v>
+        <v>0.005665412172675133</v>
       </c>
       <c r="CE12" t="n">
-        <v>0.03734462708234787</v>
+        <v>0.03868352621793747</v>
       </c>
       <c r="CF12" t="n">
-        <v>0.01602564565837383</v>
+        <v>0.005497399717569351</v>
       </c>
       <c r="CG12" t="n">
-        <v>0.02047174423933029</v>
+        <v>0.05516249686479568</v>
       </c>
       <c r="CH12" t="n">
-        <v>0.003118960419669747</v>
+        <v>0.029716731980443</v>
       </c>
       <c r="CI12" t="n">
-        <v>0.009752776473760605</v>
+        <v>0.097272127866745</v>
       </c>
       <c r="CJ12" t="n">
-        <v>0.01482559181749821</v>
+        <v>0.03143806755542755</v>
       </c>
       <c r="CK12" t="n">
-        <v>0.004124489612877369</v>
+        <v>0.02785496786236763</v>
       </c>
       <c r="CL12" t="n">
-        <v>0.01015758886933327</v>
+        <v>0.01999547518789768</v>
       </c>
       <c r="CM12" t="n">
-        <v>0.04432275891304016</v>
+        <v>0.01866134628653526</v>
       </c>
       <c r="CN12" t="n">
-        <v>0.05903714895248413</v>
+        <v>0.04161688312888145</v>
       </c>
       <c r="CO12" t="n">
-        <v>0.00621985225006938</v>
+        <v>0.05547364056110382</v>
       </c>
       <c r="CP12" t="n">
-        <v>0.0002233628183603287</v>
+        <v>0.0699579268693924</v>
       </c>
       <c r="CQ12" t="n">
-        <v>0.0361078754067421</v>
+        <v>0.2215415686368942</v>
       </c>
       <c r="CR12" t="n">
-        <v>0.02096855826675892</v>
+        <v>0.01707781665027142</v>
       </c>
       <c r="CS12" t="n">
-        <v>0.000352892093360424</v>
+        <v>0.1379721313714981</v>
       </c>
       <c r="CT12" t="n">
-        <v>0.01099222805351019</v>
+        <v>0.06655404716730118</v>
       </c>
       <c r="CU12" t="n">
-        <v>0.007741023786365986</v>
+        <v>0.01994745433330536</v>
       </c>
       <c r="CV12" t="n">
-        <v>0.008853035978972912</v>
+        <v>0.00992902833968401</v>
       </c>
       <c r="CW12" t="n">
-        <v>0.02955111861228943</v>
+        <v>0.04093021899461746</v>
       </c>
       <c r="CX12" t="n">
-        <v>0.02261408232152462</v>
+        <v>0.009148022159934044</v>
       </c>
       <c r="CY12" t="n">
-        <v>0.03009816631674767</v>
+        <v>0.05905104428529739</v>
       </c>
       <c r="CZ12" t="n">
-        <v>0.001571446307934821</v>
+        <v>0.04666499421000481</v>
       </c>
       <c r="DA12" t="n">
-        <v>0.004151764325797558</v>
+        <v>0.09757187962532043</v>
       </c>
       <c r="DB12" t="n">
-        <v>0.01924166083335876</v>
+        <v>0.0326717421412468</v>
       </c>
       <c r="DC12" t="n">
-        <v>0.002053769305348396</v>
+        <v>0.02060923352837563</v>
       </c>
       <c r="DD12" t="n">
-        <v>0.007138515822589397</v>
+        <v>0.01241664681583643</v>
       </c>
       <c r="DE12" t="n">
-        <v>0.0109074953943491</v>
+        <v>0.01804933696985245</v>
       </c>
       <c r="DF12" t="n">
-        <v>0.1124329194426537</v>
+        <v>0.08918852359056473</v>
       </c>
       <c r="DG12" t="n">
-        <v>0.0214379895478487</v>
+        <v>0.1658213436603546</v>
       </c>
       <c r="DH12" t="n">
-        <v>0.04770540446043015</v>
+        <v>0.1111874133348465</v>
       </c>
       <c r="DI12" t="n">
-        <v>0.04380932077765465</v>
+        <v>0.01011876203119755</v>
       </c>
       <c r="DJ12" t="n">
-        <v>0.0100316759198904</v>
+        <v>0.04404794052243233</v>
       </c>
       <c r="DK12" t="n">
-        <v>0.0365857258439064</v>
+        <v>0.02655724063515663</v>
       </c>
       <c r="DL12" t="n">
-        <v>0.01055251434445381</v>
+        <v>0.1071893945336342</v>
       </c>
       <c r="DM12" t="n">
-        <v>0.02739844471216202</v>
+        <v>0.01578838378190994</v>
       </c>
       <c r="DN12" t="n">
-        <v>0.004352197982370853</v>
+        <v>0.01525038853287697</v>
       </c>
       <c r="DO12" t="n">
-        <v>0.02229442074894905</v>
+        <v>0.008479579351842403</v>
       </c>
       <c r="DP12" t="n">
-        <v>0.02437069453299046</v>
+        <v>0.05817843601107597</v>
       </c>
       <c r="DQ12" t="n">
-        <v>0.01346274651587009</v>
+        <v>0.1486160159111023</v>
       </c>
       <c r="DR12" t="n">
-        <v>0.01346653141081333</v>
+        <v>0.117215022444725</v>
       </c>
       <c r="DS12" t="n">
-        <v>0.003007953055202961</v>
+        <v>0.1369598656892776</v>
       </c>
       <c r="DT12" t="n">
-        <v>0.00873944628983736</v>
+        <v>0.0856742337346077</v>
       </c>
       <c r="DU12" t="n">
-        <v>0.002528009936213493</v>
+        <v>0.04710580408573151</v>
       </c>
       <c r="DV12" t="n">
-        <v>0.01069669425487518</v>
+        <v>0.0230146087706089</v>
       </c>
       <c r="DW12" t="n">
-        <v>0.007051223888993263</v>
+        <v>0.03703974187374115</v>
       </c>
       <c r="DX12" t="n">
-        <v>0.0232523363083601</v>
+        <v>0.03173743933439255</v>
       </c>
       <c r="DY12" t="n">
-        <v>0.008176561444997787</v>
+        <v>0.1292451322078705</v>
       </c>
       <c r="DZ12" t="n">
-        <v>0.02775929123163223</v>
+        <v>0.01904100179672241</v>
       </c>
       <c r="EA12" t="n">
-        <v>0.01716288179159164</v>
+        <v>0.08023165911436081</v>
       </c>
       <c r="EB12" t="n">
-        <v>0.00657057948410511</v>
+        <v>0.06711848825216293</v>
       </c>
       <c r="EC12" t="n">
-        <v>0.006841639056801796</v>
+        <v>0.0327555388212204</v>
       </c>
       <c r="ED12" t="n">
-        <v>0.02243871428072453</v>
+        <v>0.08900407701730728</v>
       </c>
       <c r="EE12" t="n">
-        <v>0.006937999278306961</v>
+        <v>0.04923143982887268</v>
       </c>
       <c r="EF12" t="n">
-        <v>0.01645047031342983</v>
+        <v>0.01522617973387241</v>
       </c>
       <c r="EG12" t="n">
-        <v>0.006432628259062767</v>
+        <v>0.04800380766391754</v>
       </c>
       <c r="EH12" t="n">
-        <v>0.01246527023613453</v>
+        <v>0.01541044190526009</v>
       </c>
       <c r="EI12" t="n">
-        <v>0.02562850527465343</v>
+        <v>0.1158249527215958</v>
       </c>
       <c r="EJ12" t="n">
-        <v>0.0009617595933377743</v>
+        <v>0.01976234093308449</v>
       </c>
       <c r="EK12" t="n">
-        <v>0.009307783097028732</v>
+        <v>0.0477975457906723</v>
       </c>
       <c r="EL12" t="n">
-        <v>0.0182349868118763</v>
+        <v>0.004530712962150574</v>
       </c>
       <c r="EM12" t="n">
-        <v>0.01523933745920658</v>
+        <v>0.02657649293541908</v>
       </c>
       <c r="EN12" t="n">
-        <v>0.003979125060141087</v>
+        <v>0.009287131018936634</v>
       </c>
       <c r="EO12" t="n">
-        <v>0.02333500981330872</v>
+        <v>0.09405428916215897</v>
       </c>
       <c r="EP12" t="n">
-        <v>0.0120912529528141</v>
+        <v>0.01481149531900883</v>
       </c>
       <c r="EQ12" t="n">
-        <v>0.03127643838524818</v>
+        <v>0.01191231608390808</v>
       </c>
       <c r="ER12" t="n">
-        <v>0.02167622372508049</v>
+        <v>0.05339881405234337</v>
       </c>
       <c r="ES12" t="n">
-        <v>0.009919458068907261</v>
+        <v>0.01505006104707718</v>
       </c>
       <c r="ET12" t="n">
-        <v>0.02452770993113518</v>
+        <v>0.02511154115200043</v>
       </c>
       <c r="EU12" t="n">
-        <v>0.01770530454814434</v>
+        <v>0.01344773545861244</v>
       </c>
       <c r="EV12" t="n">
-        <v>0.01740151830017567</v>
+        <v>0.05825892090797424</v>
       </c>
       <c r="EW12" t="n">
-        <v>0.005274505354464054</v>
+        <v>0.04464262723922729</v>
       </c>
       <c r="EX12" t="n">
-        <v>0.008473388850688934</v>
+        <v>0.01219912990927696</v>
       </c>
       <c r="EY12" t="n">
-        <v>0.02834833785891533</v>
+        <v>0.03621971234679222</v>
       </c>
       <c r="EZ12" t="n">
-        <v>0.01686108112335205</v>
+        <v>0.02203463390469551</v>
       </c>
       <c r="FA12" t="n">
-        <v>0.02208025939762592</v>
+        <v>0.07973722368478775</v>
       </c>
       <c r="FB12" t="n">
-        <v>0.003415034152567387</v>
+        <v>0.02486132271587849</v>
       </c>
       <c r="FC12" t="n">
-        <v>0.009677832014858723</v>
+        <v>0.05226775258779526</v>
       </c>
       <c r="FD12" t="n">
-        <v>0.02164895832538605</v>
+        <v>0.02584567107260227</v>
       </c>
       <c r="FE12" t="n">
-        <v>0.006756789982318878</v>
+        <v>0.0008634577970951796</v>
       </c>
       <c r="FF12" t="n">
-        <v>0.01126377657055855</v>
+        <v>0.02417352050542831</v>
       </c>
       <c r="FG12" t="n">
-        <v>0.02330981940031052</v>
+        <v>0.1620859801769257</v>
       </c>
       <c r="FH12" t="n">
-        <v>0.01132793910801411</v>
+        <v>0.06855565309524536</v>
       </c>
       <c r="FI12" t="n">
-        <v>0.01233889069408178</v>
+        <v>0.01546116545796394</v>
       </c>
       <c r="FJ12" t="n">
-        <v>0.01942241378128529</v>
+        <v>0.07029977440834045</v>
       </c>
       <c r="FK12" t="n">
-        <v>0.02283333986997604</v>
+        <v>0.04959641396999359</v>
       </c>
       <c r="FL12" t="n">
-        <v>0.00998139102011919</v>
+        <v>0.02842272445559502</v>
       </c>
       <c r="FM12" t="n">
-        <v>0.006204920820891857</v>
+        <v>0.03580297529697418</v>
       </c>
       <c r="FN12" t="n">
-        <v>0.008298092521727085</v>
+        <v>0.01363660302013159</v>
       </c>
       <c r="FO12" t="n">
-        <v>0.003195999190211296</v>
+        <v>0.08593448996543884</v>
       </c>
       <c r="FP12" t="n">
-        <v>0.01160953566431999</v>
+        <v>0.03038322180509567</v>
       </c>
       <c r="FQ12" t="n">
-        <v>0.02039339207112789</v>
+        <v>0.2817029356956482</v>
       </c>
       <c r="FR12" t="n">
-        <v>0.02272485941648483</v>
+        <v>0.1466065645217896</v>
       </c>
       <c r="FS12" t="n">
-        <v>0.02642624825239182</v>
+        <v>0.06194548681378365</v>
       </c>
       <c r="FT12" t="n">
-        <v>0.041158277541399</v>
+        <v>0.1340870261192322</v>
       </c>
       <c r="FU12" t="n">
-        <v>0.0123477578163147</v>
+        <v>0.2820918262004852</v>
       </c>
       <c r="FV12" t="n">
-        <v>0.04257439821958542</v>
+        <v>0.1368153989315033</v>
       </c>
       <c r="FW12" t="n">
-        <v>0.027730917558074</v>
+        <v>0.06048613786697388</v>
       </c>
       <c r="FX12" t="n">
-        <v>0.009275059215724468</v>
+        <v>0.09677351266145706</v>
       </c>
       <c r="FY12" t="n">
-        <v>0.02950294502079487</v>
+        <v>0.01190911792218685</v>
       </c>
       <c r="FZ12" t="n">
-        <v>0.02626432850956917</v>
+        <v>0.08227700740098953</v>
       </c>
       <c r="GA12" t="n">
-        <v>0.006773952394723892</v>
+        <v>0.0005563497543334961</v>
       </c>
       <c r="GB12" t="n">
-        <v>0.0275212824344635</v>
+        <v>0.08359633386135101</v>
       </c>
       <c r="GC12" t="n">
-        <v>0.008827678859233856</v>
+        <v>0.06378104537725449</v>
       </c>
       <c r="GD12" t="n">
-        <v>0.01373769156634808</v>
+        <v>0.03438837826251984</v>
       </c>
       <c r="GE12" t="n">
-        <v>0.04025114700198174</v>
+        <v>0.09720576554536819</v>
       </c>
       <c r="GF12" t="n">
-        <v>0.03052072040736675</v>
+        <v>0.05252422764897346</v>
       </c>
       <c r="GG12" t="n">
-        <v>0.01659888215363026</v>
+        <v>0.03083617426455021</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>0.008676064200699329</v>
+        <v>0.1345063447952271</v>
       </c>
       <c r="B13" t="n">
-        <v>0.04958638548851013</v>
+        <v>0.8164229393005371</v>
       </c>
       <c r="C13" t="n">
-        <v>0.008834203705191612</v>
+        <v>0.1382916420698166</v>
       </c>
       <c r="D13" t="n">
-        <v>0.01301433611661196</v>
+        <v>0.1746516227722168</v>
       </c>
       <c r="E13" t="n">
-        <v>0.01054393500089645</v>
+        <v>0.7314703464508057</v>
       </c>
       <c r="F13" t="n">
-        <v>0.006623279303312302</v>
+        <v>0.7408394813537598</v>
       </c>
       <c r="G13" t="n">
-        <v>0.003487671259790659</v>
+        <v>0.3115389049053192</v>
       </c>
       <c r="H13" t="n">
-        <v>0.0002708961255848408</v>
+        <v>0.2070877403020859</v>
       </c>
       <c r="I13" t="n">
-        <v>0.02329428121447563</v>
+        <v>0.203955203294754</v>
       </c>
       <c r="J13" t="n">
-        <v>0.009547888301312923</v>
+        <v>0.3428571224212646</v>
       </c>
       <c r="K13" t="n">
-        <v>0.03771455958485603</v>
+        <v>1.168225288391113</v>
       </c>
       <c r="L13" t="n">
-        <v>0.002359800739213824</v>
+        <v>0.2764265239238739</v>
       </c>
       <c r="M13" t="n">
-        <v>0.01635487377643585</v>
+        <v>0.1157747358083725</v>
       </c>
       <c r="N13" t="n">
-        <v>0.01960704103112221</v>
+        <v>0.9956402182579041</v>
       </c>
       <c r="O13" t="n">
-        <v>0.01220927387475967</v>
+        <v>0.7976300120353699</v>
       </c>
       <c r="P13" t="n">
-        <v>0.006894475314766169</v>
+        <v>0.1676781624555588</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.008400885388255119</v>
+        <v>0.315623939037323</v>
       </c>
       <c r="R13" t="n">
-        <v>0.01524210441857576</v>
+        <v>0.2935907244682312</v>
       </c>
       <c r="S13" t="n">
-        <v>0.0005399186047725379</v>
+        <v>0.1288398802280426</v>
       </c>
       <c r="T13" t="n">
-        <v>0.01216866914182901</v>
+        <v>0.2500561773777008</v>
       </c>
       <c r="U13" t="n">
-        <v>0.005326594226062298</v>
+        <v>0.03657560050487518</v>
       </c>
       <c r="V13" t="n">
-        <v>0.006427286192774773</v>
+        <v>0.2355343699455261</v>
       </c>
       <c r="W13" t="n">
-        <v>0.001721352804452181</v>
+        <v>0.0327276922762394</v>
       </c>
       <c r="X13" t="n">
-        <v>0.007816656492650509</v>
+        <v>0.1632111221551895</v>
       </c>
       <c r="Y13" t="n">
-        <v>0.002615335397422314</v>
+        <v>0.01951855979859829</v>
       </c>
       <c r="Z13" t="n">
-        <v>0.0003963869530707598</v>
+        <v>0.1479780972003937</v>
       </c>
       <c r="AA13" t="n">
-        <v>0.004826529417186975</v>
+        <v>0.1264539957046509</v>
       </c>
       <c r="AB13" t="n">
-        <v>0.005152301862835884</v>
+        <v>0.1882027387619019</v>
       </c>
       <c r="AC13" t="n">
-        <v>0.01025805529206991</v>
+        <v>0.03058443963527679</v>
       </c>
       <c r="AD13" t="n">
-        <v>0.003584008431062102</v>
+        <v>0.2701973915100098</v>
       </c>
       <c r="AE13" t="n">
-        <v>0.006669943686574697</v>
+        <v>0.1436704993247986</v>
       </c>
       <c r="AF13" t="n">
-        <v>0.0003553852438926697</v>
+        <v>0.2212673872709274</v>
       </c>
       <c r="AG13" t="n">
-        <v>0.004499354399740696</v>
+        <v>0.3333984911441803</v>
       </c>
       <c r="AH13" t="n">
-        <v>0.004373177886009216</v>
+        <v>0.2247237861156464</v>
       </c>
       <c r="AI13" t="n">
-        <v>0.008273818530142307</v>
+        <v>0.3306092321872711</v>
       </c>
       <c r="AJ13" t="n">
-        <v>0.001990548567846417</v>
+        <v>0.04676377773284912</v>
       </c>
       <c r="AK13" t="n">
-        <v>0.008657385595142841</v>
+        <v>0.2310621440410614</v>
       </c>
       <c r="AL13" t="n">
-        <v>0.004169071093201637</v>
+        <v>0.4566195905208588</v>
       </c>
       <c r="AM13" t="n">
-        <v>0.002106253756210208</v>
+        <v>0.001041576266288757</v>
       </c>
       <c r="AN13" t="n">
-        <v>0.0006198503542691469</v>
+        <v>0.06483951210975647</v>
       </c>
       <c r="AO13" t="n">
-        <v>0.007054601795971394</v>
+        <v>0.3084823489189148</v>
       </c>
       <c r="AP13" t="n">
-        <v>0.004441935569047928</v>
+        <v>0.09497903287410736</v>
       </c>
       <c r="AQ13" t="n">
-        <v>0.005416220054030418</v>
+        <v>0.03562399744987488</v>
       </c>
       <c r="AR13" t="n">
-        <v>0.002965324558317661</v>
+        <v>0.2593701481819153</v>
       </c>
       <c r="AS13" t="n">
-        <v>0.002599492436274886</v>
+        <v>0.07125359028577805</v>
       </c>
       <c r="AT13" t="n">
-        <v>0.003724593669176102</v>
+        <v>0.3622227609157562</v>
       </c>
       <c r="AU13" t="n">
-        <v>0.0408700592815876</v>
+        <v>1.551352620124817</v>
       </c>
       <c r="AV13" t="n">
-        <v>0.001882073003798723</v>
+        <v>0.1245900988578796</v>
       </c>
       <c r="AW13" t="n">
-        <v>0.001090344041585922</v>
+        <v>0.1266666203737259</v>
       </c>
       <c r="AX13" t="n">
-        <v>0.004536909516900778</v>
+        <v>0.2852203249931335</v>
       </c>
       <c r="AY13" t="n">
-        <v>0.002264587674289942</v>
+        <v>0.3975745439529419</v>
       </c>
       <c r="AZ13" t="n">
-        <v>0.004840201232582331</v>
+        <v>0.1000944748520851</v>
       </c>
       <c r="BA13" t="n">
-        <v>0.0009483827743679285</v>
+        <v>0.0768195316195488</v>
       </c>
       <c r="BB13" t="n">
-        <v>0.007148376200348139</v>
+        <v>0.1330519467592239</v>
       </c>
       <c r="BC13" t="n">
-        <v>0.0004730148939415812</v>
+        <v>0.2059061527252197</v>
       </c>
       <c r="BD13" t="n">
-        <v>0.01375743094831705</v>
+        <v>0.4460189938545227</v>
       </c>
       <c r="BE13" t="n">
-        <v>0.009716911241412163</v>
+        <v>0.1857019513845444</v>
       </c>
       <c r="BF13" t="n">
-        <v>0.0004804420750588179</v>
+        <v>0.3319895267486572</v>
       </c>
       <c r="BG13" t="n">
-        <v>0.01542109251022339</v>
+        <v>0.7106130719184875</v>
       </c>
       <c r="BH13" t="n">
-        <v>0.01174703240394592</v>
+        <v>0.1068241074681282</v>
       </c>
       <c r="BI13" t="n">
-        <v>0.003202307969331741</v>
+        <v>0.02782563120126724</v>
       </c>
       <c r="BJ13" t="n">
-        <v>0.009393231943249702</v>
+        <v>0.05701576173305511</v>
       </c>
       <c r="BK13" t="n">
-        <v>0.008833847939968109</v>
+        <v>0.08424441516399384</v>
       </c>
       <c r="BL13" t="n">
-        <v>0.005812732502818108</v>
+        <v>0.05008244514465332</v>
       </c>
       <c r="BM13" t="n">
-        <v>0.01466188859194517</v>
+        <v>0.2070488333702087</v>
       </c>
       <c r="BN13" t="n">
-        <v>0.00496769743040204</v>
+        <v>0.09092146903276443</v>
       </c>
       <c r="BO13" t="n">
-        <v>0.003044697223231196</v>
+        <v>0.05666891112923622</v>
       </c>
       <c r="BP13" t="n">
-        <v>0.02632438018918037</v>
+        <v>0.493706613779068</v>
       </c>
       <c r="BQ13" t="n">
-        <v>0.008861000649631023</v>
+        <v>0.3938592076301575</v>
       </c>
       <c r="BR13" t="n">
-        <v>0.001288044964894652</v>
+        <v>0.4306043088436127</v>
       </c>
       <c r="BS13" t="n">
-        <v>0.007102520205080509</v>
+        <v>0.1502172499895096</v>
       </c>
       <c r="BT13" t="n">
-        <v>0.001535851275548339</v>
+        <v>0.02155390940606594</v>
       </c>
       <c r="BU13" t="n">
-        <v>8.66224872879684e-05</v>
+        <v>0.3079985976219177</v>
       </c>
       <c r="BV13" t="n">
-        <v>0.02187457494437695</v>
+        <v>0.993224561214447</v>
       </c>
       <c r="BW13" t="n">
-        <v>0.006835273001343012</v>
+        <v>0.1605329513549805</v>
       </c>
       <c r="BX13" t="n">
-        <v>0.003887441474944353</v>
+        <v>0.4298484325408936</v>
       </c>
       <c r="BY13" t="n">
-        <v>0.002925107721239328</v>
+        <v>0.01069366093724966</v>
       </c>
       <c r="BZ13" t="n">
-        <v>0.008847400546073914</v>
+        <v>0.1281894743442535</v>
       </c>
       <c r="CA13" t="n">
-        <v>0.007921113632619381</v>
+        <v>0.04689294099807739</v>
       </c>
       <c r="CB13" t="n">
-        <v>0.001111075980588794</v>
+        <v>0.06145381927490234</v>
       </c>
       <c r="CC13" t="n">
-        <v>0.005923517979681492</v>
+        <v>0.2000187188386917</v>
       </c>
       <c r="CD13" t="n">
-        <v>0.000977948191575706</v>
+        <v>0.1132100224494934</v>
       </c>
       <c r="CE13" t="n">
-        <v>0.01043812651187181</v>
+        <v>0.3931438326835632</v>
       </c>
       <c r="CF13" t="n">
-        <v>0.0008294368162751198</v>
+        <v>0.003457469865679741</v>
       </c>
       <c r="CG13" t="n">
-        <v>0.003000666387379169</v>
+        <v>0.01046524476259947</v>
       </c>
       <c r="CH13" t="n">
-        <v>0.001546519692055881</v>
+        <v>0.0847739577293396</v>
       </c>
       <c r="CI13" t="n">
-        <v>0.000460771145299077</v>
+        <v>0.1954606771469116</v>
       </c>
       <c r="CJ13" t="n">
-        <v>0.0002544490853324533</v>
+        <v>0.1526163965463638</v>
       </c>
       <c r="CK13" t="n">
-        <v>0.001793769421055913</v>
+        <v>0.0617847628891468</v>
       </c>
       <c r="CL13" t="n">
-        <v>0.006271248683333397</v>
+        <v>0.04823438823223114</v>
       </c>
       <c r="CM13" t="n">
-        <v>0.01681257784366608</v>
+        <v>0.06224687397480011</v>
       </c>
       <c r="CN13" t="n">
-        <v>0.02126665413379669</v>
+        <v>0.9693200588226318</v>
       </c>
       <c r="CO13" t="n">
-        <v>0.001173389260657132</v>
+        <v>0.2064522802829742</v>
       </c>
       <c r="CP13" t="n">
-        <v>0.006446820683777332</v>
+        <v>0.2560314536094666</v>
       </c>
       <c r="CQ13" t="n">
-        <v>0.01196786295622587</v>
+        <v>0.02719378843903542</v>
       </c>
       <c r="CR13" t="n">
-        <v>0.002593519864603877</v>
+        <v>0.2933513522148132</v>
       </c>
       <c r="CS13" t="n">
-        <v>0.003169927047565579</v>
+        <v>0.1880012452602386</v>
       </c>
       <c r="CT13" t="n">
-        <v>0.009794685989618301</v>
+        <v>0.03254938498139381</v>
       </c>
       <c r="CU13" t="n">
-        <v>0.0001825579674914479</v>
+        <v>0.03984960168600082</v>
       </c>
       <c r="CV13" t="n">
-        <v>0.001198698068037629</v>
+        <v>0.02641711011528969</v>
       </c>
       <c r="CW13" t="n">
-        <v>0.008670767769217491</v>
+        <v>0.353441059589386</v>
       </c>
       <c r="CX13" t="n">
-        <v>0.002553287195041776</v>
+        <v>0.003729648888111115</v>
       </c>
       <c r="CY13" t="n">
-        <v>0.004212602972984314</v>
+        <v>0.08747763186693192</v>
       </c>
       <c r="CZ13" t="n">
-        <v>0.0007159791421145201</v>
+        <v>0.09291300922632217</v>
       </c>
       <c r="DA13" t="n">
-        <v>0.001407136209309101</v>
+        <v>0.1974196285009384</v>
       </c>
       <c r="DB13" t="n">
-        <v>0.0004336016718298197</v>
+        <v>0.06187811493873596</v>
       </c>
       <c r="DC13" t="n">
-        <v>0.0003941272152587771</v>
+        <v>0.08628683537244797</v>
       </c>
       <c r="DD13" t="n">
-        <v>0.004356352146714926</v>
+        <v>0.05020519345998764</v>
       </c>
       <c r="DE13" t="n">
-        <v>0.009467655792832375</v>
+        <v>0.1496320068836212</v>
       </c>
       <c r="DF13" t="n">
-        <v>0.02772348187863827</v>
+        <v>0.6636837124824524</v>
       </c>
       <c r="DG13" t="n">
-        <v>0.005326599813997746</v>
+        <v>0.04096601530909538</v>
       </c>
       <c r="DH13" t="n">
-        <v>0.01424068119376898</v>
+        <v>0.2340296804904938</v>
       </c>
       <c r="DI13" t="n">
-        <v>0.002718928270041943</v>
+        <v>0.08955037593841553</v>
       </c>
       <c r="DJ13" t="n">
-        <v>0.00398374255746603</v>
+        <v>0.05946635454893112</v>
       </c>
       <c r="DK13" t="n">
-        <v>0.01729079708456993</v>
+        <v>0.2731750905513763</v>
       </c>
       <c r="DL13" t="n">
-        <v>0.005638336297124624</v>
+        <v>0.3410999774932861</v>
       </c>
       <c r="DM13" t="n">
-        <v>0.005465734750032425</v>
+        <v>0.09877479076385498</v>
       </c>
       <c r="DN13" t="n">
-        <v>0.004344390705227852</v>
+        <v>0.04728235304355621</v>
       </c>
       <c r="DO13" t="n">
-        <v>0.009323400445282459</v>
+        <v>0.1295511424541473</v>
       </c>
       <c r="DP13" t="n">
-        <v>0.006548841018229723</v>
+        <v>0.17006716132164</v>
       </c>
       <c r="DQ13" t="n">
-        <v>0.002981986850500107</v>
+        <v>0.238625779747963</v>
       </c>
       <c r="DR13" t="n">
-        <v>0.001196700264699757</v>
+        <v>0.3264626860618591</v>
       </c>
       <c r="DS13" t="n">
-        <v>0.0002957244869321585</v>
+        <v>0.03478351980447769</v>
       </c>
       <c r="DT13" t="n">
-        <v>0.011296640150249</v>
+        <v>0.08073456585407257</v>
       </c>
       <c r="DU13" t="n">
-        <v>0.001738498685881495</v>
+        <v>0.2405016273260117</v>
       </c>
       <c r="DV13" t="n">
-        <v>0.0005333541193976998</v>
+        <v>0.1752498596906662</v>
       </c>
       <c r="DW13" t="n">
-        <v>0.003053118940442801</v>
+        <v>0.08101509511470795</v>
       </c>
       <c r="DX13" t="n">
-        <v>0.004093507304787636</v>
+        <v>0.3734936714172363</v>
       </c>
       <c r="DY13" t="n">
-        <v>0.002789866644889116</v>
+        <v>0.1462711095809937</v>
       </c>
       <c r="DZ13" t="n">
-        <v>0.005514890886843204</v>
+        <v>0.0382331907749176</v>
       </c>
       <c r="EA13" t="n">
-        <v>0.004757986404001713</v>
+        <v>0.1993650645017624</v>
       </c>
       <c r="EB13" t="n">
-        <v>8.500693365931511e-05</v>
+        <v>0.3679507374763489</v>
       </c>
       <c r="EC13" t="n">
-        <v>0.003194017801433802</v>
+        <v>0.1395646631717682</v>
       </c>
       <c r="ED13" t="n">
-        <v>0.006351422518491745</v>
+        <v>0.0767984539270401</v>
       </c>
       <c r="EE13" t="n">
-        <v>0.0007985460106283426</v>
+        <v>0.1644899249076843</v>
       </c>
       <c r="EF13" t="n">
-        <v>0.002431149827316403</v>
+        <v>0.06548577547073364</v>
       </c>
       <c r="EG13" t="n">
-        <v>7.927903061499819e-05</v>
+        <v>0.03436991572380066</v>
       </c>
       <c r="EH13" t="n">
-        <v>0.0006049358053132892</v>
+        <v>0.09808515012264252</v>
       </c>
       <c r="EI13" t="n">
-        <v>0.004687369335442781</v>
+        <v>0.07802612334489822</v>
       </c>
       <c r="EJ13" t="n">
-        <v>0.001766812289133668</v>
+        <v>0.01260457560420036</v>
       </c>
       <c r="EK13" t="n">
-        <v>0.002140453550964594</v>
+        <v>0.3265533447265625</v>
       </c>
       <c r="EL13" t="n">
-        <v>0.003093896899372339</v>
+        <v>0.05894771963357925</v>
       </c>
       <c r="EM13" t="n">
-        <v>0.001373303821310401</v>
+        <v>0.08837423473596573</v>
       </c>
       <c r="EN13" t="n">
-        <v>0.006730553694069386</v>
+        <v>0.0387326218187809</v>
       </c>
       <c r="EO13" t="n">
-        <v>0.006307018455117941</v>
+        <v>0.2425727844238281</v>
       </c>
       <c r="EP13" t="n">
-        <v>0.003893093438819051</v>
+        <v>0.2951169312000275</v>
       </c>
       <c r="EQ13" t="n">
-        <v>0.003425650298595428</v>
+        <v>0.03655672445893288</v>
       </c>
       <c r="ER13" t="n">
-        <v>0.00296392641030252</v>
+        <v>0.1869465708732605</v>
       </c>
       <c r="ES13" t="n">
-        <v>0.003956046421080828</v>
+        <v>0.1177230551838875</v>
       </c>
       <c r="ET13" t="n">
-        <v>0.004257814027369022</v>
+        <v>0.1815179586410522</v>
       </c>
       <c r="EU13" t="n">
-        <v>0.003248362801969051</v>
+        <v>0.01874979585409164</v>
       </c>
       <c r="EV13" t="n">
-        <v>0.001875124522484839</v>
+        <v>0.07825027406215668</v>
       </c>
       <c r="EW13" t="n">
-        <v>0.0009619805496186018</v>
+        <v>0.101073831319809</v>
       </c>
       <c r="EX13" t="n">
-        <v>0.0005454818601720035</v>
+        <v>0.08281433582305908</v>
       </c>
       <c r="EY13" t="n">
-        <v>0.009065860882401466</v>
+        <v>0.4477978348731995</v>
       </c>
       <c r="EZ13" t="n">
-        <v>0.001122629619203508</v>
+        <v>0.02288113161921501</v>
       </c>
       <c r="FA13" t="n">
-        <v>0.002848917152732611</v>
+        <v>0.06590740382671356</v>
       </c>
       <c r="FB13" t="n">
-        <v>0.0004438519827090204</v>
+        <v>0.06991139054298401</v>
       </c>
       <c r="FC13" t="n">
-        <v>0.002705453429371119</v>
+        <v>0.1805534362792969</v>
       </c>
       <c r="FD13" t="n">
-        <v>0.0007481009233742952</v>
+        <v>0.1530807316303253</v>
       </c>
       <c r="FE13" t="n">
-        <v>0.002871013712137938</v>
+        <v>0.02388821542263031</v>
       </c>
       <c r="FF13" t="n">
-        <v>0.004200192168354988</v>
+        <v>0.08382608741521835</v>
       </c>
       <c r="FG13" t="n">
-        <v>0.004219247493892908</v>
+        <v>0.1394019573926926</v>
       </c>
       <c r="FH13" t="n">
-        <v>0.003422933397814631</v>
+        <v>0.2199984937906265</v>
       </c>
       <c r="FI13" t="n">
-        <v>0.001259922748431563</v>
+        <v>0.09789624810218811</v>
       </c>
       <c r="FJ13" t="n">
-        <v>0.003748645540326834</v>
+        <v>0.3297430872917175</v>
       </c>
       <c r="FK13" t="n">
-        <v>0.003996919374912977</v>
+        <v>0.1738463938236237</v>
       </c>
       <c r="FL13" t="n">
-        <v>0.001266135135665536</v>
+        <v>0.1783358007669449</v>
       </c>
       <c r="FM13" t="n">
-        <v>0.002284979214891791</v>
+        <v>0.09351183474063873</v>
       </c>
       <c r="FN13" t="n">
-        <v>0.003222991013899446</v>
+        <v>0.2598384320735931</v>
       </c>
       <c r="FO13" t="n">
-        <v>0.005049631930887699</v>
+        <v>0.1330447196960449</v>
       </c>
       <c r="FP13" t="n">
-        <v>0.004393718205392361</v>
+        <v>0.06429434567689896</v>
       </c>
       <c r="FQ13" t="n">
-        <v>0.0008999277488328516</v>
+        <v>0.09507174789905548</v>
       </c>
       <c r="FR13" t="n">
-        <v>0.001419591018930078</v>
+        <v>0.03377158939838409</v>
       </c>
       <c r="FS13" t="n">
-        <v>0.006377632729709148</v>
+        <v>0.1837765276432037</v>
       </c>
       <c r="FT13" t="n">
-        <v>0.01173891872167587</v>
+        <v>0.4516043066978455</v>
       </c>
       <c r="FU13" t="n">
-        <v>0.004103054292500019</v>
+        <v>0.1652038246393204</v>
       </c>
       <c r="FV13" t="n">
-        <v>0.001196963246911764</v>
+        <v>0.00320814922451973</v>
       </c>
       <c r="FW13" t="n">
-        <v>0.004270284436643124</v>
+        <v>0.2445404380559921</v>
       </c>
       <c r="FX13" t="n">
-        <v>0.004263289738446474</v>
+        <v>0.06910524517297745</v>
       </c>
       <c r="FY13" t="n">
-        <v>0.004475581459701061</v>
+        <v>0.2672756016254425</v>
       </c>
       <c r="FZ13" t="n">
-        <v>0.01249432191252708</v>
+        <v>0.1771261096000671</v>
       </c>
       <c r="GA13" t="n">
-        <v>0.006000615190714598</v>
+        <v>0.02982485666871071</v>
       </c>
       <c r="GB13" t="n">
-        <v>0.0116137657314539</v>
+        <v>0.1796163022518158</v>
       </c>
       <c r="GC13" t="n">
-        <v>0.005612440872937441</v>
+        <v>0.02505805157124996</v>
       </c>
       <c r="GD13" t="n">
-        <v>0.01194204483181238</v>
+        <v>0.2186775505542755</v>
       </c>
       <c r="GE13" t="n">
-        <v>0.006712649017572403</v>
+        <v>0.01577457040548325</v>
       </c>
       <c r="GF13" t="n">
-        <v>0.004627580288797617</v>
+        <v>0.3078018426895142</v>
       </c>
       <c r="GG13" t="n">
-        <v>0.001105137984268367</v>
+        <v>0.1306850761175156</v>
       </c>
     </row>
     <row r="14">
@@ -8396,571 +8396,571 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>0.03086357936263084</v>
+        <v>0.2036539316177368</v>
       </c>
       <c r="B15" t="n">
-        <v>0.114047572016716</v>
+        <v>0.2347987145185471</v>
       </c>
       <c r="C15" t="n">
-        <v>0.06442110985517502</v>
+        <v>0.1347550004720688</v>
       </c>
       <c r="D15" t="n">
-        <v>0.04148614406585693</v>
+        <v>0.123629242181778</v>
       </c>
       <c r="E15" t="n">
-        <v>0.1307028383016586</v>
+        <v>0.174348920583725</v>
       </c>
       <c r="F15" t="n">
-        <v>0.00745226489380002</v>
+        <v>0.05356442928314209</v>
       </c>
       <c r="G15" t="n">
-        <v>0.05193254351615906</v>
+        <v>0.149842232465744</v>
       </c>
       <c r="H15" t="n">
-        <v>0.01204896811395884</v>
+        <v>0.07977581769227982</v>
       </c>
       <c r="I15" t="n">
-        <v>0.04816148802638054</v>
+        <v>0.1073619425296783</v>
       </c>
       <c r="J15" t="n">
-        <v>0.01731887087225914</v>
+        <v>0.1375328898429871</v>
       </c>
       <c r="K15" t="n">
-        <v>0.07358475774526596</v>
+        <v>0.2841877639293671</v>
       </c>
       <c r="L15" t="n">
-        <v>0.0445631667971611</v>
+        <v>0.1017646640539169</v>
       </c>
       <c r="M15" t="n">
-        <v>0.07357557117938995</v>
+        <v>0.1324748992919922</v>
       </c>
       <c r="N15" t="n">
-        <v>0.1850914806127548</v>
+        <v>0.1809527426958084</v>
       </c>
       <c r="O15" t="n">
-        <v>0.03758701682090759</v>
+        <v>0.01962399482727051</v>
       </c>
       <c r="P15" t="n">
-        <v>0.04007458686828613</v>
+        <v>0.2273961901664734</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.0176257211714983</v>
+        <v>0.07126542925834656</v>
       </c>
       <c r="R15" t="n">
-        <v>0.03817376866936684</v>
+        <v>0.147532731294632</v>
       </c>
       <c r="S15" t="n">
-        <v>0.01173283811658621</v>
+        <v>0.04328074306249619</v>
       </c>
       <c r="T15" t="n">
-        <v>0.04618693143129349</v>
+        <v>0.09351840615272522</v>
       </c>
       <c r="U15" t="n">
-        <v>0.001238381373696029</v>
+        <v>0.0750577449798584</v>
       </c>
       <c r="V15" t="n">
-        <v>0.007840230129659176</v>
+        <v>0.0428587980568409</v>
       </c>
       <c r="W15" t="n">
-        <v>0.02424610778689384</v>
+        <v>0.03297051787376404</v>
       </c>
       <c r="X15" t="n">
-        <v>0.02532139793038368</v>
+        <v>0.03900694474577904</v>
       </c>
       <c r="Y15" t="n">
-        <v>0.00167326454538852</v>
+        <v>0.02034452557563782</v>
       </c>
       <c r="Z15" t="n">
-        <v>0.0007603329140692949</v>
+        <v>0.02857016026973724</v>
       </c>
       <c r="AA15" t="n">
-        <v>0.0007537296623922884</v>
+        <v>0.04724638536572456</v>
       </c>
       <c r="AB15" t="n">
-        <v>0.01094656996428967</v>
+        <v>0.1393029391765594</v>
       </c>
       <c r="AC15" t="n">
-        <v>0.03849664330482483</v>
+        <v>0.01267934963107109</v>
       </c>
       <c r="AD15" t="n">
-        <v>0.01360661815851927</v>
+        <v>0.1167379021644592</v>
       </c>
       <c r="AE15" t="n">
-        <v>0.01348323002457619</v>
+        <v>0.1680579632520676</v>
       </c>
       <c r="AF15" t="n">
-        <v>0.0004444243386387825</v>
+        <v>0.05026735365390778</v>
       </c>
       <c r="AG15" t="n">
-        <v>0.02321104146540165</v>
+        <v>0.001319384202361107</v>
       </c>
       <c r="AH15" t="n">
-        <v>0.01723214611411095</v>
+        <v>0.03305082023143768</v>
       </c>
       <c r="AI15" t="n">
-        <v>0.02141229808330536</v>
+        <v>0.2220075875520706</v>
       </c>
       <c r="AJ15" t="n">
-        <v>0.01157069951295853</v>
+        <v>0.120562344789505</v>
       </c>
       <c r="AK15" t="n">
-        <v>0.01205131504684687</v>
+        <v>0.06341244280338287</v>
       </c>
       <c r="AL15" t="n">
-        <v>0.05885104835033417</v>
+        <v>0.1749663949012756</v>
       </c>
       <c r="AM15" t="n">
-        <v>0.002070796443149447</v>
+        <v>0.01612268574535847</v>
       </c>
       <c r="AN15" t="n">
-        <v>0.00807685125619173</v>
+        <v>0.0480518713593483</v>
       </c>
       <c r="AO15" t="n">
-        <v>0.01745809800922871</v>
+        <v>0.193728432059288</v>
       </c>
       <c r="AP15" t="n">
-        <v>0.03071001917123795</v>
+        <v>0.02423276752233505</v>
       </c>
       <c r="AQ15" t="n">
-        <v>0.01115888543426991</v>
+        <v>0.04342642799019814</v>
       </c>
       <c r="AR15" t="n">
-        <v>0.0268898569047451</v>
+        <v>0.1004145368933678</v>
       </c>
       <c r="AS15" t="n">
-        <v>0.0298554003238678</v>
+        <v>0.01768643409013748</v>
       </c>
       <c r="AT15" t="n">
-        <v>0.06025804579257965</v>
+        <v>0.0310573223978281</v>
       </c>
       <c r="AU15" t="n">
-        <v>0.1555466651916504</v>
+        <v>0.2468738555908203</v>
       </c>
       <c r="AV15" t="n">
-        <v>0.04384229704737663</v>
+        <v>0.01849778741598129</v>
       </c>
       <c r="AW15" t="n">
-        <v>0.02973180636763573</v>
+        <v>0.09458713233470917</v>
       </c>
       <c r="AX15" t="n">
-        <v>0.01797152683138847</v>
+        <v>0.07419626414775848</v>
       </c>
       <c r="AY15" t="n">
-        <v>0.01183436345309019</v>
+        <v>0.04941686615347862</v>
       </c>
       <c r="AZ15" t="n">
-        <v>0.03642283380031586</v>
+        <v>0.05087695643305779</v>
       </c>
       <c r="BA15" t="n">
-        <v>0.01526098325848579</v>
+        <v>0.08093672245740891</v>
       </c>
       <c r="BB15" t="n">
-        <v>0.03704144433140755</v>
+        <v>0.04815338924527168</v>
       </c>
       <c r="BC15" t="n">
-        <v>0.01643550395965576</v>
+        <v>0.1395020484924316</v>
       </c>
       <c r="BD15" t="n">
-        <v>0.01818846166133881</v>
+        <v>0.1305698454380035</v>
       </c>
       <c r="BE15" t="n">
-        <v>0.02783980779349804</v>
+        <v>0.1578652411699295</v>
       </c>
       <c r="BF15" t="n">
-        <v>0.04656307399272919</v>
+        <v>0.1021727472543716</v>
       </c>
       <c r="BG15" t="n">
-        <v>0.1207215860486031</v>
+        <v>0.2101549953222275</v>
       </c>
       <c r="BH15" t="n">
-        <v>0.02284256368875504</v>
+        <v>0.03227924555540085</v>
       </c>
       <c r="BI15" t="n">
-        <v>0.007765968795865774</v>
+        <v>0.06462877243757248</v>
       </c>
       <c r="BJ15" t="n">
-        <v>0.01450574677437544</v>
+        <v>0.03715041279792786</v>
       </c>
       <c r="BK15" t="n">
-        <v>0.04334212094545364</v>
+        <v>0.02869990095496178</v>
       </c>
       <c r="BL15" t="n">
-        <v>0.03967670351266861</v>
+        <v>0.01782412081956863</v>
       </c>
       <c r="BM15" t="n">
-        <v>0.04440073296427727</v>
+        <v>0.04612945765256882</v>
       </c>
       <c r="BN15" t="n">
-        <v>0.0166324470192194</v>
+        <v>0.01088233105838299</v>
       </c>
       <c r="BO15" t="n">
-        <v>0.0376100093126297</v>
+        <v>0.08340615779161453</v>
       </c>
       <c r="BP15" t="n">
-        <v>0.1171054914593697</v>
+        <v>0.07055867463350296</v>
       </c>
       <c r="BQ15" t="n">
-        <v>0.0202159695327282</v>
+        <v>0.0402752198278904</v>
       </c>
       <c r="BR15" t="n">
-        <v>0.02136712521314621</v>
+        <v>0.101682074368</v>
       </c>
       <c r="BS15" t="n">
-        <v>0.04565046727657318</v>
+        <v>0.03174145892262459</v>
       </c>
       <c r="BT15" t="n">
-        <v>0.01624114811420441</v>
+        <v>0.07083521783351898</v>
       </c>
       <c r="BU15" t="n">
-        <v>0.036716029047966</v>
+        <v>0.006151445209980011</v>
       </c>
       <c r="BV15" t="n">
-        <v>0.06992410123348236</v>
+        <v>0.2851584851741791</v>
       </c>
       <c r="BW15" t="n">
-        <v>0.06533464789390564</v>
+        <v>0.03563413396477699</v>
       </c>
       <c r="BX15" t="n">
-        <v>0.008153541944921017</v>
+        <v>0.03981605544686317</v>
       </c>
       <c r="BY15" t="n">
-        <v>0.0002993301022797823</v>
+        <v>0.02833758480846882</v>
       </c>
       <c r="BZ15" t="n">
-        <v>0.006257203873246908</v>
+        <v>0.003665499156340957</v>
       </c>
       <c r="CA15" t="n">
-        <v>0.04251027852296829</v>
+        <v>0.06869033724069595</v>
       </c>
       <c r="CB15" t="n">
-        <v>0.00431122537702322</v>
+        <v>0.01956103555858135</v>
       </c>
       <c r="CC15" t="n">
-        <v>0.01112858392298222</v>
+        <v>0.04389049485325813</v>
       </c>
       <c r="CD15" t="n">
-        <v>0.005766828544437885</v>
+        <v>0.020944494754076</v>
       </c>
       <c r="CE15" t="n">
-        <v>0.02576014026999474</v>
+        <v>0.1196321323513985</v>
       </c>
       <c r="CF15" t="n">
-        <v>0.003964953124523163</v>
+        <v>0.04447310417890549</v>
       </c>
       <c r="CG15" t="n">
-        <v>0.0260433554649353</v>
+        <v>0.06904159486293793</v>
       </c>
       <c r="CH15" t="n">
-        <v>0.02512980625033379</v>
+        <v>0.01729791238903999</v>
       </c>
       <c r="CI15" t="n">
-        <v>0.005807354580610991</v>
+        <v>0.02124295383691788</v>
       </c>
       <c r="CJ15" t="n">
-        <v>0.0002235998399555683</v>
+        <v>0.01976841315627098</v>
       </c>
       <c r="CK15" t="n">
-        <v>0.001513633411377668</v>
+        <v>0.008068344555795193</v>
       </c>
       <c r="CL15" t="n">
-        <v>0.01142157334834337</v>
+        <v>0.01381856109946966</v>
       </c>
       <c r="CM15" t="n">
-        <v>0.06445611268281937</v>
+        <v>0.1471789926290512</v>
       </c>
       <c r="CN15" t="n">
-        <v>0.02776951156556606</v>
+        <v>0.1483254432678223</v>
       </c>
       <c r="CO15" t="n">
-        <v>0.01741184294223785</v>
+        <v>0.04606162011623383</v>
       </c>
       <c r="CP15" t="n">
-        <v>0.0303267277777195</v>
+        <v>0.09622669965028763</v>
       </c>
       <c r="CQ15" t="n">
-        <v>0.008598390966653824</v>
+        <v>0.1590401828289032</v>
       </c>
       <c r="CR15" t="n">
-        <v>0.02623383887112141</v>
+        <v>0.05960822477936745</v>
       </c>
       <c r="CS15" t="n">
-        <v>0.005547823384404182</v>
+        <v>0.0290234200656414</v>
       </c>
       <c r="CT15" t="n">
-        <v>0.008572558872401714</v>
+        <v>0.07272132486104965</v>
       </c>
       <c r="CU15" t="n">
-        <v>0.001464062486775219</v>
+        <v>0.08770506829023361</v>
       </c>
       <c r="CV15" t="n">
-        <v>0.00751130934804678</v>
+        <v>0.03366252779960632</v>
       </c>
       <c r="CW15" t="n">
-        <v>0.0141034284606576</v>
+        <v>0.1091694980859756</v>
       </c>
       <c r="CX15" t="n">
-        <v>0.001796033582650125</v>
+        <v>0.03954031318426132</v>
       </c>
       <c r="CY15" t="n">
-        <v>0.02167339809238911</v>
+        <v>0.0491781085729599</v>
       </c>
       <c r="CZ15" t="n">
-        <v>0.02644706331193447</v>
+        <v>0.02313602715730667</v>
       </c>
       <c r="DA15" t="n">
-        <v>0.005965006072074175</v>
+        <v>0.02806699462234974</v>
       </c>
       <c r="DB15" t="n">
-        <v>0.002761401701718569</v>
+        <v>0.009564613923430443</v>
       </c>
       <c r="DC15" t="n">
-        <v>0.001476374920457602</v>
+        <v>0.003400044050067663</v>
       </c>
       <c r="DD15" t="n">
-        <v>0.01709262654185295</v>
+        <v>0.02720222249627113</v>
       </c>
       <c r="DE15" t="n">
-        <v>0.02001260034739971</v>
+        <v>0.1231509372591972</v>
       </c>
       <c r="DF15" t="n">
-        <v>0.08930326998233795</v>
+        <v>0.02990975230932236</v>
       </c>
       <c r="DG15" t="n">
-        <v>0.00647867564111948</v>
+        <v>0.0019066222012043</v>
       </c>
       <c r="DH15" t="n">
-        <v>0.03809370100498199</v>
+        <v>0.05026126652956009</v>
       </c>
       <c r="DI15" t="n">
-        <v>0.02297084964811802</v>
+        <v>0.08691659569740295</v>
       </c>
       <c r="DJ15" t="n">
-        <v>0.04310175031423569</v>
+        <v>0.1667022258043289</v>
       </c>
       <c r="DK15" t="n">
-        <v>0.04769197478890419</v>
+        <v>0.03249622136354446</v>
       </c>
       <c r="DL15" t="n">
-        <v>0.02860451862215996</v>
+        <v>0.08117904514074326</v>
       </c>
       <c r="DM15" t="n">
-        <v>0.008975273929536343</v>
+        <v>0.02092825621366501</v>
       </c>
       <c r="DN15" t="n">
-        <v>0.02648491039872169</v>
+        <v>0.02010911330580711</v>
       </c>
       <c r="DO15" t="n">
-        <v>0.02562973834574223</v>
+        <v>0.07374443858861923</v>
       </c>
       <c r="DP15" t="n">
-        <v>0.007624771911650896</v>
+        <v>0.005159320309758186</v>
       </c>
       <c r="DQ15" t="n">
-        <v>0.02200786396861076</v>
+        <v>0.004482286050915718</v>
       </c>
       <c r="DR15" t="n">
-        <v>0.0007751232478767633</v>
+        <v>0.01962776482105255</v>
       </c>
       <c r="DS15" t="n">
-        <v>0.01988519169390202</v>
+        <v>0.129573717713356</v>
       </c>
       <c r="DT15" t="n">
-        <v>0.01475626043975353</v>
+        <v>0.03368324786424637</v>
       </c>
       <c r="DU15" t="n">
-        <v>0.02552494779229164</v>
+        <v>0.05953303351998329</v>
       </c>
       <c r="DV15" t="n">
-        <v>0.01887303963303566</v>
+        <v>0.007032670080661774</v>
       </c>
       <c r="DW15" t="n">
-        <v>0.03488999605178833</v>
+        <v>0.04448831081390381</v>
       </c>
       <c r="DX15" t="n">
-        <v>0.006604420486837626</v>
+        <v>0.1379692852497101</v>
       </c>
       <c r="DY15" t="n">
-        <v>0.01000242959707975</v>
+        <v>0.09270070493221283</v>
       </c>
       <c r="DZ15" t="n">
-        <v>0.03888481110334396</v>
+        <v>0.01575685478746891</v>
       </c>
       <c r="EA15" t="n">
-        <v>0.02509506978094578</v>
+        <v>0.002677913755178452</v>
       </c>
       <c r="EB15" t="n">
-        <v>0.03204833343625069</v>
+        <v>0.09152336418628693</v>
       </c>
       <c r="EC15" t="n">
-        <v>0.01938971318304539</v>
+        <v>0.06101033091545105</v>
       </c>
       <c r="ED15" t="n">
-        <v>0.003209502436220646</v>
+        <v>0.002938344841822982</v>
       </c>
       <c r="EE15" t="n">
-        <v>0.008237580768764019</v>
+        <v>0.05881953611969948</v>
       </c>
       <c r="EF15" t="n">
-        <v>0.007214284967631102</v>
+        <v>0.04134210199117661</v>
       </c>
       <c r="EG15" t="n">
-        <v>0.009226007387042046</v>
+        <v>0.01888264715671539</v>
       </c>
       <c r="EH15" t="n">
-        <v>0.004931233357638121</v>
+        <v>0.03578335791826248</v>
       </c>
       <c r="EI15" t="n">
-        <v>0.03940292075276375</v>
+        <v>0.09629747271537781</v>
       </c>
       <c r="EJ15" t="n">
-        <v>0.02899158746004105</v>
+        <v>0.01170051004737616</v>
       </c>
       <c r="EK15" t="n">
-        <v>0.01813130266964436</v>
+        <v>0.01041417010128498</v>
       </c>
       <c r="EL15" t="n">
-        <v>0.02423266507685184</v>
+        <v>0.01019029319286346</v>
       </c>
       <c r="EM15" t="n">
-        <v>0.01554515119642019</v>
+        <v>0.0009198046755045652</v>
       </c>
       <c r="EN15" t="n">
-        <v>0.02066678553819656</v>
+        <v>0.0117301419377327</v>
       </c>
       <c r="EO15" t="n">
-        <v>0.01406373269855976</v>
+        <v>0.03109181113541126</v>
       </c>
       <c r="EP15" t="n">
-        <v>0.006666903384029865</v>
+        <v>0.07596442103385925</v>
       </c>
       <c r="EQ15" t="n">
-        <v>0.0315515361726284</v>
+        <v>0.002033255994319916</v>
       </c>
       <c r="ER15" t="n">
-        <v>0.005441290326416492</v>
+        <v>0.08713836222887039</v>
       </c>
       <c r="ES15" t="n">
-        <v>0.02822106890380383</v>
+        <v>0.001948697143234313</v>
       </c>
       <c r="ET15" t="n">
-        <v>0.0112704336643219</v>
+        <v>0.09691086411476135</v>
       </c>
       <c r="EU15" t="n">
-        <v>0.02490088157355785</v>
+        <v>0.001446951180696487</v>
       </c>
       <c r="EV15" t="n">
-        <v>0.01724489592015743</v>
+        <v>0.02551665157079697</v>
       </c>
       <c r="EW15" t="n">
-        <v>0.03516515716910362</v>
+        <v>0.03237627074122429</v>
       </c>
       <c r="EX15" t="n">
-        <v>0.006184790283441544</v>
+        <v>0.02459505014121532</v>
       </c>
       <c r="EY15" t="n">
-        <v>0.01453076116740704</v>
+        <v>0.128105491399765</v>
       </c>
       <c r="EZ15" t="n">
-        <v>0.001495983218774199</v>
+        <v>0.03482554852962494</v>
       </c>
       <c r="FA15" t="n">
-        <v>0.02744377963244915</v>
+        <v>0.04947857931256294</v>
       </c>
       <c r="FB15" t="n">
-        <v>0.03255492076277733</v>
+        <v>0.02882320806384087</v>
       </c>
       <c r="FC15" t="n">
-        <v>0.008262860588729382</v>
+        <v>0.03111718967556953</v>
       </c>
       <c r="FD15" t="n">
-        <v>0.003103805240243673</v>
+        <v>0.02007466554641724</v>
       </c>
       <c r="FE15" t="n">
-        <v>0.0004300308064557612</v>
+        <v>0.005410272628068924</v>
       </c>
       <c r="FF15" t="n">
-        <v>0.007860823534429073</v>
+        <v>0.02630200423300266</v>
       </c>
       <c r="FG15" t="n">
-        <v>0.04814270511269569</v>
+        <v>0.03097336553037167</v>
       </c>
       <c r="FH15" t="n">
-        <v>0.0332900732755661</v>
+        <v>0.01868747919797897</v>
       </c>
       <c r="FI15" t="n">
-        <v>0.023856271058321</v>
+        <v>0.007306739687919617</v>
       </c>
       <c r="FJ15" t="n">
-        <v>0.007621153257787228</v>
+        <v>0.00851922295987606</v>
       </c>
       <c r="FK15" t="n">
-        <v>0.01711449772119522</v>
+        <v>0.01269201841205359</v>
       </c>
       <c r="FL15" t="n">
-        <v>0.003624563803896308</v>
+        <v>0.0293673612177372</v>
       </c>
       <c r="FM15" t="n">
-        <v>0.02688107267022133</v>
+        <v>0.008020397275686264</v>
       </c>
       <c r="FN15" t="n">
-        <v>0.02598337270319462</v>
+        <v>0.1022765338420868</v>
       </c>
       <c r="FO15" t="n">
-        <v>0.01479048561304808</v>
+        <v>0.01107243821024895</v>
       </c>
       <c r="FP15" t="n">
-        <v>0.0168162677437067</v>
+        <v>0.1843595057725906</v>
       </c>
       <c r="FQ15" t="n">
-        <v>0.01314506679773331</v>
+        <v>0.05252936854958534</v>
       </c>
       <c r="FR15" t="n">
-        <v>0.03570446744561195</v>
+        <v>0.06705170869827271</v>
       </c>
       <c r="FS15" t="n">
-        <v>0.08216044306755066</v>
+        <v>0.0684238076210022</v>
       </c>
       <c r="FT15" t="n">
-        <v>0.04463142901659012</v>
+        <v>0.1377064883708954</v>
       </c>
       <c r="FU15" t="n">
-        <v>0.001102256122976542</v>
+        <v>0.07385040819644928</v>
       </c>
       <c r="FV15" t="n">
-        <v>0.01086058467626572</v>
+        <v>0.09958714246749878</v>
       </c>
       <c r="FW15" t="n">
-        <v>0.03936813399195671</v>
+        <v>0.03005875833332539</v>
       </c>
       <c r="FX15" t="n">
-        <v>0.008170614019036293</v>
+        <v>0.1066131442785263</v>
       </c>
       <c r="FY15" t="n">
-        <v>0.01403181068599224</v>
+        <v>0.05585342273116112</v>
       </c>
       <c r="FZ15" t="n">
-        <v>0.02965125255286694</v>
+        <v>0.03092851303517818</v>
       </c>
       <c r="GA15" t="n">
-        <v>0.01761110499501228</v>
+        <v>0.009719432331621647</v>
       </c>
       <c r="GB15" t="n">
-        <v>0.04848411306738853</v>
+        <v>0.006688127294182777</v>
       </c>
       <c r="GC15" t="n">
-        <v>0.0009786278242245317</v>
+        <v>0.06160762906074524</v>
       </c>
       <c r="GD15" t="n">
-        <v>0.04589315876364708</v>
+        <v>0.008277084678411484</v>
       </c>
       <c r="GE15" t="n">
-        <v>0.04322196543216705</v>
+        <v>0.01210255175828934</v>
       </c>
       <c r="GF15" t="n">
-        <v>0.003387385280802846</v>
+        <v>0.0729832649230957</v>
       </c>
       <c r="GG15" t="n">
-        <v>0.004732729867100716</v>
+        <v>0.03699399530887604</v>
       </c>
     </row>
   </sheetData>
